--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1815"/>
+  <dimension ref="A1:K1848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64594,6 +64594,1267 @@
         <v>2025</v>
       </c>
     </row>
+    <row r="1816">
+      <c r="A1816" s="1" t="n">
+        <v>1814</v>
+      </c>
+      <c r="B1816" t="inlineStr"/>
+      <c r="C1816" t="inlineStr"/>
+      <c r="D1816" t="inlineStr"/>
+      <c r="E1816" t="inlineStr"/>
+      <c r="F1816" t="inlineStr"/>
+      <c r="G1816" t="inlineStr"/>
+      <c r="H1816" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="I1816" t="inlineStr"/>
+      <c r="J1816" t="inlineStr"/>
+      <c r="K1816" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="1" t="n">
+        <v>1815</v>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>$111.02m (€103m)</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>02m</t>
+        </is>
+      </c>
+      <c r="D1817" t="inlineStr"/>
+      <c r="E1817" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F1817" t="n">
+        <v>111</v>
+      </c>
+      <c r="G1817" t="n">
+        <v>111</v>
+      </c>
+      <c r="H1817" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="I1817" t="n">
+        <v>102.6447198076568</v>
+      </c>
+      <c r="J1817" t="n">
+        <v>111</v>
+      </c>
+      <c r="K1817" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="1" t="n">
+        <v>1816</v>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>SEK10 billion (approximately $946 million)</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr"/>
+      <c r="D1818" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1818" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="F1818" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1818" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="H1818" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="I1818" t="n">
+        <v>882192070.8576671</v>
+      </c>
+      <c r="J1818" t="n">
+        <v>954002505.4254811</v>
+      </c>
+      <c r="K1818" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="1" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>2.5m euros ($2.7m)</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="D1819" t="inlineStr"/>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1819" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1819" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1819" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="I1819" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1819" t="n">
+        <v>2.1688</v>
+      </c>
+      <c r="K1819" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" s="1" t="n">
+        <v>1818</v>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>£423m</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr"/>
+      <c r="D1820" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1820" t="n">
+        <v>423</v>
+      </c>
+      <c r="G1820" t="n">
+        <v>423000000</v>
+      </c>
+      <c r="H1820" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1820" t="n">
+        <v>486514463.1663696</v>
+      </c>
+      <c r="J1820" t="n">
+        <v>512640289.8384036</v>
+      </c>
+      <c r="K1820" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" s="1" t="n">
+        <v>1819</v>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>£423m</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr"/>
+      <c r="D1821" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1821" t="n">
+        <v>423</v>
+      </c>
+      <c r="G1821" t="n">
+        <v>423000000</v>
+      </c>
+      <c r="H1821" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1821" t="n">
+        <v>486514463.1663696</v>
+      </c>
+      <c r="J1821" t="n">
+        <v>512640289.8384036</v>
+      </c>
+      <c r="K1821" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" s="1" t="n">
+        <v>1820</v>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>£423m</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr"/>
+      <c r="D1822" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1822" t="n">
+        <v>423</v>
+      </c>
+      <c r="G1822" t="n">
+        <v>423000000</v>
+      </c>
+      <c r="H1822" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1822" t="n">
+        <v>486514463.1663696</v>
+      </c>
+      <c r="J1822" t="n">
+        <v>512640289.8384036</v>
+      </c>
+      <c r="K1822" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" s="1" t="n">
+        <v>1821</v>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>up to £1.12bn</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>12bn</t>
+        </is>
+      </c>
+      <c r="D1823" t="inlineStr"/>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1823" t="inlineStr">
+        <is>
+          <t>[None, 1.0]</t>
+        </is>
+      </c>
+      <c r="G1823" t="inlineStr">
+        <is>
+          <t>[None, 1.0]</t>
+        </is>
+      </c>
+      <c r="H1823" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1823" t="inlineStr">
+        <is>
+          <t>[None, 1.1501523951923631]</t>
+        </is>
+      </c>
+      <c r="J1823" t="inlineStr">
+        <is>
+          <t>[None, 1.211915578814193]</t>
+        </is>
+      </c>
+      <c r="K1823" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" s="1" t="n">
+        <v>1822</v>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>up to £1.12bn</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>12bn</t>
+        </is>
+      </c>
+      <c r="D1824" t="inlineStr"/>
+      <c r="E1824" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1824" t="inlineStr">
+        <is>
+          <t>[None, 1.0]</t>
+        </is>
+      </c>
+      <c r="G1824" t="inlineStr">
+        <is>
+          <t>[None, 1.0]</t>
+        </is>
+      </c>
+      <c r="H1824" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1824" t="inlineStr">
+        <is>
+          <t>[None, 1.1501523951923631]</t>
+        </is>
+      </c>
+      <c r="J1824" t="inlineStr">
+        <is>
+          <t>[None, 1.211915578814193]</t>
+        </is>
+      </c>
+      <c r="K1824" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" s="1" t="n">
+        <v>1823</v>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>up to £1.12bn</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>12bn</t>
+        </is>
+      </c>
+      <c r="D1825" t="inlineStr"/>
+      <c r="E1825" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1825" t="inlineStr">
+        <is>
+          <t>[None, 1.0]</t>
+        </is>
+      </c>
+      <c r="G1825" t="inlineStr">
+        <is>
+          <t>[None, 1.0]</t>
+        </is>
+      </c>
+      <c r="H1825" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1825" t="inlineStr">
+        <is>
+          <t>[None, 1.1501523951923631]</t>
+        </is>
+      </c>
+      <c r="J1825" t="inlineStr">
+        <is>
+          <t>[None, 1.211915578814193]</t>
+        </is>
+      </c>
+      <c r="K1825" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" s="1" t="n">
+        <v>1824</v>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>up to £3bn</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr"/>
+      <c r="D1826" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1826" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1826" t="inlineStr">
+        <is>
+          <t>[None, 3.0]</t>
+        </is>
+      </c>
+      <c r="G1826" t="inlineStr">
+        <is>
+          <t>[None, 3000000000.0]</t>
+        </is>
+      </c>
+      <c r="H1826" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1826" t="inlineStr">
+        <is>
+          <t>[None, 3450457185.5770893]</t>
+        </is>
+      </c>
+      <c r="J1826" t="inlineStr">
+        <is>
+          <t>[None, 3635746736.4425793]</t>
+        </is>
+      </c>
+      <c r="K1826" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="1" t="n">
+        <v>1825</v>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>up to £3bn</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr"/>
+      <c r="D1827" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1827" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1827" t="inlineStr">
+        <is>
+          <t>[None, 3.0]</t>
+        </is>
+      </c>
+      <c r="G1827" t="inlineStr">
+        <is>
+          <t>[None, 3000000000.0]</t>
+        </is>
+      </c>
+      <c r="H1827" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1827" t="inlineStr">
+        <is>
+          <t>[None, 3450457185.5770893]</t>
+        </is>
+      </c>
+      <c r="J1827" t="inlineStr">
+        <is>
+          <t>[None, 3635746736.4425793]</t>
+        </is>
+      </c>
+      <c r="K1827" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="1" t="n">
+        <v>1826</v>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>up to £3bn</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr"/>
+      <c r="D1828" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1828" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1828" t="inlineStr">
+        <is>
+          <t>[None, 3.0]</t>
+        </is>
+      </c>
+      <c r="G1828" t="inlineStr">
+        <is>
+          <t>[None, 3000000000.0]</t>
+        </is>
+      </c>
+      <c r="H1828" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1828" t="inlineStr">
+        <is>
+          <t>[None, 3450457185.5770893]</t>
+        </is>
+      </c>
+      <c r="J1828" t="inlineStr">
+        <is>
+          <t>[None, 3635746736.4425793]</t>
+        </is>
+      </c>
+      <c r="K1828" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="1" t="n">
+        <v>1827</v>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>EUR850m</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr"/>
+      <c r="D1829" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1829" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1829" t="n">
+        <v>850</v>
+      </c>
+      <c r="G1829" t="n">
+        <v>850000000</v>
+      </c>
+      <c r="H1829" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="I1829" t="n">
+        <v>850000000</v>
+      </c>
+      <c r="J1829" t="n">
+        <v>921740000</v>
+      </c>
+      <c r="K1829" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="1" t="n">
+        <v>1828</v>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>EUR600m</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr"/>
+      <c r="D1830" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1830" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1830" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1830" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="H1830" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="I1830" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="J1830" t="n">
+        <v>650640000</v>
+      </c>
+      <c r="K1830" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="1" t="n">
+        <v>1829</v>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>EUR650m</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr"/>
+      <c r="D1831" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1831" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1831" t="n">
+        <v>650</v>
+      </c>
+      <c r="G1831" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="H1831" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="I1831" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="J1831" t="n">
+        <v>704860000</v>
+      </c>
+      <c r="K1831" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="1" t="n">
+        <v>1830</v>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>GBP250m</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr"/>
+      <c r="D1832" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1832" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1832" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1832" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="H1832" s="2" t="n">
+        <v>45200</v>
+      </c>
+      <c r="I1832" t="n">
+        <v>288779195.5766728</v>
+      </c>
+      <c r="J1832" t="n">
+        <v>304700555.2261333</v>
+      </c>
+      <c r="K1832" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="1" t="n">
+        <v>1831</v>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>GBP250m</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr"/>
+      <c r="D1833" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1833" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1833" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1833" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="H1833" s="2" t="n">
+        <v>45200</v>
+      </c>
+      <c r="I1833" t="n">
+        <v>288779195.5766728</v>
+      </c>
+      <c r="J1833" t="n">
+        <v>304700555.2261333</v>
+      </c>
+      <c r="K1833" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="1" t="n">
+        <v>1832</v>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>GBP250m</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr"/>
+      <c r="D1834" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1834" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1834" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1834" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="H1834" s="2" t="n">
+        <v>45200</v>
+      </c>
+      <c r="I1834" t="n">
+        <v>288779195.5766728</v>
+      </c>
+      <c r="J1834" t="n">
+        <v>304700555.2261333</v>
+      </c>
+      <c r="K1834" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="1" t="n">
+        <v>1833</v>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>EUR400m</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr"/>
+      <c r="D1835" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1835" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1835" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1835" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="H1835" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1835" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="J1835" t="n">
+        <v>421480000.0000001</v>
+      </c>
+      <c r="K1835" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="1" t="n">
+        <v>1834</v>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>£2.5 billion</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr"/>
+      <c r="D1836" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1836" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1836" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G1836" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="H1836" s="2" t="n">
+        <v>45200</v>
+      </c>
+      <c r="I1836" t="n">
+        <v>2887791955.766728</v>
+      </c>
+      <c r="J1836" t="n">
+        <v>3047005552.261333</v>
+      </c>
+      <c r="K1836" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="1" t="n">
+        <v>1835</v>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>GBP4bn</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr"/>
+      <c r="D1837" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1837" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="H1837" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1837" t="n">
+        <v>4600609580.769452</v>
+      </c>
+      <c r="J1837" t="n">
+        <v>4847662315.256772</v>
+      </c>
+      <c r="K1837" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="1" t="n">
+        <v>1836</v>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>GBP1bn</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr"/>
+      <c r="D1838" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1838" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1838" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1838" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="H1838" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1838" t="n">
+        <v>1150152395.192363</v>
+      </c>
+      <c r="J1838" t="n">
+        <v>1211915578.814193</v>
+      </c>
+      <c r="K1838" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="1" t="n">
+        <v>1837</v>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>GBP1bn</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr"/>
+      <c r="D1839" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1839" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1839" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1839" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="H1839" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1839" t="n">
+        <v>1150152395.192363</v>
+      </c>
+      <c r="J1839" t="n">
+        <v>1211915578.814193</v>
+      </c>
+      <c r="K1839" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="1" t="n">
+        <v>1838</v>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>EUR400m</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr"/>
+      <c r="D1840" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1840" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1840" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="H1840" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1840" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="J1840" t="n">
+        <v>421480000.0000001</v>
+      </c>
+      <c r="K1840" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="1" t="n">
+        <v>1839</v>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>GBP3bn</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr"/>
+      <c r="D1841" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1841" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1841" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1841" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="H1841" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1841" t="n">
+        <v>3450457185.577089</v>
+      </c>
+      <c r="J1841" t="n">
+        <v>3635746736.442579</v>
+      </c>
+      <c r="K1841" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="1" t="n">
+        <v>1840</v>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>GBP3bn</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr"/>
+      <c r="D1842" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1842" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1842" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="H1842" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1842" t="n">
+        <v>3450457185.577089</v>
+      </c>
+      <c r="J1842" t="n">
+        <v>3635746736.442579</v>
+      </c>
+      <c r="K1842" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="1" t="n">
+        <v>1841</v>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>GBP3bn</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr"/>
+      <c r="D1843" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1843" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1843" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="H1843" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1843" t="n">
+        <v>3450457185.577089</v>
+      </c>
+      <c r="J1843" t="n">
+        <v>3635746736.442579</v>
+      </c>
+      <c r="K1843" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="1" t="n">
+        <v>1842</v>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>GBP100m</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr"/>
+      <c r="D1844" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1844" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="H1844" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="I1844" t="n">
+        <v>116907105.6138792</v>
+      </c>
+      <c r="J1844" t="n">
+        <v>126774065.3276906</v>
+      </c>
+      <c r="K1844" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="1" t="n">
+        <v>1843</v>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>GBP100m</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr"/>
+      <c r="D1845" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1845" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1845" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1845" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="H1845" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="I1845" t="n">
+        <v>116907105.6138792</v>
+      </c>
+      <c r="J1845" t="n">
+        <v>126774065.3276906</v>
+      </c>
+      <c r="K1845" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="1" t="n">
+        <v>1844</v>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>GBP100m</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr"/>
+      <c r="D1846" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1846" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1846" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="H1846" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="I1846" t="n">
+        <v>116907105.6138792</v>
+      </c>
+      <c r="J1846" t="n">
+        <v>126774065.3276906</v>
+      </c>
+      <c r="K1846" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="1" t="n">
+        <v>1845</v>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>GBP100m</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr"/>
+      <c r="D1847" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1847" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="H1847" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="I1847" t="n">
+        <v>116907105.6138792</v>
+      </c>
+      <c r="J1847" t="n">
+        <v>126774065.3276906</v>
+      </c>
+      <c r="K1847" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="1" t="n">
+        <v>1846</v>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>GBP100m</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr"/>
+      <c r="D1848" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1848" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F1848" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="H1848" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="I1848" t="n">
+        <v>116907105.6138792</v>
+      </c>
+      <c r="J1848" t="n">
+        <v>126774065.3276906</v>
+      </c>
+      <c r="K1848" t="n">
+        <v>2023</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -62747,32 +62747,32 @@
       </c>
       <c r="B1747" t="inlineStr">
         <is>
-          <t>SEK 10 billion (c.£808 million)</t>
+          <t>€956 million</t>
         </is>
       </c>
       <c r="C1747" t="inlineStr"/>
       <c r="D1747" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="E1747" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F1747" t="n">
-        <v>10</v>
+        <v>956</v>
       </c>
       <c r="G1747" t="n">
-        <v>10000000000</v>
+        <v>956000000</v>
       </c>
       <c r="H1747" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="I1747" t="n">
-        <v>957505888.6612153</v>
+        <v>956000000</v>
       </c>
       <c r="J1747" t="n">
-        <v>1078151630.632528</v>
+        <v>1076456000</v>
       </c>
       <c r="K1747" t="n">
         <v>2022</v>
@@ -62932,35 +62932,35 @@
       </c>
       <c r="B1752" t="inlineStr">
         <is>
-          <t>€160 million ($176 million)</t>
+          <t>SEK 10 billion (c.£808 million)</t>
         </is>
       </c>
       <c r="C1752" t="inlineStr"/>
       <c r="D1752" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="E1752" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="F1752" t="n">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="G1752" t="n">
-        <v>160000000</v>
+        <v>10000000000</v>
       </c>
       <c r="H1752" s="2" t="n">
-        <v>45078</v>
+        <v>44593</v>
       </c>
       <c r="I1752" t="n">
-        <v>160000000</v>
+        <v>957505888.6612153</v>
       </c>
       <c r="J1752" t="n">
-        <v>171152000</v>
+        <v>1078151630.632528</v>
       </c>
       <c r="K1752" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1753">
@@ -63043,7 +63043,7 @@
       </c>
       <c r="B1755" t="inlineStr">
         <is>
-          <t>€550 million</t>
+          <t>€160 million ($176 million)</t>
         </is>
       </c>
       <c r="C1755" t="inlineStr"/>
@@ -63056,22 +63056,22 @@
         </is>
       </c>
       <c r="F1755" t="n">
-        <v>550</v>
+        <v>160</v>
       </c>
       <c r="G1755" t="n">
-        <v>550000000</v>
+        <v>160000000</v>
       </c>
       <c r="H1755" s="2" t="n">
-        <v>44440</v>
+        <v>45078</v>
       </c>
       <c r="I1755" t="n">
-        <v>550000000</v>
+        <v>160000000</v>
       </c>
       <c r="J1755" t="n">
-        <v>649935000</v>
+        <v>171152000</v>
       </c>
       <c r="K1755" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1756">
@@ -63115,56 +63115,56 @@
       <c r="A1757" s="1" t="n">
         <v>1755</v>
       </c>
-      <c r="B1757" t="inlineStr"/>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>€550 million</t>
+        </is>
+      </c>
       <c r="C1757" t="inlineStr"/>
-      <c r="D1757" t="inlineStr"/>
-      <c r="E1757" t="inlineStr"/>
-      <c r="F1757" t="inlineStr"/>
-      <c r="G1757" t="inlineStr"/>
+      <c r="D1757" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1757" t="n">
+        <v>550</v>
+      </c>
+      <c r="G1757" t="n">
+        <v>550000000</v>
+      </c>
       <c r="H1757" s="2" t="n">
-        <v>44835</v>
-      </c>
-      <c r="I1757" t="inlineStr"/>
-      <c r="J1757" t="inlineStr"/>
+        <v>44440</v>
+      </c>
+      <c r="I1757" t="n">
+        <v>550000000</v>
+      </c>
+      <c r="J1757" t="n">
+        <v>649935000</v>
+      </c>
       <c r="K1757" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1758">
       <c r="A1758" s="1" t="n">
         <v>1756</v>
       </c>
-      <c r="B1758" t="inlineStr">
-        <is>
-          <t>500 million euros ($589 million)</t>
-        </is>
-      </c>
+      <c r="B1758" t="inlineStr"/>
       <c r="C1758" t="inlineStr"/>
-      <c r="D1758" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E1758" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F1758" t="n">
-        <v>500</v>
-      </c>
-      <c r="G1758" t="n">
-        <v>500000000</v>
-      </c>
+      <c r="D1758" t="inlineStr"/>
+      <c r="E1758" t="inlineStr"/>
+      <c r="F1758" t="inlineStr"/>
+      <c r="G1758" t="inlineStr"/>
       <c r="H1758" s="2" t="n">
-        <v>43221</v>
-      </c>
-      <c r="I1758" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="J1758" t="n">
-        <v>602150000</v>
-      </c>
+        <v>44835</v>
+      </c>
+      <c r="I1758" t="inlineStr"/>
+      <c r="J1758" t="inlineStr"/>
       <c r="K1758" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1759">
@@ -63173,7 +63173,7 @@
       </c>
       <c r="B1759" t="inlineStr">
         <is>
-          <t>800 million euros</t>
+          <t>500 million euros ($589 million)</t>
         </is>
       </c>
       <c r="C1759" t="inlineStr"/>
@@ -63186,22 +63186,22 @@
         </is>
       </c>
       <c r="F1759" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G1759" t="n">
-        <v>800000000</v>
+        <v>500000000</v>
       </c>
       <c r="H1759" s="2" t="n">
-        <v>45901</v>
+        <v>43221</v>
       </c>
       <c r="I1759" t="n">
-        <v>800000000</v>
+        <v>500000000</v>
       </c>
       <c r="J1759" t="n">
-        <v>932320000</v>
+        <v>602150000</v>
       </c>
       <c r="K1759" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1760">
@@ -63210,7 +63210,7 @@
       </c>
       <c r="B1760" t="inlineStr">
         <is>
-          <t>€680m</t>
+          <t>800 million euros</t>
         </is>
       </c>
       <c r="C1760" t="inlineStr"/>
@@ -63223,19 +63223,19 @@
         </is>
       </c>
       <c r="F1760" t="n">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="G1760" t="n">
-        <v>680000000</v>
+        <v>800000000</v>
       </c>
       <c r="H1760" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="I1760" t="n">
-        <v>680000000</v>
+        <v>800000000</v>
       </c>
       <c r="J1760" t="n">
-        <v>792472000</v>
+        <v>932320000</v>
       </c>
       <c r="K1760" t="n">
         <v>2025</v>
@@ -63245,17 +63245,35 @@
       <c r="A1761" s="1" t="n">
         <v>1759</v>
       </c>
-      <c r="B1761" t="inlineStr"/>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>€680m</t>
+        </is>
+      </c>
       <c r="C1761" t="inlineStr"/>
-      <c r="D1761" t="inlineStr"/>
-      <c r="E1761" t="inlineStr"/>
-      <c r="F1761" t="inlineStr"/>
-      <c r="G1761" t="inlineStr"/>
+      <c r="D1761" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1761" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1761" t="n">
+        <v>680</v>
+      </c>
+      <c r="G1761" t="n">
+        <v>680000000</v>
+      </c>
       <c r="H1761" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="I1761" t="inlineStr"/>
-      <c r="J1761" t="inlineStr"/>
+      <c r="I1761" t="n">
+        <v>680000000</v>
+      </c>
+      <c r="J1761" t="n">
+        <v>792472000</v>
+      </c>
       <c r="K1761" t="n">
         <v>2025</v>
       </c>
@@ -63264,35 +63282,17 @@
       <c r="A1762" s="1" t="n">
         <v>1760</v>
       </c>
-      <c r="B1762" t="inlineStr">
-        <is>
-          <t>€690 million</t>
-        </is>
-      </c>
+      <c r="B1762" t="inlineStr"/>
       <c r="C1762" t="inlineStr"/>
-      <c r="D1762" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E1762" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F1762" t="n">
-        <v>690</v>
-      </c>
-      <c r="G1762" t="n">
-        <v>690000000</v>
-      </c>
+      <c r="D1762" t="inlineStr"/>
+      <c r="E1762" t="inlineStr"/>
+      <c r="F1762" t="inlineStr"/>
+      <c r="G1762" t="inlineStr"/>
       <c r="H1762" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="I1762" t="n">
-        <v>690000000</v>
-      </c>
-      <c r="J1762" t="n">
-        <v>804126000</v>
-      </c>
+      <c r="I1762" t="inlineStr"/>
+      <c r="J1762" t="inlineStr"/>
       <c r="K1762" t="n">
         <v>2025</v>
       </c>
@@ -63340,7 +63340,7 @@
       </c>
       <c r="B1764" t="inlineStr">
         <is>
-          <t>€680m</t>
+          <t>€690 million</t>
         </is>
       </c>
       <c r="C1764" t="inlineStr"/>
@@ -63353,19 +63353,19 @@
         </is>
       </c>
       <c r="F1764" t="n">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="G1764" t="n">
-        <v>680000000</v>
+        <v>690000000</v>
       </c>
       <c r="H1764" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="I1764" t="n">
-        <v>680000000</v>
+        <v>690000000</v>
       </c>
       <c r="J1764" t="n">
-        <v>792472000</v>
+        <v>804126000</v>
       </c>
       <c r="K1764" t="n">
         <v>2025</v>
@@ -63377,7 +63377,7 @@
       </c>
       <c r="B1765" t="inlineStr">
         <is>
-          <t>€55 million</t>
+          <t>€680m</t>
         </is>
       </c>
       <c r="C1765" t="inlineStr"/>
@@ -63390,19 +63390,19 @@
         </is>
       </c>
       <c r="F1765" t="n">
-        <v>55</v>
+        <v>680</v>
       </c>
       <c r="G1765" t="n">
-        <v>55000000</v>
+        <v>680000000</v>
       </c>
       <c r="H1765" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="I1765" t="n">
-        <v>55000000</v>
+        <v>680000000</v>
       </c>
       <c r="J1765" t="n">
-        <v>64097000</v>
+        <v>792472000</v>
       </c>
       <c r="K1765" t="n">
         <v>2025</v>
@@ -63412,17 +63412,35 @@
       <c r="A1766" s="1" t="n">
         <v>1764</v>
       </c>
-      <c r="B1766" t="inlineStr"/>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>€55 million</t>
+        </is>
+      </c>
       <c r="C1766" t="inlineStr"/>
-      <c r="D1766" t="inlineStr"/>
-      <c r="E1766" t="inlineStr"/>
-      <c r="F1766" t="inlineStr"/>
-      <c r="G1766" t="inlineStr"/>
+      <c r="D1766" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1766" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1766" t="n">
+        <v>55</v>
+      </c>
+      <c r="G1766" t="n">
+        <v>55000000</v>
+      </c>
       <c r="H1766" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="I1766" t="inlineStr"/>
-      <c r="J1766" t="inlineStr"/>
+      <c r="I1766" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="J1766" t="n">
+        <v>64097000</v>
+      </c>
       <c r="K1766" t="n">
         <v>2025</v>
       </c>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1955"/>
+  <dimension ref="A1:K1970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70394,6 +70394,559 @@
         <v>2024</v>
       </c>
     </row>
+    <row r="1956">
+      <c r="A1956" s="1" t="n">
+        <v>1954</v>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>around two billion euros</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr"/>
+      <c r="D1956" t="inlineStr"/>
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1956" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G1956" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="H1956" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="I1956" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="J1956" t="n">
+        <v>1081300000</v>
+      </c>
+      <c r="K1956" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="1" t="n">
+        <v>1955</v>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>50 million euro</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr"/>
+      <c r="D1957" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1957" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1957" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="H1957" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I1957" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="J1957" t="n">
+        <v>58270000</v>
+      </c>
+      <c r="K1957" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="1" t="n">
+        <v>1956</v>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>50 million euro</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr"/>
+      <c r="D1958" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1958" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1958" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="H1958" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I1958" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="J1958" t="n">
+        <v>58270000</v>
+      </c>
+      <c r="K1958" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="1" t="n">
+        <v>1957</v>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>50 million euro</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr"/>
+      <c r="D1959" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1959" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1959" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="H1959" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I1959" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="J1959" t="n">
+        <v>58270000</v>
+      </c>
+      <c r="K1959" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="1" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>50 million euro</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr"/>
+      <c r="D1960" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1960" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1960" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="H1960" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I1960" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="J1960" t="n">
+        <v>58270000</v>
+      </c>
+      <c r="K1960" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="1" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>€1.8 billion</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr"/>
+      <c r="D1961" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1961" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G1961" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="H1961" s="2" t="n">
+        <v>45597</v>
+      </c>
+      <c r="I1961" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="J1961" t="n">
+        <v>1959300000</v>
+      </c>
+      <c r="K1961" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>€1.8 billion</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr"/>
+      <c r="D1962" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1962" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G1962" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="H1962" s="2" t="n">
+        <v>45597</v>
+      </c>
+      <c r="I1962" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="J1962" t="n">
+        <v>1959300000</v>
+      </c>
+      <c r="K1962" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>€1.8 billion</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr"/>
+      <c r="D1963" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1963" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1963" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G1963" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="H1963" s="2" t="n">
+        <v>45597</v>
+      </c>
+      <c r="I1963" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="J1963" t="n">
+        <v>1959300000</v>
+      </c>
+      <c r="K1963" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="1" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>SEK 6.2 billion</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr"/>
+      <c r="D1964" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="F1964" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G1964" t="n">
+        <v>6200000000</v>
+      </c>
+      <c r="H1964" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I1964" t="n">
+        <v>525156699.9830595</v>
+      </c>
+      <c r="J1964" t="n">
+        <v>553357614.7721499</v>
+      </c>
+      <c r="K1964" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="1" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>€13.6 million</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr"/>
+      <c r="D1965" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1965" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G1965" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="H1965" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I1965" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="J1965" t="n">
+        <v>15849440</v>
+      </c>
+      <c r="K1965" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>€13.6 million</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr"/>
+      <c r="D1966" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1966" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1966" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G1966" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="H1966" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I1966" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="J1966" t="n">
+        <v>15849440</v>
+      </c>
+      <c r="K1966" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="1" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>€13.6 million</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr"/>
+      <c r="D1967" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1967" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G1967" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="H1967" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I1967" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="J1967" t="n">
+        <v>15849440</v>
+      </c>
+      <c r="K1967" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="1" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>€1.65 billion</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr"/>
+      <c r="D1968" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1968" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1968" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G1968" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="H1968" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I1968" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="J1968" t="n">
+        <v>1772925000</v>
+      </c>
+      <c r="K1968" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="1" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>€1.65 billion</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr"/>
+      <c r="D1969" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1969" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1969" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G1969" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="H1969" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I1969" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="J1969" t="n">
+        <v>1772925000</v>
+      </c>
+      <c r="K1969" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="1" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>€1.65 billion</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr"/>
+      <c r="D1970" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E1970" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F1970" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G1970" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="H1970" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I1970" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="J1970" t="n">
+        <v>1772925000</v>
+      </c>
+      <c r="K1970" t="n">
+        <v>2024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1970"/>
+  <dimension ref="A1:J1991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65040,6 +65040,762 @@
         <v>2024</v>
       </c>
     </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>single-digit billion-euro sum</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>single digit billion</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr"/>
+      <c r="D1971" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1971" t="inlineStr"/>
+      <c r="F1971" t="inlineStr"/>
+      <c r="G1971" s="2" t="n">
+        <v>44713</v>
+      </c>
+      <c r="H1971" t="inlineStr"/>
+      <c r="I1971" t="inlineStr"/>
+      <c r="J1971" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>single-digit billion-euro sum</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>single digit billion</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr"/>
+      <c r="D1972" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1972" t="inlineStr"/>
+      <c r="F1972" t="inlineStr"/>
+      <c r="G1972" s="2" t="n">
+        <v>44713</v>
+      </c>
+      <c r="H1972" t="inlineStr"/>
+      <c r="I1972" t="inlineStr"/>
+      <c r="J1972" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>single-digit billion-euro sum</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>single digit billion</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr"/>
+      <c r="D1973" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1973" t="inlineStr"/>
+      <c r="F1973" t="inlineStr"/>
+      <c r="G1973" s="2" t="n">
+        <v>44713</v>
+      </c>
+      <c r="H1973" t="inlineStr"/>
+      <c r="I1973" t="inlineStr"/>
+      <c r="J1973" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>EUR 3.5 billion</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr"/>
+      <c r="C1974" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1974" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1974" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1974" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="G1974" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H1974" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="I1974" t="n">
+        <v>3743950000</v>
+      </c>
+      <c r="J1974" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>EUR 3.5 billion</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr"/>
+      <c r="C1975" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1975" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1975" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1975" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="G1975" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H1975" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="I1975" t="n">
+        <v>3743950000</v>
+      </c>
+      <c r="J1975" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>EUR 3.5 billion</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr"/>
+      <c r="C1976" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1976" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1976" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1976" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="G1976" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H1976" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="I1976" t="n">
+        <v>3743950000</v>
+      </c>
+      <c r="J1976" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>EUR 3.5 billion</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr"/>
+      <c r="C1977" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1977" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1977" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1977" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="G1977" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H1977" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="I1977" t="n">
+        <v>3743950000</v>
+      </c>
+      <c r="J1977" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>€1 billion</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr"/>
+      <c r="C1978" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1978" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1978" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1978" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G1978" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="H1978" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I1978" t="n">
+        <v>1081300000</v>
+      </c>
+      <c r="J1978" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>€1.8 billion</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr"/>
+      <c r="C1979" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1979" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1979" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F1979" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="G1979" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="H1979" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="I1979" t="n">
+        <v>1946340000</v>
+      </c>
+      <c r="J1979" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>€1.8 billion</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr"/>
+      <c r="C1980" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1980" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1980" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F1980" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="G1980" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="H1980" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="I1980" t="n">
+        <v>1946340000</v>
+      </c>
+      <c r="J1980" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>€1.8 billion</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr"/>
+      <c r="C1981" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1981" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1981" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F1981" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="G1981" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="H1981" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="I1981" t="n">
+        <v>1946340000</v>
+      </c>
+      <c r="J1981" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr"/>
+      <c r="C1982" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1982" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1982" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G1982" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H1982" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1982" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
+      </c>
+      <c r="J1982" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr"/>
+      <c r="C1983" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1983" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1983" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1983" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G1983" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H1983" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1983" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
+      </c>
+      <c r="J1983" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr"/>
+      <c r="C1984" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1984" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1984" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G1984" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H1984" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1984" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
+      </c>
+      <c r="J1984" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr"/>
+      <c r="C1985" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1985" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1985" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G1985" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H1985" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1985" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
+      </c>
+      <c r="J1985" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr"/>
+      <c r="C1986" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1986" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1986" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1986" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G1986" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H1986" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1986" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
+      </c>
+      <c r="J1986" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr"/>
+      <c r="C1987" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1987" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1987" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1987" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G1987" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H1987" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1987" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
+      </c>
+      <c r="J1987" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr"/>
+      <c r="C1988" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1988" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1988" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1988" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G1988" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H1988" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1988" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
+      </c>
+      <c r="J1988" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr"/>
+      <c r="C1989" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1989" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1989" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G1989" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H1989" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1989" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
+      </c>
+      <c r="J1989" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>two billion euros</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr"/>
+      <c r="C1990" t="inlineStr"/>
+      <c r="D1990" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1990" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F1990" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G1990" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="H1990" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I1990" t="n">
+        <v>1053700000</v>
+      </c>
+      <c r="J1990" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>two billion euros</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr"/>
+      <c r="C1991" t="inlineStr"/>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1991" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F1991" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G1991" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="H1991" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I1991" t="n">
+        <v>1053700000</v>
+      </c>
+      <c r="J1991" t="n">
+        <v>2023</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1991"/>
+  <dimension ref="A1:J2048"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64535,33 +64535,35 @@
     <row r="1956">
       <c r="A1956" t="inlineStr">
         <is>
-          <t>around two billion euros</t>
+          <t>50 million euro</t>
         </is>
       </c>
       <c r="B1956" t="inlineStr"/>
-      <c r="C1956" t="inlineStr"/>
+      <c r="C1956" t="n">
+        <v>1000000</v>
+      </c>
       <c r="D1956" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
       <c r="E1956" t="n">
-        <v>1000000000</v>
+        <v>50</v>
       </c>
       <c r="F1956" t="n">
-        <v>1000000000</v>
+        <v>50000000</v>
       </c>
       <c r="G1956" s="2" t="n">
-        <v>45352</v>
+        <v>45901</v>
       </c>
       <c r="H1956" t="n">
-        <v>1000000000</v>
+        <v>50000000</v>
       </c>
       <c r="I1956" t="n">
-        <v>1081300000</v>
+        <v>58270000</v>
       </c>
       <c r="J1956" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1957">
@@ -64669,12 +64671,12 @@
     <row r="1960">
       <c r="A1960" t="inlineStr">
         <is>
-          <t>50 million euro</t>
+          <t>€1.8 billion</t>
         </is>
       </c>
       <c r="B1960" t="inlineStr"/>
       <c r="C1960" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1960" t="inlineStr">
         <is>
@@ -64682,22 +64684,22 @@
         </is>
       </c>
       <c r="E1960" t="n">
-        <v>50</v>
+        <v>1.8</v>
       </c>
       <c r="F1960" t="n">
-        <v>50000000</v>
+        <v>1800000000</v>
       </c>
       <c r="G1960" s="2" t="n">
-        <v>45901</v>
+        <v>45597</v>
       </c>
       <c r="H1960" t="n">
-        <v>50000000</v>
+        <v>1800000000</v>
       </c>
       <c r="I1960" t="n">
-        <v>58270000</v>
+        <v>1959300000</v>
       </c>
       <c r="J1960" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1961">
@@ -64771,7 +64773,7 @@
     <row r="1963">
       <c r="A1963" t="inlineStr">
         <is>
-          <t>€1.8 billion</t>
+          <t>SEK 6.2 billion</t>
         </is>
       </c>
       <c r="B1963" t="inlineStr"/>
@@ -64780,60 +64782,60 @@
       </c>
       <c r="D1963" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="E1963" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="F1963" t="n">
-        <v>1800000000</v>
+        <v>6200000000</v>
       </c>
       <c r="G1963" s="2" t="n">
-        <v>45597</v>
+        <v>45231</v>
       </c>
       <c r="H1963" t="n">
-        <v>1800000000</v>
+        <v>525156699.9830595</v>
       </c>
       <c r="I1963" t="n">
-        <v>1959300000</v>
+        <v>553357614.7721499</v>
       </c>
       <c r="J1963" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1964">
       <c r="A1964" t="inlineStr">
         <is>
-          <t>SEK 6.2 billion</t>
+          <t>€13.6 million</t>
         </is>
       </c>
       <c r="B1964" t="inlineStr"/>
       <c r="C1964" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1964" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1964" t="n">
-        <v>6.2</v>
+        <v>13.6</v>
       </c>
       <c r="F1964" t="n">
-        <v>6200000000</v>
+        <v>13600000</v>
       </c>
       <c r="G1964" s="2" t="n">
-        <v>45231</v>
+        <v>45901</v>
       </c>
       <c r="H1964" t="n">
-        <v>525156699.9830595</v>
+        <v>13600000</v>
       </c>
       <c r="I1964" t="n">
-        <v>553357614.7721499</v>
+        <v>15849440</v>
       </c>
       <c r="J1964" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1965">
@@ -64907,12 +64909,12 @@
     <row r="1967">
       <c r="A1967" t="inlineStr">
         <is>
-          <t>€13.6 million</t>
+          <t>€1.65 billion</t>
         </is>
       </c>
       <c r="B1967" t="inlineStr"/>
       <c r="C1967" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1967" t="inlineStr">
         <is>
@@ -64920,22 +64922,22 @@
         </is>
       </c>
       <c r="E1967" t="n">
-        <v>13.6</v>
+        <v>1.65</v>
       </c>
       <c r="F1967" t="n">
-        <v>13600000</v>
+        <v>1650000000</v>
       </c>
       <c r="G1967" s="2" t="n">
-        <v>45901</v>
+        <v>45474</v>
       </c>
       <c r="H1967" t="n">
-        <v>13600000</v>
+        <v>1650000000</v>
       </c>
       <c r="I1967" t="n">
-        <v>15849440</v>
+        <v>1772925000</v>
       </c>
       <c r="J1967" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1968">
@@ -65009,35 +65011,29 @@
     <row r="1970">
       <c r="A1970" t="inlineStr">
         <is>
-          <t>€1.65 billion</t>
-        </is>
-      </c>
-      <c r="B1970" t="inlineStr"/>
-      <c r="C1970" t="n">
-        <v>1000000000</v>
-      </c>
+          <t>single-digit billion-euro sum</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>single digit billion</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr"/>
       <c r="D1970" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1970" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="F1970" t="n">
-        <v>1650000000</v>
-      </c>
+      <c r="E1970" t="inlineStr"/>
+      <c r="F1970" t="inlineStr"/>
       <c r="G1970" s="2" t="n">
-        <v>45474</v>
-      </c>
-      <c r="H1970" t="n">
-        <v>1650000000</v>
-      </c>
-      <c r="I1970" t="n">
-        <v>1772925000</v>
-      </c>
+        <v>44713</v>
+      </c>
+      <c r="H1970" t="inlineStr"/>
+      <c r="I1970" t="inlineStr"/>
       <c r="J1970" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1971">
@@ -65099,29 +65095,35 @@
     <row r="1973">
       <c r="A1973" t="inlineStr">
         <is>
-          <t>single-digit billion-euro sum</t>
-        </is>
-      </c>
-      <c r="B1973" t="inlineStr">
-        <is>
-          <t>single digit billion</t>
-        </is>
-      </c>
-      <c r="C1973" t="inlineStr"/>
+          <t>EUR 3.5 billion</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr"/>
+      <c r="C1973" t="n">
+        <v>1000000000</v>
+      </c>
       <c r="D1973" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1973" t="inlineStr"/>
-      <c r="F1973" t="inlineStr"/>
+      <c r="E1973" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1973" t="n">
+        <v>3500000000</v>
+      </c>
       <c r="G1973" s="2" t="n">
-        <v>44713</v>
-      </c>
-      <c r="H1973" t="inlineStr"/>
-      <c r="I1973" t="inlineStr"/>
+        <v>45078</v>
+      </c>
+      <c r="H1973" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="I1973" t="n">
+        <v>3743950000</v>
+      </c>
       <c r="J1973" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1974">
@@ -65229,7 +65231,7 @@
     <row r="1977">
       <c r="A1977" t="inlineStr">
         <is>
-          <t>EUR 3.5 billion</t>
+          <t>€1 billion</t>
         </is>
       </c>
       <c r="B1977" t="inlineStr"/>
@@ -65242,28 +65244,28 @@
         </is>
       </c>
       <c r="E1977" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="F1977" t="n">
-        <v>3500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G1977" s="2" t="n">
-        <v>45078</v>
+        <v>45352</v>
       </c>
       <c r="H1977" t="n">
-        <v>3500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I1977" t="n">
-        <v>3743950000</v>
+        <v>1081300000</v>
       </c>
       <c r="J1977" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1978">
       <c r="A1978" t="inlineStr">
         <is>
-          <t>€1 billion</t>
+          <t>€1.8 billion</t>
         </is>
       </c>
       <c r="B1978" t="inlineStr"/>
@@ -65276,19 +65278,19 @@
         </is>
       </c>
       <c r="E1978" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="F1978" t="n">
-        <v>1000000000</v>
+        <v>1800000000</v>
       </c>
       <c r="G1978" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="H1978" t="n">
-        <v>1000000000</v>
+        <v>1800000000</v>
       </c>
       <c r="I1978" t="n">
-        <v>1081300000</v>
+        <v>1946340000</v>
       </c>
       <c r="J1978" t="n">
         <v>2024</v>
@@ -65365,7 +65367,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>€1.8 billion</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr"/>
@@ -65377,23 +65379,31 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1981" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F1981" t="n">
-        <v>1800000000</v>
+      <c r="E1981" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1981" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G1981" s="2" t="n">
-        <v>45352</v>
-      </c>
-      <c r="H1981" t="n">
-        <v>1800000000</v>
-      </c>
-      <c r="I1981" t="n">
-        <v>1946340000</v>
+        <v>44256</v>
+      </c>
+      <c r="H1981" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1981" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
       </c>
       <c r="J1981" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1982">
@@ -65693,43 +65703,33 @@
     <row r="1989">
       <c r="A1989" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>two billion euros</t>
         </is>
       </c>
       <c r="B1989" t="inlineStr"/>
-      <c r="C1989" t="n">
-        <v>1000000000</v>
-      </c>
+      <c r="C1989" t="inlineStr"/>
       <c r="D1989" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1989" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F1989" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+      <c r="E1989" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F1989" t="n">
+        <v>1000000000</v>
       </c>
       <c r="G1989" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="H1989" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I1989" t="inlineStr">
-        <is>
-          <t>[1205300000.0, 1807950000.0]</t>
-        </is>
+        <v>45231</v>
+      </c>
+      <c r="H1989" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I1989" t="n">
+        <v>1053700000</v>
       </c>
       <c r="J1989" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1990">
@@ -65767,32 +65767,1910 @@
     <row r="1991">
       <c r="A1991" t="inlineStr">
         <is>
+          <t>EUR 165m</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr"/>
+      <c r="C1991" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1991" t="n">
+        <v>165</v>
+      </c>
+      <c r="F1991" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="G1991" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="H1991" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="I1991" t="n">
+        <v>199144000</v>
+      </c>
+      <c r="J1991" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>EUR 165m</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr"/>
+      <c r="C1992" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D1992" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1992" t="n">
+        <v>165</v>
+      </c>
+      <c r="F1992" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="G1992" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="H1992" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="I1992" t="n">
+        <v>199144000</v>
+      </c>
+      <c r="J1992" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr"/>
+      <c r="B1993" t="inlineStr"/>
+      <c r="C1993" t="inlineStr"/>
+      <c r="D1993" t="inlineStr"/>
+      <c r="E1993" t="inlineStr"/>
+      <c r="F1993" t="inlineStr"/>
+      <c r="G1993" s="2" t="n">
+        <v>44652</v>
+      </c>
+      <c r="H1993" t="inlineStr"/>
+      <c r="I1993" t="inlineStr"/>
+      <c r="J1993" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr"/>
+      <c r="B1994" t="inlineStr"/>
+      <c r="C1994" t="inlineStr"/>
+      <c r="D1994" t="inlineStr"/>
+      <c r="E1994" t="inlineStr"/>
+      <c r="F1994" t="inlineStr"/>
+      <c r="G1994" s="2" t="n">
+        <v>44652</v>
+      </c>
+      <c r="H1994" t="inlineStr"/>
+      <c r="I1994" t="inlineStr"/>
+      <c r="J1994" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>€55 million</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr"/>
+      <c r="C1995" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D1995" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1995" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1995" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="G1995" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="H1995" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="I1995" t="n">
+        <v>64097000</v>
+      </c>
+      <c r="J1995" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>20 million euros</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr"/>
+      <c r="C1996" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D1996" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1996" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1996" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G1996" s="2" t="n">
+        <v>45017</v>
+      </c>
+      <c r="H1996" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I1996" t="n">
+        <v>21746666.66666666</v>
+      </c>
+      <c r="J1996" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>$20.35m</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>35m</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr"/>
+      <c r="D1997" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E1997" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1997" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1997" s="2" t="n">
+        <v>44743</v>
+      </c>
+      <c r="H1997" t="n">
+        <v>19.18465227817746</v>
+      </c>
+      <c r="I1997" t="n">
+        <v>20</v>
+      </c>
+      <c r="J1997" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>€50 million</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr"/>
+      <c r="C1998" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D1998" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1998" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1998" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G1998" s="2" t="n">
+        <v>44378</v>
+      </c>
+      <c r="H1998" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="I1998" t="n">
+        <v>59419999.99999999</v>
+      </c>
+      <c r="J1998" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>€1 billion</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr"/>
+      <c r="C1999" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1999" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1999" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1999" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G1999" s="2" t="n">
+        <v>44378</v>
+      </c>
+      <c r="H1999" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I1999" t="n">
+        <v>1188400000</v>
+      </c>
+      <c r="J1999" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>around two billion euros</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr"/>
+      <c r="C2000" t="inlineStr"/>
+      <c r="D2000" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2000" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F2000" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G2000" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H2000" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I2000" t="n">
+        <v>1081400000</v>
+      </c>
+      <c r="J2000" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>€2 billion</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr"/>
+      <c r="C2001" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2001" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2001" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2001" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="G2001" s="2" t="n">
+        <v>44805</v>
+      </c>
+      <c r="H2001" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="I2001" t="n">
+        <v>2000800000</v>
+      </c>
+      <c r="J2001" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>€2 billion</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr"/>
+      <c r="C2002" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2002" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2002" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2002" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="G2002" s="2" t="n">
+        <v>44805</v>
+      </c>
+      <c r="H2002" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="I2002" t="n">
+        <v>2000800000</v>
+      </c>
+      <c r="J2002" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
           <t>two billion euros</t>
         </is>
       </c>
-      <c r="B1991" t="inlineStr"/>
-      <c r="C1991" t="inlineStr"/>
-      <c r="D1991" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E1991" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="F1991" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="G1991" s="2" t="n">
-        <v>45231</v>
-      </c>
-      <c r="H1991" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="I1991" t="n">
-        <v>1053700000</v>
-      </c>
-      <c r="J1991" t="n">
+      <c r="B2003" t="inlineStr"/>
+      <c r="C2003" t="inlineStr"/>
+      <c r="D2003" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2003" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F2003" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G2003" s="2" t="n">
+        <v>45261</v>
+      </c>
+      <c r="H2003" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I2003" t="n">
+        <v>1087500000</v>
+      </c>
+      <c r="J2003" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>two billion euros</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr"/>
+      <c r="C2004" t="inlineStr"/>
+      <c r="D2004" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2004" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F2004" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G2004" s="2" t="n">
+        <v>45108</v>
+      </c>
+      <c r="H2004" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I2004" t="n">
+        <v>1087700000</v>
+      </c>
+      <c r="J2004" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>€74 million</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr"/>
+      <c r="C2005" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2005" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2005" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2005" t="n">
+        <v>74000000</v>
+      </c>
+      <c r="G2005" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="H2005" t="n">
+        <v>74000000</v>
+      </c>
+      <c r="I2005" t="n">
+        <v>79513000</v>
+      </c>
+      <c r="J2005" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>SEK 6.2 billion</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr"/>
+      <c r="C2006" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2006" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="E2006" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F2006" t="n">
+        <v>6200000000</v>
+      </c>
+      <c r="G2006" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H2006" t="n">
+        <v>532394487.1409557</v>
+      </c>
+      <c r="I2006" t="n">
+        <v>569502382.8946804</v>
+      </c>
+      <c r="J2006" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>SEK 400 million</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr"/>
+      <c r="C2007" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2007" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="E2007" t="n">
+        <v>400</v>
+      </c>
+      <c r="F2007" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="G2007" s="2" t="n">
+        <v>45536</v>
+      </c>
+      <c r="H2007" t="n">
+        <v>35255233.19867793</v>
+      </c>
+      <c r="I2007" t="n">
+        <v>39026367.97649651</v>
+      </c>
+      <c r="J2007" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr"/>
+      <c r="B2008" t="inlineStr"/>
+      <c r="C2008" t="inlineStr"/>
+      <c r="D2008" t="inlineStr"/>
+      <c r="E2008" t="inlineStr"/>
+      <c r="F2008" t="inlineStr"/>
+      <c r="G2008" s="2" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H2008" t="inlineStr"/>
+      <c r="I2008" t="inlineStr"/>
+      <c r="J2008" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>€4.2 billion</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr"/>
+      <c r="C2009" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2009" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F2009" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="G2009" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2009" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="I2009" t="n">
+        <v>4611390000</v>
+      </c>
+      <c r="J2009" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>€4.2 billion</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr"/>
+      <c r="C2010" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2010" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2010" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F2010" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="G2010" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2010" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="I2010" t="n">
+        <v>4611390000</v>
+      </c>
+      <c r="J2010" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>€4.2 billion</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr"/>
+      <c r="C2011" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2011" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2011" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F2011" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="G2011" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2011" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="I2011" t="n">
+        <v>4611390000</v>
+      </c>
+      <c r="J2011" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>€300 million</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr"/>
+      <c r="C2012" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2012" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2012" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="G2012" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2012" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="I2012" t="n">
+        <v>329385000</v>
+      </c>
+      <c r="J2012" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>€300 million</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr"/>
+      <c r="C2013" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2013" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2013" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2013" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="G2013" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2013" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="I2013" t="n">
+        <v>329385000</v>
+      </c>
+      <c r="J2013" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>€300 million</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr"/>
+      <c r="C2014" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2014" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2014" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2014" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="G2014" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2014" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="I2014" t="n">
+        <v>329385000</v>
+      </c>
+      <c r="J2014" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>€250 million</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr"/>
+      <c r="C2015" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2015" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2015" t="n">
+        <v>250</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="G2015" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2015" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="I2015" t="n">
+        <v>274487500</v>
+      </c>
+      <c r="J2015" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>€250 million</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr"/>
+      <c r="C2016" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2016" t="n">
+        <v>250</v>
+      </c>
+      <c r="F2016" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="G2016" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2016" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="I2016" t="n">
+        <v>274487500</v>
+      </c>
+      <c r="J2016" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>€250 million</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr"/>
+      <c r="C2017" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2017" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2017" t="n">
+        <v>250</v>
+      </c>
+      <c r="F2017" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="G2017" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2017" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="I2017" t="n">
+        <v>274487500</v>
+      </c>
+      <c r="J2017" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>€265m ($284m)</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr"/>
+      <c r="C2018" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2018" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2018" t="n">
+        <v>265</v>
+      </c>
+      <c r="F2018" t="n">
+        <v>265000000</v>
+      </c>
+      <c r="G2018" s="2" t="n">
+        <v>45444</v>
+      </c>
+      <c r="H2018" t="n">
+        <v>265000000</v>
+      </c>
+      <c r="I2018" t="n">
+        <v>287489666.6666667</v>
+      </c>
+      <c r="J2018" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>$150m</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr"/>
+      <c r="C2019" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2019" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E2019" t="n">
+        <v>150</v>
+      </c>
+      <c r="F2019" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="G2019" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="H2019" t="n">
+        <v>139387068.5970227</v>
+      </c>
+      <c r="I2019" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="J2019" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>$150m</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr"/>
+      <c r="C2020" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2020" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E2020" t="n">
+        <v>150</v>
+      </c>
+      <c r="F2020" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="G2020" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="H2020" t="n">
+        <v>139387068.5970227</v>
+      </c>
+      <c r="I2020" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="J2020" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr"/>
+      <c r="B2021" t="inlineStr"/>
+      <c r="C2021" t="inlineStr"/>
+      <c r="D2021" t="inlineStr"/>
+      <c r="E2021" t="inlineStr"/>
+      <c r="F2021" t="inlineStr"/>
+      <c r="G2021" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="H2021" t="inlineStr"/>
+      <c r="I2021" t="inlineStr"/>
+      <c r="J2021" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr"/>
+      <c r="B2022" t="inlineStr"/>
+      <c r="C2022" t="inlineStr"/>
+      <c r="D2022" t="inlineStr"/>
+      <c r="E2022" t="inlineStr"/>
+      <c r="F2022" t="inlineStr"/>
+      <c r="G2022" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="H2022" t="inlineStr"/>
+      <c r="I2022" t="inlineStr"/>
+      <c r="J2022" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>€55 million</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr"/>
+      <c r="C2023" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2023" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2023" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2023" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="G2023" s="2" t="n">
+        <v>44958</v>
+      </c>
+      <c r="H2023" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="I2023" t="n">
+        <v>59916999.99999999</v>
+      </c>
+      <c r="J2023" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr"/>
+      <c r="C2024" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2024" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F2024" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G2024" s="2" t="n">
+        <v>44287</v>
+      </c>
+      <c r="H2024" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I2024" t="inlineStr">
+        <is>
+          <t>[1174600000.0, 1761900000.0000002]</t>
+        </is>
+      </c>
+      <c r="J2024" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr"/>
+      <c r="C2025" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2025" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F2025" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G2025" s="2" t="n">
+        <v>44287</v>
+      </c>
+      <c r="H2025" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I2025" t="inlineStr">
+        <is>
+          <t>[1174600000.0, 1761900000.0000002]</t>
+        </is>
+      </c>
+      <c r="J2025" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr"/>
+      <c r="C2026" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2026" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F2026" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G2026" s="2" t="n">
+        <v>44287</v>
+      </c>
+      <c r="H2026" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I2026" t="inlineStr">
+        <is>
+          <t>[1174600000.0, 1761900000.0000002]</t>
+        </is>
+      </c>
+      <c r="J2026" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr"/>
+      <c r="C2027" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2027" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F2027" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="G2027" s="2" t="n">
+        <v>44287</v>
+      </c>
+      <c r="H2027" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I2027" t="inlineStr">
+        <is>
+          <t>[1174600000.0, 1761900000.0000002]</t>
+        </is>
+      </c>
+      <c r="J2027" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>€2.5 billion</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr"/>
+      <c r="C2028" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2028" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2028" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2028" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="G2028" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="H2028" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="I2028" t="n">
+        <v>2742500000</v>
+      </c>
+      <c r="J2028" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>€2.5 billion</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr"/>
+      <c r="C2029" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2029" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2029" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2029" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="G2029" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="H2029" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="I2029" t="n">
+        <v>2742500000</v>
+      </c>
+      <c r="J2029" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>€2.5 billion</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr"/>
+      <c r="C2030" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2030" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2030" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2030" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="G2030" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="H2030" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="I2030" t="n">
+        <v>2742500000</v>
+      </c>
+      <c r="J2030" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>€2.5 billion</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr"/>
+      <c r="C2031" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2031" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2031" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2031" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="G2031" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="H2031" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="I2031" t="n">
+        <v>2742500000</v>
+      </c>
+      <c r="J2031" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>€1.3 billion</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr"/>
+      <c r="C2032" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2032" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2032" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F2032" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="G2032" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H2032" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="I2032" t="n">
+        <v>1405820000</v>
+      </c>
+      <c r="J2032" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>€1.3 billion</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr"/>
+      <c r="C2033" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2033" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2033" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F2033" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="G2033" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H2033" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="I2033" t="n">
+        <v>1405820000</v>
+      </c>
+      <c r="J2033" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>€1.3 billion</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr"/>
+      <c r="C2034" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2034" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2034" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F2034" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="G2034" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H2034" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="I2034" t="n">
+        <v>1405820000</v>
+      </c>
+      <c r="J2034" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>€1.3 billion</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr"/>
+      <c r="C2035" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2035" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2035" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F2035" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="G2035" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H2035" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="I2035" t="n">
+        <v>1405820000</v>
+      </c>
+      <c r="J2035" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>€1.3 billion</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr"/>
+      <c r="C2036" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2036" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2036" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F2036" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="G2036" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H2036" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="I2036" t="n">
+        <v>1405820000</v>
+      </c>
+      <c r="J2036" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>€1.3 billion</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr"/>
+      <c r="C2037" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2037" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2037" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F2037" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="G2037" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H2037" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="I2037" t="n">
+        <v>1405820000</v>
+      </c>
+      <c r="J2037" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>€1.3 billion</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr"/>
+      <c r="C2038" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2038" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2038" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F2038" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="G2038" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H2038" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="I2038" t="n">
+        <v>1405820000</v>
+      </c>
+      <c r="J2038" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>€1.3 billion</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr"/>
+      <c r="C2039" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2039" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2039" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F2039" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="G2039" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H2039" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="I2039" t="n">
+        <v>1405820000</v>
+      </c>
+      <c r="J2039" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>EUR € 50 million</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr"/>
+      <c r="C2040" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2040" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2040" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2040" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G2040" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H2040" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="I2040" t="n">
+        <v>60265000</v>
+      </c>
+      <c r="J2040" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>EUR € 50 million</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr"/>
+      <c r="C2041" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2041" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2041" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2041" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G2041" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H2041" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="I2041" t="n">
+        <v>60265000</v>
+      </c>
+      <c r="J2041" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>€8 million ($8.7m)</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr"/>
+      <c r="C2042" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2042" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2042" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2042" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="G2042" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2042" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I2042" t="n">
+        <v>8783600</v>
+      </c>
+      <c r="J2042" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>EUR 4.5 billion</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr"/>
+      <c r="C2043" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2043" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2043" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F2043" t="n">
+        <v>4500000000</v>
+      </c>
+      <c r="G2043" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="H2043" t="n">
+        <v>4500000000</v>
+      </c>
+      <c r="I2043" t="n">
+        <v>4842630000</v>
+      </c>
+      <c r="J2043" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>EUR 2.6 billion</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr"/>
+      <c r="C2044" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2044" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2044" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F2044" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="G2044" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2044" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="I2044" t="n">
+        <v>2854670000</v>
+      </c>
+      <c r="J2044" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>EUR 2.6 billion</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr"/>
+      <c r="C2045" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2045" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2045" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F2045" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="G2045" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2045" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="I2045" t="n">
+        <v>2854670000</v>
+      </c>
+      <c r="J2045" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>three million euros</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr"/>
+      <c r="C2046" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2046" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2046" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2046" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G2046" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="H2046" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I2046" t="n">
+        <v>3291000</v>
+      </c>
+      <c r="J2046" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>EUR 1.5 billion</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr"/>
+      <c r="C2047" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2047" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2047" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2047" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="G2047" s="2" t="n">
+        <v>44986</v>
+      </c>
+      <c r="H2047" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="I2047" t="n">
+        <v>1602600000</v>
+      </c>
+      <c r="J2047" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>EUR 1.5 billion</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr"/>
+      <c r="C2048" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2048" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2048" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2048" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="G2048" s="2" t="n">
+        <v>44986</v>
+      </c>
+      <c r="H2048" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="I2048" t="n">
+        <v>1602600000</v>
+      </c>
+      <c r="J2048" t="n">
         <v>2023</v>
       </c>
     </row>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2048"/>
+  <dimension ref="A1:J2062"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61963,59 +61963,67 @@
     <row r="1881">
       <c r="A1881" t="inlineStr">
         <is>
-          <t>double-digit million euro amount</t>
-        </is>
-      </c>
-      <c r="B1881" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C1881" t="inlineStr"/>
+          <t>EUR800m</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr"/>
+      <c r="C1881" t="n">
+        <v>1000000</v>
+      </c>
       <c r="D1881" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1881" t="inlineStr">
-        <is>
-          <t>[10000000.0, 99000000.0]</t>
-        </is>
-      </c>
-      <c r="F1881" t="inlineStr">
-        <is>
-          <t>[10000000.0, 99000000.0]</t>
-        </is>
+      <c r="E1881" t="n">
+        <v>800</v>
+      </c>
+      <c r="F1881" t="n">
+        <v>800000000</v>
       </c>
       <c r="G1881" s="2" t="n">
-        <v>44986</v>
-      </c>
-      <c r="H1881" t="inlineStr">
-        <is>
-          <t>[10000000.0, 99000000.0]</t>
-        </is>
-      </c>
-      <c r="I1881" t="inlineStr">
-        <is>
-          <t>[10684000.0, 105771600.0]</t>
-        </is>
+        <v>45017</v>
+      </c>
+      <c r="H1881" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="I1881" t="n">
+        <v>869866666.6666666</v>
       </c>
       <c r="J1881" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="1882">
-      <c r="A1882" t="inlineStr"/>
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>EUR800m</t>
+        </is>
+      </c>
       <c r="B1882" t="inlineStr"/>
-      <c r="C1882" t="inlineStr"/>
-      <c r="D1882" t="inlineStr"/>
-      <c r="E1882" t="inlineStr"/>
-      <c r="F1882" t="inlineStr"/>
+      <c r="C1882" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1882" t="n">
+        <v>800</v>
+      </c>
+      <c r="F1882" t="n">
+        <v>800000000</v>
+      </c>
       <c r="G1882" s="2" t="n">
-        <v>44986</v>
-      </c>
-      <c r="H1882" t="inlineStr"/>
-      <c r="I1882" t="inlineStr"/>
+        <v>45017</v>
+      </c>
+      <c r="H1882" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="I1882" t="n">
+        <v>869866666.6666666</v>
+      </c>
       <c r="J1882" t="n">
         <v>2023</v>
       </c>
@@ -62023,71 +62031,59 @@
     <row r="1883">
       <c r="A1883" t="inlineStr">
         <is>
-          <t>$13.4bn</t>
+          <t>double-digit million euro amount</t>
         </is>
       </c>
       <c r="B1883" t="inlineStr">
         <is>
-          <t>4bn</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C1883" t="inlineStr"/>
       <c r="D1883" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E1883" t="n">
-        <v>13</v>
-      </c>
-      <c r="F1883" t="n">
-        <v>13</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1883" t="inlineStr">
+        <is>
+          <t>[10000000.0, 99000000.0]</t>
+        </is>
+      </c>
+      <c r="F1883" t="inlineStr">
+        <is>
+          <t>[10000000.0, 99000000.0]</t>
+        </is>
       </c>
       <c r="G1883" s="2" t="n">
-        <v>44927</v>
-      </c>
-      <c r="H1883" t="n">
-        <v>12.17532467532468</v>
-      </c>
-      <c r="I1883" t="n">
-        <v>13</v>
+        <v>44986</v>
+      </c>
+      <c r="H1883" t="inlineStr">
+        <is>
+          <t>[10000000.0, 99000000.0]</t>
+        </is>
+      </c>
+      <c r="I1883" t="inlineStr">
+        <is>
+          <t>[10684000.0, 105771600.0]</t>
+        </is>
       </c>
       <c r="J1883" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="1884">
-      <c r="A1884" t="inlineStr">
-        <is>
-          <t>€6.8bn</t>
-        </is>
-      </c>
-      <c r="B1884" t="inlineStr">
-        <is>
-          <t>8bn</t>
-        </is>
-      </c>
+      <c r="A1884" t="inlineStr"/>
+      <c r="B1884" t="inlineStr"/>
       <c r="C1884" t="inlineStr"/>
-      <c r="D1884" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E1884" t="n">
-        <v>6</v>
-      </c>
-      <c r="F1884" t="n">
-        <v>6</v>
-      </c>
+      <c r="D1884" t="inlineStr"/>
+      <c r="E1884" t="inlineStr"/>
+      <c r="F1884" t="inlineStr"/>
       <c r="G1884" s="2" t="n">
-        <v>44927</v>
-      </c>
-      <c r="H1884" t="n">
-        <v>6</v>
-      </c>
-      <c r="I1884" t="n">
-        <v>6.4064</v>
-      </c>
+        <v>44986</v>
+      </c>
+      <c r="H1884" t="inlineStr"/>
+      <c r="I1884" t="inlineStr"/>
       <c r="J1884" t="n">
         <v>2023</v>
       </c>
@@ -62095,32 +62091,34 @@
     <row r="1885">
       <c r="A1885" t="inlineStr">
         <is>
-          <t>GBP300m</t>
-        </is>
-      </c>
-      <c r="B1885" t="inlineStr"/>
-      <c r="C1885" t="n">
-        <v>1000000</v>
-      </c>
+          <t>$13.4bn</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>4bn</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr"/>
       <c r="D1885" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E1885" t="n">
-        <v>300</v>
+        <v>13</v>
       </c>
       <c r="F1885" t="n">
-        <v>300000000</v>
+        <v>13</v>
       </c>
       <c r="G1885" s="2" t="n">
-        <v>44986</v>
+        <v>44927</v>
       </c>
       <c r="H1885" t="n">
-        <v>338699844.1980717</v>
+        <v>12.17532467532468</v>
       </c>
       <c r="I1885" t="n">
-        <v>361866913.5412198</v>
+        <v>13</v>
       </c>
       <c r="J1885" t="n">
         <v>2023</v>
@@ -62129,32 +62127,34 @@
     <row r="1886">
       <c r="A1886" t="inlineStr">
         <is>
-          <t>EUR650 million</t>
-        </is>
-      </c>
-      <c r="B1886" t="inlineStr"/>
-      <c r="C1886" t="n">
-        <v>1000000</v>
-      </c>
+          <t>€6.8bn</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>8bn</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr"/>
       <c r="D1886" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
       <c r="E1886" t="n">
-        <v>650</v>
+        <v>6</v>
       </c>
       <c r="F1886" t="n">
-        <v>650000000</v>
+        <v>6</v>
       </c>
       <c r="G1886" s="2" t="n">
-        <v>45047</v>
+        <v>44927</v>
       </c>
       <c r="H1886" t="n">
-        <v>650000000</v>
+        <v>6</v>
       </c>
       <c r="I1886" t="n">
-        <v>712985000.0000001</v>
+        <v>6.4064</v>
       </c>
       <c r="J1886" t="n">
         <v>2023</v>
@@ -62163,7 +62163,7 @@
     <row r="1887">
       <c r="A1887" t="inlineStr">
         <is>
-          <t>EUR650 million</t>
+          <t>GBP300m</t>
         </is>
       </c>
       <c r="B1887" t="inlineStr"/>
@@ -62172,23 +62172,23 @@
       </c>
       <c r="D1887" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1887" t="n">
-        <v>650</v>
+        <v>300</v>
       </c>
       <c r="F1887" t="n">
-        <v>650000000</v>
+        <v>300000000</v>
       </c>
       <c r="G1887" s="2" t="n">
-        <v>45047</v>
+        <v>44986</v>
       </c>
       <c r="H1887" t="n">
-        <v>650000000</v>
+        <v>338699844.1980717</v>
       </c>
       <c r="I1887" t="n">
-        <v>712985000.0000001</v>
+        <v>361866913.5412198</v>
       </c>
       <c r="J1887" t="n">
         <v>2023</v>
@@ -62197,32 +62197,32 @@
     <row r="1888">
       <c r="A1888" t="inlineStr">
         <is>
-          <t>GBP15bn</t>
+          <t>EUR650 million</t>
         </is>
       </c>
       <c r="B1888" t="inlineStr"/>
       <c r="C1888" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1888" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1888" t="n">
-        <v>15</v>
+        <v>650</v>
       </c>
       <c r="F1888" t="n">
-        <v>15000000000</v>
+        <v>650000000</v>
       </c>
       <c r="G1888" s="2" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="H1888" t="n">
-        <v>17069377536.69916</v>
+        <v>650000000</v>
       </c>
       <c r="I1888" t="n">
-        <v>18560103174.90422</v>
+        <v>712985000.0000001</v>
       </c>
       <c r="J1888" t="n">
         <v>2023</v>
@@ -62231,32 +62231,32 @@
     <row r="1889">
       <c r="A1889" t="inlineStr">
         <is>
-          <t>GBP15bn</t>
+          <t>EUR650 million</t>
         </is>
       </c>
       <c r="B1889" t="inlineStr"/>
       <c r="C1889" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1889" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1889" t="n">
-        <v>15</v>
+        <v>650</v>
       </c>
       <c r="F1889" t="n">
-        <v>15000000000</v>
+        <v>650000000</v>
       </c>
       <c r="G1889" s="2" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="H1889" t="n">
-        <v>17069377536.69916</v>
+        <v>650000000</v>
       </c>
       <c r="I1889" t="n">
-        <v>18560103174.90422</v>
+        <v>712985000.0000001</v>
       </c>
       <c r="J1889" t="n">
         <v>2023</v>
@@ -62401,32 +62401,32 @@
     <row r="1894">
       <c r="A1894" t="inlineStr">
         <is>
-          <t>EUR130m</t>
+          <t>GBP15bn</t>
         </is>
       </c>
       <c r="B1894" t="inlineStr"/>
       <c r="C1894" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1894" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1894" t="n">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="F1894" t="n">
-        <v>130000000</v>
+        <v>15000000000</v>
       </c>
       <c r="G1894" s="2" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="H1894" t="n">
-        <v>130000000</v>
+        <v>17069377536.69916</v>
       </c>
       <c r="I1894" t="n">
-        <v>138892000</v>
+        <v>18560103174.90422</v>
       </c>
       <c r="J1894" t="n">
         <v>2023</v>
@@ -62435,32 +62435,32 @@
     <row r="1895">
       <c r="A1895" t="inlineStr">
         <is>
-          <t>EUR750m</t>
+          <t>GBP15bn</t>
         </is>
       </c>
       <c r="B1895" t="inlineStr"/>
       <c r="C1895" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1895" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1895" t="n">
-        <v>750</v>
+        <v>15</v>
       </c>
       <c r="F1895" t="n">
-        <v>750000000</v>
+        <v>15000000000</v>
       </c>
       <c r="G1895" s="2" t="n">
-        <v>44958</v>
+        <v>45017</v>
       </c>
       <c r="H1895" t="n">
-        <v>750000000</v>
+        <v>17069377536.69916</v>
       </c>
       <c r="I1895" t="n">
-        <v>817050000</v>
+        <v>18560103174.90422</v>
       </c>
       <c r="J1895" t="n">
         <v>2023</v>
@@ -62469,7 +62469,7 @@
     <row r="1896">
       <c r="A1896" t="inlineStr">
         <is>
-          <t>€40m</t>
+          <t>EUR130m</t>
         </is>
       </c>
       <c r="B1896" t="inlineStr"/>
@@ -62482,19 +62482,19 @@
         </is>
       </c>
       <c r="E1896" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="F1896" t="n">
-        <v>40000000</v>
+        <v>130000000</v>
       </c>
       <c r="G1896" s="2" t="n">
-        <v>45017</v>
+        <v>44986</v>
       </c>
       <c r="H1896" t="n">
-        <v>40000000</v>
+        <v>130000000</v>
       </c>
       <c r="I1896" t="n">
-        <v>43493333.33333333</v>
+        <v>138892000</v>
       </c>
       <c r="J1896" t="n">
         <v>2023</v>
@@ -62503,7 +62503,7 @@
     <row r="1897">
       <c r="A1897" t="inlineStr">
         <is>
-          <t>EUR800m</t>
+          <t>EUR750m</t>
         </is>
       </c>
       <c r="B1897" t="inlineStr"/>
@@ -62516,19 +62516,19 @@
         </is>
       </c>
       <c r="E1897" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="F1897" t="n">
-        <v>800000000</v>
+        <v>750000000</v>
       </c>
       <c r="G1897" s="2" t="n">
-        <v>44986</v>
+        <v>44958</v>
       </c>
       <c r="H1897" t="n">
-        <v>800000000</v>
+        <v>750000000</v>
       </c>
       <c r="I1897" t="n">
-        <v>854720000</v>
+        <v>817050000</v>
       </c>
       <c r="J1897" t="n">
         <v>2023</v>
@@ -62537,7 +62537,7 @@
     <row r="1898">
       <c r="A1898" t="inlineStr">
         <is>
-          <t>EUR800m</t>
+          <t>€40m</t>
         </is>
       </c>
       <c r="B1898" t="inlineStr"/>
@@ -62550,19 +62550,19 @@
         </is>
       </c>
       <c r="E1898" t="n">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F1898" t="n">
-        <v>800000000</v>
+        <v>40000000</v>
       </c>
       <c r="G1898" s="2" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="H1898" t="n">
-        <v>800000000</v>
+        <v>40000000</v>
       </c>
       <c r="I1898" t="n">
-        <v>854720000</v>
+        <v>43493333.33333333</v>
       </c>
       <c r="J1898" t="n">
         <v>2023</v>
@@ -62571,34 +62571,32 @@
     <row r="1899">
       <c r="A1899" t="inlineStr">
         <is>
-          <t>£3.8bn</t>
-        </is>
-      </c>
-      <c r="B1899" t="inlineStr">
-        <is>
-          <t>8bn</t>
-        </is>
-      </c>
-      <c r="C1899" t="inlineStr"/>
+          <t>EUR800m</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr"/>
+      <c r="C1899" t="n">
+        <v>1000000</v>
+      </c>
       <c r="D1899" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1899" t="n">
-        <v>3</v>
+        <v>800</v>
       </c>
       <c r="F1899" t="n">
-        <v>3</v>
+        <v>800000000</v>
       </c>
       <c r="G1899" s="2" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="H1899" t="n">
-        <v>3.393166163347019</v>
+        <v>800000000</v>
       </c>
       <c r="I1899" t="n">
-        <v>3.696515218350243</v>
+        <v>854720000</v>
       </c>
       <c r="J1899" t="n">
         <v>2023</v>
@@ -62607,34 +62605,32 @@
     <row r="1900">
       <c r="A1900" t="inlineStr">
         <is>
-          <t>EUR1.4bn</t>
-        </is>
-      </c>
-      <c r="B1900" t="inlineStr">
-        <is>
-          <t>4bn</t>
-        </is>
-      </c>
-      <c r="C1900" t="inlineStr"/>
+          <t>EUR800m</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr"/>
+      <c r="C1900" t="n">
+        <v>1000000</v>
+      </c>
       <c r="D1900" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
       <c r="E1900" t="n">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="F1900" t="n">
-        <v>1</v>
+        <v>800000000</v>
       </c>
       <c r="G1900" s="2" t="n">
-        <v>45017</v>
+        <v>44986</v>
       </c>
       <c r="H1900" t="n">
-        <v>1</v>
+        <v>800000000</v>
       </c>
       <c r="I1900" t="n">
-        <v>1.087333333333333</v>
+        <v>854720000</v>
       </c>
       <c r="J1900" t="n">
         <v>2023</v>
@@ -62643,7 +62639,7 @@
     <row r="1901">
       <c r="A1901" t="inlineStr">
         <is>
-          <t>GBP3.8bn</t>
+          <t>£3.8bn</t>
         </is>
       </c>
       <c r="B1901" t="inlineStr">
@@ -62679,34 +62675,34 @@
     <row r="1902">
       <c r="A1902" t="inlineStr">
         <is>
-          <t>$7.5bn</t>
+          <t>EUR1.4bn</t>
         </is>
       </c>
       <c r="B1902" t="inlineStr">
         <is>
-          <t>5bn</t>
+          <t>4bn</t>
         </is>
       </c>
       <c r="C1902" t="inlineStr"/>
       <c r="D1902" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1902" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F1902" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1902" s="2" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="H1902" t="n">
-        <v>6.551853238487458</v>
+        <v>1</v>
       </c>
       <c r="I1902" t="n">
-        <v>7</v>
+        <v>1.087333333333333</v>
       </c>
       <c r="J1902" t="n">
         <v>2023</v>
@@ -62715,32 +62711,34 @@
     <row r="1903">
       <c r="A1903" t="inlineStr">
         <is>
-          <t>KRW100bn (US$75m)</t>
-        </is>
-      </c>
-      <c r="B1903" t="inlineStr"/>
-      <c r="C1903" t="n">
-        <v>1000000000</v>
-      </c>
+          <t>GBP3.8bn</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>8bn</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr"/>
       <c r="D1903" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1903" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="F1903" t="n">
-        <v>100000000000</v>
+        <v>3</v>
       </c>
       <c r="G1903" s="2" t="n">
-        <v>45047</v>
+        <v>44958</v>
       </c>
       <c r="H1903" t="n">
-        <v>68005814.4971395</v>
+        <v>3.393166163347019</v>
       </c>
       <c r="I1903" t="n">
-        <v>74595577.92191233</v>
+        <v>3.696515218350243</v>
       </c>
       <c r="J1903" t="n">
         <v>2023</v>
@@ -62749,32 +62747,34 @@
     <row r="1904">
       <c r="A1904" t="inlineStr">
         <is>
-          <t>US$285m</t>
-        </is>
-      </c>
-      <c r="B1904" t="inlineStr"/>
-      <c r="C1904" t="n">
-        <v>1000000</v>
-      </c>
+          <t>$7.5bn</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>5bn</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr"/>
       <c r="D1904" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="E1904" t="n">
-        <v>285</v>
+        <v>7</v>
       </c>
       <c r="F1904" t="n">
-        <v>285000000</v>
+        <v>7</v>
       </c>
       <c r="G1904" s="2" t="n">
-        <v>45017</v>
+        <v>44986</v>
       </c>
       <c r="H1904" t="n">
-        <v>262109135.4996935</v>
+        <v>6.551853238487458</v>
       </c>
       <c r="I1904" t="n">
-        <v>285000000</v>
+        <v>7</v>
       </c>
       <c r="J1904" t="n">
         <v>2023</v>
@@ -62783,32 +62783,32 @@
     <row r="1905">
       <c r="A1905" t="inlineStr">
         <is>
-          <t>€460 million</t>
+          <t>KRW100bn (US$75m)</t>
         </is>
       </c>
       <c r="B1905" t="inlineStr"/>
       <c r="C1905" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1905" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="E1905" t="n">
-        <v>460</v>
+        <v>100</v>
       </c>
       <c r="F1905" t="n">
-        <v>460000000</v>
+        <v>100000000000</v>
       </c>
       <c r="G1905" s="2" t="n">
-        <v>44958</v>
+        <v>45047</v>
       </c>
       <c r="H1905" t="n">
-        <v>460000000</v>
+        <v>68005814.4971395</v>
       </c>
       <c r="I1905" t="n">
-        <v>501123999.9999999</v>
+        <v>74595577.92191233</v>
       </c>
       <c r="J1905" t="n">
         <v>2023</v>
@@ -62817,7 +62817,7 @@
     <row r="1906">
       <c r="A1906" t="inlineStr">
         <is>
-          <t>€460 million</t>
+          <t>US$285m</t>
         </is>
       </c>
       <c r="B1906" t="inlineStr"/>
@@ -62826,23 +62826,23 @@
       </c>
       <c r="D1906" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E1906" t="n">
-        <v>460</v>
+        <v>285</v>
       </c>
       <c r="F1906" t="n">
-        <v>460000000</v>
+        <v>285000000</v>
       </c>
       <c r="G1906" s="2" t="n">
-        <v>44958</v>
+        <v>45017</v>
       </c>
       <c r="H1906" t="n">
-        <v>460000000</v>
+        <v>262109135.4996935</v>
       </c>
       <c r="I1906" t="n">
-        <v>501123999.9999999</v>
+        <v>285000000</v>
       </c>
       <c r="J1906" t="n">
         <v>2023</v>
@@ -62851,7 +62851,7 @@
     <row r="1907">
       <c r="A1907" t="inlineStr">
         <is>
-          <t>GBP75m</t>
+          <t>€460 million</t>
         </is>
       </c>
       <c r="B1907" t="inlineStr"/>
@@ -62860,23 +62860,23 @@
       </c>
       <c r="D1907" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1907" t="n">
-        <v>75</v>
+        <v>460</v>
       </c>
       <c r="F1907" t="n">
-        <v>75000000</v>
+        <v>460000000</v>
       </c>
       <c r="G1907" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="H1907" t="n">
-        <v>84829154.08367547</v>
+        <v>460000000</v>
       </c>
       <c r="I1907" t="n">
-        <v>92412880.45875606</v>
+        <v>501123999.9999999</v>
       </c>
       <c r="J1907" t="n">
         <v>2023</v>
@@ -62885,7 +62885,7 @@
     <row r="1908">
       <c r="A1908" t="inlineStr">
         <is>
-          <t>GBP35m</t>
+          <t>€460 million</t>
         </is>
       </c>
       <c r="B1908" t="inlineStr"/>
@@ -62894,23 +62894,23 @@
       </c>
       <c r="D1908" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1908" t="n">
-        <v>35</v>
+        <v>460</v>
       </c>
       <c r="F1908" t="n">
-        <v>35000000</v>
+        <v>460000000</v>
       </c>
       <c r="G1908" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="H1908" t="n">
-        <v>39586938.57238189</v>
+        <v>460000000</v>
       </c>
       <c r="I1908" t="n">
-        <v>43126010.88075283</v>
+        <v>501123999.9999999</v>
       </c>
       <c r="J1908" t="n">
         <v>2023</v>
@@ -62919,7 +62919,7 @@
     <row r="1909">
       <c r="A1909" t="inlineStr">
         <is>
-          <t>GBP35m</t>
+          <t>GBP75m</t>
         </is>
       </c>
       <c r="B1909" t="inlineStr"/>
@@ -62932,19 +62932,19 @@
         </is>
       </c>
       <c r="E1909" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F1909" t="n">
-        <v>35000000</v>
+        <v>75000000</v>
       </c>
       <c r="G1909" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="H1909" t="n">
-        <v>39586938.57238189</v>
+        <v>84829154.08367547</v>
       </c>
       <c r="I1909" t="n">
-        <v>43126010.88075283</v>
+        <v>92412880.45875606</v>
       </c>
       <c r="J1909" t="n">
         <v>2023</v>
@@ -62985,17 +62985,35 @@
       </c>
     </row>
     <row r="1911">
-      <c r="A1911" t="inlineStr"/>
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>GBP35m</t>
+        </is>
+      </c>
       <c r="B1911" t="inlineStr"/>
-      <c r="C1911" t="inlineStr"/>
-      <c r="D1911" t="inlineStr"/>
-      <c r="E1911" t="inlineStr"/>
-      <c r="F1911" t="inlineStr"/>
+      <c r="C1911" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E1911" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1911" t="n">
+        <v>35000000</v>
+      </c>
       <c r="G1911" s="2" t="n">
-        <v>45047</v>
-      </c>
-      <c r="H1911" t="inlineStr"/>
-      <c r="I1911" t="inlineStr"/>
+        <v>44958</v>
+      </c>
+      <c r="H1911" t="n">
+        <v>39586938.57238189</v>
+      </c>
+      <c r="I1911" t="n">
+        <v>43126010.88075283</v>
+      </c>
       <c r="J1911" t="n">
         <v>2023</v>
       </c>
@@ -63003,69 +63021,49 @@
     <row r="1912">
       <c r="A1912" t="inlineStr">
         <is>
-          <t>£3.8bn</t>
-        </is>
-      </c>
-      <c r="B1912" t="inlineStr">
-        <is>
-          <t>8bn</t>
-        </is>
-      </c>
-      <c r="C1912" t="inlineStr"/>
+          <t>GBP35m</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr"/>
+      <c r="C1912" t="n">
+        <v>1000000</v>
+      </c>
       <c r="D1912" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
       <c r="E1912" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F1912" t="n">
-        <v>3</v>
+        <v>35000000</v>
       </c>
       <c r="G1912" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="H1912" t="n">
-        <v>3.393166163347019</v>
+        <v>39586938.57238189</v>
       </c>
       <c r="I1912" t="n">
-        <v>3.696515218350243</v>
+        <v>43126010.88075283</v>
       </c>
       <c r="J1912" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="1913">
-      <c r="A1913" t="inlineStr">
-        <is>
-          <t>GBP600m</t>
-        </is>
-      </c>
+      <c r="A1913" t="inlineStr"/>
       <c r="B1913" t="inlineStr"/>
-      <c r="C1913" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D1913" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="E1913" t="n">
-        <v>600</v>
-      </c>
-      <c r="F1913" t="n">
-        <v>600000000</v>
-      </c>
+      <c r="C1913" t="inlineStr"/>
+      <c r="D1913" t="inlineStr"/>
+      <c r="E1913" t="inlineStr"/>
+      <c r="F1913" t="inlineStr"/>
       <c r="G1913" s="2" t="n">
-        <v>44986</v>
-      </c>
-      <c r="H1913" t="n">
-        <v>677399688.3961433</v>
-      </c>
-      <c r="I1913" t="n">
-        <v>723733827.0824395</v>
-      </c>
+        <v>45047</v>
+      </c>
+      <c r="H1913" t="inlineStr"/>
+      <c r="I1913" t="inlineStr"/>
       <c r="J1913" t="n">
         <v>2023</v>
       </c>
@@ -63073,39 +63071,43 @@
     <row r="1914">
       <c r="A1914" t="inlineStr">
         <is>
-          <t>€541,000 (approx. £465,000)</t>
-        </is>
-      </c>
-      <c r="B1914" t="inlineStr"/>
+          <t>£3.8bn</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>8bn</t>
+        </is>
+      </c>
       <c r="C1914" t="inlineStr"/>
       <c r="D1914" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1914" t="n">
-        <v>541000</v>
+        <v>3</v>
       </c>
       <c r="F1914" t="n">
-        <v>541000</v>
+        <v>3</v>
       </c>
       <c r="G1914" s="2" t="n">
-        <v>44896</v>
+        <v>44958</v>
       </c>
       <c r="H1914" t="n">
-        <v>541000</v>
+        <v>3.393166163347019</v>
       </c>
       <c r="I1914" t="n">
-        <v>565561.4</v>
+        <v>3.696515218350243</v>
       </c>
       <c r="J1914" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1915">
       <c r="A1915" t="inlineStr">
         <is>
-          <t>GBP380m</t>
+          <t>GBP600m</t>
         </is>
       </c>
       <c r="B1915" t="inlineStr"/>
@@ -63118,53 +63120,51 @@
         </is>
       </c>
       <c r="E1915" t="n">
-        <v>380</v>
+        <v>600</v>
       </c>
       <c r="F1915" t="n">
-        <v>380000000</v>
+        <v>600000000</v>
       </c>
       <c r="G1915" s="2" t="n">
-        <v>44896</v>
+        <v>44986</v>
       </c>
       <c r="H1915" t="n">
-        <v>443329638.9196757</v>
+        <v>677399688.3961433</v>
       </c>
       <c r="I1915" t="n">
-        <v>463456804.526629</v>
+        <v>723733827.0824395</v>
       </c>
       <c r="J1915" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1916">
       <c r="A1916" t="inlineStr">
         <is>
-          <t>GBP24m</t>
+          <t>€541,000 (approx. £465,000)</t>
         </is>
       </c>
       <c r="B1916" t="inlineStr"/>
-      <c r="C1916" t="n">
-        <v>1000000</v>
-      </c>
+      <c r="C1916" t="inlineStr"/>
       <c r="D1916" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1916" t="n">
-        <v>24</v>
+        <v>541000</v>
       </c>
       <c r="F1916" t="n">
-        <v>24000000</v>
+        <v>541000</v>
       </c>
       <c r="G1916" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="H1916" t="n">
-        <v>27999766.66861109</v>
+        <v>541000</v>
       </c>
       <c r="I1916" t="n">
-        <v>29270956.07536604</v>
+        <v>565561.4</v>
       </c>
       <c r="J1916" t="n">
         <v>2022</v>
@@ -63173,7 +63173,7 @@
     <row r="1917">
       <c r="A1917" t="inlineStr">
         <is>
-          <t>€100m ($97m)</t>
+          <t>GBP380m</t>
         </is>
       </c>
       <c r="B1917" t="inlineStr"/>
@@ -63182,23 +63182,23 @@
       </c>
       <c r="D1917" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1917" t="n">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="F1917" t="n">
-        <v>100000000</v>
+        <v>380000000</v>
       </c>
       <c r="G1917" s="2" t="n">
-        <v>44835</v>
+        <v>44896</v>
       </c>
       <c r="H1917" t="n">
-        <v>100000000</v>
+        <v>443329638.9196757</v>
       </c>
       <c r="I1917" t="n">
-        <v>97533333.33333334</v>
+        <v>463456804.526629</v>
       </c>
       <c r="J1917" t="n">
         <v>2022</v>
@@ -63207,7 +63207,7 @@
     <row r="1918">
       <c r="A1918" t="inlineStr">
         <is>
-          <t>EUR650m</t>
+          <t>GBP24m</t>
         </is>
       </c>
       <c r="B1918" t="inlineStr"/>
@@ -63216,23 +63216,23 @@
       </c>
       <c r="D1918" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1918" t="n">
-        <v>650</v>
+        <v>24</v>
       </c>
       <c r="F1918" t="n">
-        <v>650000000</v>
+        <v>24000000</v>
       </c>
       <c r="G1918" s="2" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="H1918" t="n">
-        <v>650000000</v>
+        <v>27999766.66861109</v>
       </c>
       <c r="I1918" t="n">
-        <v>646555000</v>
+        <v>29270956.07536604</v>
       </c>
       <c r="J1918" t="n">
         <v>2022</v>
@@ -63241,7 +63241,7 @@
     <row r="1919">
       <c r="A1919" t="inlineStr">
         <is>
-          <t>GBP230m</t>
+          <t>€100m ($97m)</t>
         </is>
       </c>
       <c r="B1919" t="inlineStr"/>
@@ -63250,37 +63250,37 @@
       </c>
       <c r="D1919" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1919" t="n">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="F1919" t="n">
-        <v>230000000</v>
+        <v>100000000</v>
       </c>
       <c r="G1919" s="2" t="n">
-        <v>45901</v>
+        <v>44835</v>
       </c>
       <c r="H1919" t="n">
-        <v>265007489.3420901</v>
+        <v>100000000</v>
       </c>
       <c r="I1919" t="n">
-        <v>308839728.0792718</v>
+        <v>97533333.33333334</v>
       </c>
       <c r="J1919" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1920">
       <c r="A1920" t="inlineStr">
         <is>
-          <t>€17bn</t>
+          <t>EUR650m</t>
         </is>
       </c>
       <c r="B1920" t="inlineStr"/>
       <c r="C1920" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1920" t="inlineStr">
         <is>
@@ -63288,19 +63288,19 @@
         </is>
       </c>
       <c r="E1920" t="n">
-        <v>17</v>
+        <v>650</v>
       </c>
       <c r="F1920" t="n">
-        <v>17000000000</v>
+        <v>650000000</v>
       </c>
       <c r="G1920" s="2" t="n">
-        <v>44805</v>
+        <v>44866</v>
       </c>
       <c r="H1920" t="n">
-        <v>17000000000</v>
+        <v>650000000</v>
       </c>
       <c r="I1920" t="n">
-        <v>17006800000</v>
+        <v>646555000</v>
       </c>
       <c r="J1920" t="n">
         <v>2022</v>
@@ -63309,41 +63309,41 @@
     <row r="1921">
       <c r="A1921" t="inlineStr">
         <is>
-          <t>$1bn</t>
+          <t>GBP230m</t>
         </is>
       </c>
       <c r="B1921" t="inlineStr"/>
       <c r="C1921" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1921" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1921" t="n">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="F1921" t="n">
-        <v>1000000000</v>
+        <v>230000000</v>
       </c>
       <c r="G1921" s="2" t="n">
-        <v>44805</v>
+        <v>45901</v>
       </c>
       <c r="H1921" t="n">
-        <v>999600159.9360256</v>
+        <v>265007489.3420901</v>
       </c>
       <c r="I1921" t="n">
-        <v>1000000000</v>
+        <v>308839728.0792718</v>
       </c>
       <c r="J1921" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1922">
       <c r="A1922" t="inlineStr">
         <is>
-          <t>$1bn</t>
+          <t>€17bn</t>
         </is>
       </c>
       <c r="B1922" t="inlineStr"/>
@@ -63352,23 +63352,23 @@
       </c>
       <c r="D1922" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1922" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F1922" t="n">
-        <v>1000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="G1922" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="H1922" t="n">
-        <v>999600159.9360256</v>
+        <v>17000000000</v>
       </c>
       <c r="I1922" t="n">
-        <v>1000000000</v>
+        <v>17006800000</v>
       </c>
       <c r="J1922" t="n">
         <v>2022</v>
@@ -63377,32 +63377,32 @@
     <row r="1923">
       <c r="A1923" t="inlineStr">
         <is>
-          <t>EUR75m</t>
+          <t>$1bn</t>
         </is>
       </c>
       <c r="B1923" t="inlineStr"/>
       <c r="C1923" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1923" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E1923" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="F1923" t="n">
-        <v>75000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G1923" s="2" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="H1923" t="n">
-        <v>75000000</v>
+        <v>999600159.9360256</v>
       </c>
       <c r="I1923" t="n">
-        <v>73150000</v>
+        <v>1000000000</v>
       </c>
       <c r="J1923" t="n">
         <v>2022</v>
@@ -63411,38 +63411,32 @@
     <row r="1924">
       <c r="A1924" t="inlineStr">
         <is>
-          <t>triple-digit million euros</t>
+          <t>$1bn</t>
         </is>
       </c>
       <c r="B1924" t="inlineStr"/>
-      <c r="C1924" t="inlineStr"/>
+      <c r="C1924" t="n">
+        <v>1000000000</v>
+      </c>
       <c r="D1924" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E1924" t="inlineStr">
-        <is>
-          <t>[100000000.0, 999000000.0]</t>
-        </is>
-      </c>
-      <c r="F1924" t="inlineStr">
-        <is>
-          <t>[100000000.0, 999000000.0]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E1924" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1924" t="n">
+        <v>1000000000</v>
       </c>
       <c r="G1924" s="2" t="n">
         <v>44805</v>
       </c>
-      <c r="H1924" t="inlineStr">
-        <is>
-          <t>[100000000.0, 999000000.0]</t>
-        </is>
-      </c>
-      <c r="I1924" t="inlineStr">
-        <is>
-          <t>[100040000.0, 999399600.0]</t>
-        </is>
+      <c r="H1924" t="n">
+        <v>999600159.9360256</v>
+      </c>
+      <c r="I1924" t="n">
+        <v>1000000000</v>
       </c>
       <c r="J1924" t="n">
         <v>2022</v>
@@ -63451,38 +63445,32 @@
     <row r="1925">
       <c r="A1925" t="inlineStr">
         <is>
-          <t>triple-digit million euros</t>
+          <t>EUR75m</t>
         </is>
       </c>
       <c r="B1925" t="inlineStr"/>
-      <c r="C1925" t="inlineStr"/>
+      <c r="C1925" t="n">
+        <v>1000000</v>
+      </c>
       <c r="D1925" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1925" t="inlineStr">
-        <is>
-          <t>[100000000.0, 999000000.0]</t>
-        </is>
-      </c>
-      <c r="F1925" t="inlineStr">
-        <is>
-          <t>[100000000.0, 999000000.0]</t>
-        </is>
+      <c r="E1925" t="n">
+        <v>75</v>
+      </c>
+      <c r="F1925" t="n">
+        <v>75000000</v>
       </c>
       <c r="G1925" s="2" t="n">
-        <v>44805</v>
-      </c>
-      <c r="H1925" t="inlineStr">
-        <is>
-          <t>[100000000.0, 999000000.0]</t>
-        </is>
-      </c>
-      <c r="I1925" t="inlineStr">
-        <is>
-          <t>[100040000.0, 999399600.0]</t>
-        </is>
+        <v>44835</v>
+      </c>
+      <c r="H1925" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="I1925" t="n">
+        <v>73150000</v>
       </c>
       <c r="J1925" t="n">
         <v>2022</v>
@@ -63491,32 +63479,38 @@
     <row r="1926">
       <c r="A1926" t="inlineStr">
         <is>
-          <t>€800 million</t>
+          <t>triple-digit million euros</t>
         </is>
       </c>
       <c r="B1926" t="inlineStr"/>
-      <c r="C1926" t="n">
-        <v>1000000</v>
-      </c>
+      <c r="C1926" t="inlineStr"/>
       <c r="D1926" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1926" t="n">
-        <v>800</v>
-      </c>
-      <c r="F1926" t="n">
-        <v>800000000</v>
+      <c r="E1926" t="inlineStr">
+        <is>
+          <t>[100000000.0, 999000000.0]</t>
+        </is>
+      </c>
+      <c r="F1926" t="inlineStr">
+        <is>
+          <t>[100000000.0, 999000000.0]</t>
+        </is>
       </c>
       <c r="G1926" s="2" t="n">
-        <v>44835</v>
-      </c>
-      <c r="H1926" t="n">
-        <v>800000000</v>
-      </c>
-      <c r="I1926" t="n">
-        <v>780266666.6666667</v>
+        <v>44805</v>
+      </c>
+      <c r="H1926" t="inlineStr">
+        <is>
+          <t>[100000000.0, 999000000.0]</t>
+        </is>
+      </c>
+      <c r="I1926" t="inlineStr">
+        <is>
+          <t>[100040000.0, 999399600.0]</t>
+        </is>
       </c>
       <c r="J1926" t="n">
         <v>2022</v>
@@ -63525,32 +63519,38 @@
     <row r="1927">
       <c r="A1927" t="inlineStr">
         <is>
-          <t>€800 million</t>
+          <t>triple-digit million euros</t>
         </is>
       </c>
       <c r="B1927" t="inlineStr"/>
-      <c r="C1927" t="n">
-        <v>1000000</v>
-      </c>
+      <c r="C1927" t="inlineStr"/>
       <c r="D1927" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1927" t="n">
-        <v>800</v>
-      </c>
-      <c r="F1927" t="n">
-        <v>800000000</v>
+      <c r="E1927" t="inlineStr">
+        <is>
+          <t>[100000000.0, 999000000.0]</t>
+        </is>
+      </c>
+      <c r="F1927" t="inlineStr">
+        <is>
+          <t>[100000000.0, 999000000.0]</t>
+        </is>
       </c>
       <c r="G1927" s="2" t="n">
-        <v>44835</v>
-      </c>
-      <c r="H1927" t="n">
-        <v>800000000</v>
-      </c>
-      <c r="I1927" t="n">
-        <v>780266666.6666667</v>
+        <v>44805</v>
+      </c>
+      <c r="H1927" t="inlineStr">
+        <is>
+          <t>[100000000.0, 999000000.0]</t>
+        </is>
+      </c>
+      <c r="I1927" t="inlineStr">
+        <is>
+          <t>[100040000.0, 999399600.0]</t>
+        </is>
       </c>
       <c r="J1927" t="n">
         <v>2022</v>
@@ -63695,7 +63695,7 @@
     <row r="1932">
       <c r="A1932" t="inlineStr">
         <is>
-          <t>$14.8 million</t>
+          <t>€800 million</t>
         </is>
       </c>
       <c r="B1932" t="inlineStr"/>
@@ -63704,23 +63704,23 @@
       </c>
       <c r="D1932" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1932" t="n">
-        <v>14.8</v>
+        <v>800</v>
       </c>
       <c r="F1932" t="n">
-        <v>14800000</v>
+        <v>800000000</v>
       </c>
       <c r="G1932" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="H1932" t="n">
-        <v>15174299.3848257</v>
+        <v>800000000</v>
       </c>
       <c r="I1932" t="n">
-        <v>14800000</v>
+        <v>780266666.6666667</v>
       </c>
       <c r="J1932" t="n">
         <v>2022</v>
@@ -63729,12 +63729,12 @@
     <row r="1933">
       <c r="A1933" t="inlineStr">
         <is>
-          <t>€1bn</t>
+          <t>€800 million</t>
         </is>
       </c>
       <c r="B1933" t="inlineStr"/>
       <c r="C1933" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1933" t="inlineStr">
         <is>
@@ -63742,19 +63742,19 @@
         </is>
       </c>
       <c r="E1933" t="n">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="F1933" t="n">
-        <v>1000000000</v>
+        <v>800000000</v>
       </c>
       <c r="G1933" s="2" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="H1933" t="n">
-        <v>1000000000</v>
+        <v>800000000</v>
       </c>
       <c r="I1933" t="n">
-        <v>1000400000</v>
+        <v>780266666.6666667</v>
       </c>
       <c r="J1933" t="n">
         <v>2022</v>
@@ -63763,7 +63763,7 @@
     <row r="1934">
       <c r="A1934" t="inlineStr">
         <is>
-          <t>€135m</t>
+          <t>$14.8 million</t>
         </is>
       </c>
       <c r="B1934" t="inlineStr"/>
@@ -63772,23 +63772,23 @@
       </c>
       <c r="D1934" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E1934" t="n">
-        <v>135</v>
+        <v>14.8</v>
       </c>
       <c r="F1934" t="n">
-        <v>135000000</v>
+        <v>14800000</v>
       </c>
       <c r="G1934" s="2" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="H1934" t="n">
-        <v>135000000</v>
+        <v>15174299.3848257</v>
       </c>
       <c r="I1934" t="n">
-        <v>135054000</v>
+        <v>14800000</v>
       </c>
       <c r="J1934" t="n">
         <v>2022</v>
@@ -63797,12 +63797,12 @@
     <row r="1935">
       <c r="A1935" t="inlineStr">
         <is>
-          <t>€135m</t>
+          <t>€1bn</t>
         </is>
       </c>
       <c r="B1935" t="inlineStr"/>
       <c r="C1935" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1935" t="inlineStr">
         <is>
@@ -63810,19 +63810,19 @@
         </is>
       </c>
       <c r="E1935" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="F1935" t="n">
-        <v>135000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G1935" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="H1935" t="n">
-        <v>135000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I1935" t="n">
-        <v>135054000</v>
+        <v>1000400000</v>
       </c>
       <c r="J1935" t="n">
         <v>2022</v>
@@ -63831,7 +63831,7 @@
     <row r="1936">
       <c r="A1936" t="inlineStr">
         <is>
-          <t>GBP380m</t>
+          <t>€135m</t>
         </is>
       </c>
       <c r="B1936" t="inlineStr"/>
@@ -63840,23 +63840,23 @@
       </c>
       <c r="D1936" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1936" t="n">
-        <v>380</v>
+        <v>135</v>
       </c>
       <c r="F1936" t="n">
-        <v>380000000</v>
+        <v>135000000</v>
       </c>
       <c r="G1936" s="2" t="n">
-        <v>44896</v>
+        <v>44805</v>
       </c>
       <c r="H1936" t="n">
-        <v>443329638.9196757</v>
+        <v>135000000</v>
       </c>
       <c r="I1936" t="n">
-        <v>463456804.526629</v>
+        <v>135054000</v>
       </c>
       <c r="J1936" t="n">
         <v>2022</v>
@@ -63865,7 +63865,7 @@
     <row r="1937">
       <c r="A1937" t="inlineStr">
         <is>
-          <t>GBP24m</t>
+          <t>€135m</t>
         </is>
       </c>
       <c r="B1937" t="inlineStr"/>
@@ -63874,23 +63874,23 @@
       </c>
       <c r="D1937" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1937" t="n">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="F1937" t="n">
-        <v>24000000</v>
+        <v>135000000</v>
       </c>
       <c r="G1937" s="2" t="n">
-        <v>44896</v>
+        <v>44805</v>
       </c>
       <c r="H1937" t="n">
-        <v>27999766.66861109</v>
+        <v>135000000</v>
       </c>
       <c r="I1937" t="n">
-        <v>29270956.07536604</v>
+        <v>135054000</v>
       </c>
       <c r="J1937" t="n">
         <v>2022</v>
@@ -63899,7 +63899,7 @@
     <row r="1938">
       <c r="A1938" t="inlineStr">
         <is>
-          <t>EUR650m</t>
+          <t>GBP380m</t>
         </is>
       </c>
       <c r="B1938" t="inlineStr"/>
@@ -63908,23 +63908,23 @@
       </c>
       <c r="D1938" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1938" t="n">
-        <v>650</v>
+        <v>380</v>
       </c>
       <c r="F1938" t="n">
-        <v>650000000</v>
+        <v>380000000</v>
       </c>
       <c r="G1938" s="2" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="H1938" t="n">
-        <v>650000000</v>
+        <v>443329638.9196757</v>
       </c>
       <c r="I1938" t="n">
-        <v>646555000</v>
+        <v>463456804.526629</v>
       </c>
       <c r="J1938" t="n">
         <v>2022</v>
@@ -63933,7 +63933,7 @@
     <row r="1939">
       <c r="A1939" t="inlineStr">
         <is>
-          <t>EUR650m</t>
+          <t>GBP24m</t>
         </is>
       </c>
       <c r="B1939" t="inlineStr"/>
@@ -63942,23 +63942,23 @@
       </c>
       <c r="D1939" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1939" t="n">
-        <v>650</v>
+        <v>24</v>
       </c>
       <c r="F1939" t="n">
-        <v>650000000</v>
+        <v>24000000</v>
       </c>
       <c r="G1939" s="2" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="H1939" t="n">
-        <v>650000000</v>
+        <v>27999766.66861109</v>
       </c>
       <c r="I1939" t="n">
-        <v>646555000</v>
+        <v>29270956.07536604</v>
       </c>
       <c r="J1939" t="n">
         <v>2022</v>
@@ -63967,7 +63967,7 @@
     <row r="1940">
       <c r="A1940" t="inlineStr">
         <is>
-          <t>GBP500m</t>
+          <t>EUR650m</t>
         </is>
       </c>
       <c r="B1940" t="inlineStr"/>
@@ -63976,23 +63976,23 @@
       </c>
       <c r="D1940" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1940" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="F1940" t="n">
-        <v>500000000</v>
+        <v>650000000</v>
       </c>
       <c r="G1940" s="2" t="n">
-        <v>44805</v>
+        <v>44866</v>
       </c>
       <c r="H1940" t="n">
-        <v>578215165.4273589</v>
+        <v>650000000</v>
       </c>
       <c r="I1940" t="n">
-        <v>578446451.4935298</v>
+        <v>646555000</v>
       </c>
       <c r="J1940" t="n">
         <v>2022</v>
@@ -64001,7 +64001,7 @@
     <row r="1941">
       <c r="A1941" t="inlineStr">
         <is>
-          <t>GBP500m</t>
+          <t>EUR650m</t>
         </is>
       </c>
       <c r="B1941" t="inlineStr"/>
@@ -64010,23 +64010,23 @@
       </c>
       <c r="D1941" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1941" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="F1941" t="n">
-        <v>500000000</v>
+        <v>650000000</v>
       </c>
       <c r="G1941" s="2" t="n">
-        <v>44805</v>
+        <v>44866</v>
       </c>
       <c r="H1941" t="n">
-        <v>578215165.4273589</v>
+        <v>650000000</v>
       </c>
       <c r="I1941" t="n">
-        <v>578446451.4935298</v>
+        <v>646555000</v>
       </c>
       <c r="J1941" t="n">
         <v>2022</v>
@@ -64069,80 +64069,80 @@
     <row r="1943">
       <c r="A1943" t="inlineStr">
         <is>
-          <t>EUR 2 billion</t>
+          <t>GBP500m</t>
         </is>
       </c>
       <c r="B1943" t="inlineStr"/>
       <c r="C1943" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1943" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1943" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="F1943" t="n">
-        <v>2000000000</v>
+        <v>500000000</v>
       </c>
       <c r="G1943" s="2" t="n">
-        <v>45901</v>
+        <v>44805</v>
       </c>
       <c r="H1943" t="n">
-        <v>2000000000</v>
+        <v>578215165.4273589</v>
       </c>
       <c r="I1943" t="n">
-        <v>2330800000</v>
+        <v>578446451.4935298</v>
       </c>
       <c r="J1943" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1944">
       <c r="A1944" t="inlineStr">
         <is>
-          <t>EUR 2 billion</t>
+          <t>GBP500m</t>
         </is>
       </c>
       <c r="B1944" t="inlineStr"/>
       <c r="C1944" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1944" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E1944" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="F1944" t="n">
-        <v>2000000000</v>
+        <v>500000000</v>
       </c>
       <c r="G1944" s="2" t="n">
-        <v>45901</v>
+        <v>44805</v>
       </c>
       <c r="H1944" t="n">
-        <v>2000000000</v>
+        <v>578215165.4273589</v>
       </c>
       <c r="I1944" t="n">
-        <v>2330800000</v>
+        <v>578446451.4935298</v>
       </c>
       <c r="J1944" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1945">
       <c r="A1945" t="inlineStr">
         <is>
-          <t>EUR 2 billion</t>
+          <t>€126-million</t>
         </is>
       </c>
       <c r="B1945" t="inlineStr"/>
       <c r="C1945" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1945" t="inlineStr">
         <is>
@@ -64150,28 +64150,28 @@
         </is>
       </c>
       <c r="E1945" t="n">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="F1945" t="n">
-        <v>2000000000</v>
+        <v>126000000</v>
       </c>
       <c r="G1945" s="2" t="n">
-        <v>45901</v>
+        <v>43647</v>
       </c>
       <c r="H1945" t="n">
-        <v>2000000000</v>
+        <v>126000000</v>
       </c>
       <c r="I1945" t="n">
-        <v>2330800000</v>
+        <v>142997400</v>
       </c>
       <c r="J1945" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1946">
       <c r="A1946" t="inlineStr">
         <is>
-          <t>120 billion forints ($320.2 million)</t>
+          <t>EUR 2 billion</t>
         </is>
       </c>
       <c r="B1946" t="inlineStr"/>
@@ -64180,32 +64180,32 @@
       </c>
       <c r="D1946" t="inlineStr">
         <is>
-          <t>HUF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1946" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="F1946" t="n">
-        <v>120000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="G1946" s="2" t="n">
-        <v>44713</v>
+        <v>45901</v>
       </c>
       <c r="H1946" t="n">
-        <v>303774396.8812495</v>
+        <v>2000000000</v>
       </c>
       <c r="I1946" t="n">
-        <v>325403133.9391945</v>
+        <v>2330800000</v>
       </c>
       <c r="J1946" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1947">
       <c r="A1947" t="inlineStr">
         <is>
-          <t>over EUR 1 billion</t>
+          <t>EUR 2 billion</t>
         </is>
       </c>
       <c r="B1947" t="inlineStr"/>
@@ -64217,28 +64217,20 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1947" t="inlineStr">
-        <is>
-          <t>[1.0, None]</t>
-        </is>
-      </c>
-      <c r="F1947" t="inlineStr">
-        <is>
-          <t>[1000000000.0, None]</t>
-        </is>
+      <c r="E1947" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1947" t="n">
+        <v>2000000000</v>
       </c>
       <c r="G1947" s="2" t="n">
-        <v>45839</v>
-      </c>
-      <c r="H1947" t="inlineStr">
-        <is>
-          <t>[1000000000.0, None]</t>
-        </is>
-      </c>
-      <c r="I1947" t="inlineStr">
-        <is>
-          <t>[1181000000.0, None]</t>
-        </is>
+        <v>45901</v>
+      </c>
+      <c r="H1947" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="I1947" t="n">
+        <v>2330800000</v>
       </c>
       <c r="J1947" t="n">
         <v>2025</v>
@@ -64247,7 +64239,7 @@
     <row r="1948">
       <c r="A1948" t="inlineStr">
         <is>
-          <t>over EUR 1 billion</t>
+          <t>EUR 2 billion</t>
         </is>
       </c>
       <c r="B1948" t="inlineStr"/>
@@ -64259,28 +64251,20 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1948" t="inlineStr">
-        <is>
-          <t>[1.0, None]</t>
-        </is>
-      </c>
-      <c r="F1948" t="inlineStr">
-        <is>
-          <t>[1000000000.0, None]</t>
-        </is>
+      <c r="E1948" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1948" t="n">
+        <v>2000000000</v>
       </c>
       <c r="G1948" s="2" t="n">
-        <v>45839</v>
-      </c>
-      <c r="H1948" t="inlineStr">
-        <is>
-          <t>[1000000000.0, None]</t>
-        </is>
-      </c>
-      <c r="I1948" t="inlineStr">
-        <is>
-          <t>[1181000000.0, None]</t>
-        </is>
+        <v>45901</v>
+      </c>
+      <c r="H1948" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="I1948" t="n">
+        <v>2330800000</v>
       </c>
       <c r="J1948" t="n">
         <v>2025</v>
@@ -64289,49 +64273,41 @@
     <row r="1949">
       <c r="A1949" t="inlineStr">
         <is>
-          <t>more than EUR 100 million</t>
+          <t>120 billion forints ($320.2 million)</t>
         </is>
       </c>
       <c r="B1949" t="inlineStr"/>
       <c r="C1949" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1949" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E1949" t="inlineStr">
-        <is>
-          <t>[100.0, None]</t>
-        </is>
-      </c>
-      <c r="F1949" t="inlineStr">
-        <is>
-          <t>[100000000.0, None]</t>
-        </is>
+          <t>HUF</t>
+        </is>
+      </c>
+      <c r="E1949" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1949" t="n">
+        <v>120000000000</v>
       </c>
       <c r="G1949" s="2" t="n">
-        <v>44470</v>
-      </c>
-      <c r="H1949" t="inlineStr">
-        <is>
-          <t>[100000000.0, None]</t>
-        </is>
-      </c>
-      <c r="I1949" t="inlineStr">
-        <is>
-          <t>[115999999.99999999, None]</t>
-        </is>
+        <v>44713</v>
+      </c>
+      <c r="H1949" t="n">
+        <v>303774396.8812495</v>
+      </c>
+      <c r="I1949" t="n">
+        <v>325403133.9391945</v>
       </c>
       <c r="J1949" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1950">
       <c r="A1950" t="inlineStr">
         <is>
-          <t>HUF 10 billion (EUR 26.2 million)</t>
+          <t>EUR 1.2 billion</t>
         </is>
       </c>
       <c r="B1950" t="inlineStr"/>
@@ -64340,32 +64316,32 @@
       </c>
       <c r="D1950" t="inlineStr">
         <is>
-          <t>HUF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1950" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="F1950" t="n">
-        <v>10000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="G1950" s="2" t="n">
-        <v>45139</v>
+        <v>43739</v>
       </c>
       <c r="H1950" t="n">
-        <v>25690430.31470777</v>
+        <v>1200000000</v>
       </c>
       <c r="I1950" t="n">
-        <v>28182402.05523442</v>
+        <v>1307760000</v>
       </c>
       <c r="J1950" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1951">
       <c r="A1951" t="inlineStr">
         <is>
-          <t>around 1 billion euros</t>
+          <t>over EUR 1 billion</t>
         </is>
       </c>
       <c r="B1951" t="inlineStr"/>
@@ -64377,29 +64353,37 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1951" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1951" t="n">
-        <v>1000000000</v>
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>[1.0, None]</t>
+        </is>
+      </c>
+      <c r="F1951" t="inlineStr">
+        <is>
+          <t>[1000000000.0, None]</t>
+        </is>
       </c>
       <c r="G1951" s="2" t="n">
-        <v>45474</v>
-      </c>
-      <c r="H1951" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="I1951" t="n">
-        <v>1074500000</v>
+        <v>45839</v>
+      </c>
+      <c r="H1951" t="inlineStr">
+        <is>
+          <t>[1000000000.0, None]</t>
+        </is>
+      </c>
+      <c r="I1951" t="inlineStr">
+        <is>
+          <t>[1181000000.0, None]</t>
+        </is>
       </c>
       <c r="J1951" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1952">
       <c r="A1952" t="inlineStr">
         <is>
-          <t>€1 billion ($1.08 billion)</t>
+          <t>over EUR 1 billion</t>
         </is>
       </c>
       <c r="B1952" t="inlineStr"/>
@@ -64411,29 +64395,37 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1952" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1952" t="n">
-        <v>1000000000</v>
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>[1.0, None]</t>
+        </is>
+      </c>
+      <c r="F1952" t="inlineStr">
+        <is>
+          <t>[1000000000.0, None]</t>
+        </is>
       </c>
       <c r="G1952" s="2" t="n">
-        <v>45474</v>
-      </c>
-      <c r="H1952" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="I1952" t="n">
-        <v>1074500000</v>
+        <v>45839</v>
+      </c>
+      <c r="H1952" t="inlineStr">
+        <is>
+          <t>[1000000000.0, None]</t>
+        </is>
+      </c>
+      <c r="I1952" t="inlineStr">
+        <is>
+          <t>[1181000000.0, None]</t>
+        </is>
       </c>
       <c r="J1952" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1953">
       <c r="A1953" t="inlineStr">
         <is>
-          <t>€100 million</t>
+          <t>more than EUR 100 million</t>
         </is>
       </c>
       <c r="B1953" t="inlineStr"/>
@@ -64445,68 +64437,76 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1953" t="n">
-        <v>100</v>
-      </c>
-      <c r="F1953" t="n">
-        <v>100000000</v>
+      <c r="E1953" t="inlineStr">
+        <is>
+          <t>[100.0, None]</t>
+        </is>
+      </c>
+      <c r="F1953" t="inlineStr">
+        <is>
+          <t>[100000000.0, None]</t>
+        </is>
       </c>
       <c r="G1953" s="2" t="n">
-        <v>45658</v>
-      </c>
-      <c r="H1953" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="I1953" t="n">
-        <v>103550000</v>
+        <v>44470</v>
+      </c>
+      <c r="H1953" t="inlineStr">
+        <is>
+          <t>[100000000.0, None]</t>
+        </is>
+      </c>
+      <c r="I1953" t="inlineStr">
+        <is>
+          <t>[115999999.99999999, None]</t>
+        </is>
       </c>
       <c r="J1953" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1954">
       <c r="A1954" t="inlineStr">
         <is>
-          <t>400 million euros</t>
+          <t>HUF 10 billion (EUR 26.2 million)</t>
         </is>
       </c>
       <c r="B1954" t="inlineStr"/>
       <c r="C1954" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1954" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>HUF</t>
         </is>
       </c>
       <c r="E1954" t="n">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="F1954" t="n">
-        <v>400000000</v>
+        <v>10000000000</v>
       </c>
       <c r="G1954" s="2" t="n">
-        <v>45383</v>
+        <v>45139</v>
       </c>
       <c r="H1954" t="n">
-        <v>400000000</v>
+        <v>25690430.31470777</v>
       </c>
       <c r="I1954" t="n">
-        <v>430456000.0000001</v>
+        <v>28182402.05523442</v>
       </c>
       <c r="J1954" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1955">
       <c r="A1955" t="inlineStr">
         <is>
-          <t>400 million euros</t>
+          <t>around 1 billion euros</t>
         </is>
       </c>
       <c r="B1955" t="inlineStr"/>
       <c r="C1955" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1955" t="inlineStr">
         <is>
@@ -64514,19 +64514,19 @@
         </is>
       </c>
       <c r="E1955" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="F1955" t="n">
-        <v>400000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G1955" s="2" t="n">
-        <v>45383</v>
+        <v>45474</v>
       </c>
       <c r="H1955" t="n">
-        <v>400000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I1955" t="n">
-        <v>430456000.0000001</v>
+        <v>1074500000</v>
       </c>
       <c r="J1955" t="n">
         <v>2024</v>
@@ -64535,12 +64535,12 @@
     <row r="1956">
       <c r="A1956" t="inlineStr">
         <is>
-          <t>50 million euro</t>
+          <t>€1 billion ($1.08 billion)</t>
         </is>
       </c>
       <c r="B1956" t="inlineStr"/>
       <c r="C1956" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1956" t="inlineStr">
         <is>
@@ -64548,28 +64548,28 @@
         </is>
       </c>
       <c r="E1956" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F1956" t="n">
-        <v>50000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G1956" s="2" t="n">
-        <v>45901</v>
+        <v>45474</v>
       </c>
       <c r="H1956" t="n">
-        <v>50000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I1956" t="n">
-        <v>58270000</v>
+        <v>1074500000</v>
       </c>
       <c r="J1956" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1957">
       <c r="A1957" t="inlineStr">
         <is>
-          <t>50 million euro</t>
+          <t>€100 million</t>
         </is>
       </c>
       <c r="B1957" t="inlineStr"/>
@@ -64582,19 +64582,19 @@
         </is>
       </c>
       <c r="E1957" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F1957" t="n">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="G1957" s="2" t="n">
-        <v>45901</v>
+        <v>45658</v>
       </c>
       <c r="H1957" t="n">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="I1957" t="n">
-        <v>58270000</v>
+        <v>103550000</v>
       </c>
       <c r="J1957" t="n">
         <v>2025</v>
@@ -64603,7 +64603,7 @@
     <row r="1958">
       <c r="A1958" t="inlineStr">
         <is>
-          <t>50 million euro</t>
+          <t>400 million euros</t>
         </is>
       </c>
       <c r="B1958" t="inlineStr"/>
@@ -64616,28 +64616,28 @@
         </is>
       </c>
       <c r="E1958" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="F1958" t="n">
-        <v>50000000</v>
+        <v>400000000</v>
       </c>
       <c r="G1958" s="2" t="n">
-        <v>45901</v>
+        <v>45383</v>
       </c>
       <c r="H1958" t="n">
-        <v>50000000</v>
+        <v>400000000</v>
       </c>
       <c r="I1958" t="n">
-        <v>58270000</v>
+        <v>430456000.0000001</v>
       </c>
       <c r="J1958" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1959">
       <c r="A1959" t="inlineStr">
         <is>
-          <t>50 million euro</t>
+          <t>400 million euros</t>
         </is>
       </c>
       <c r="B1959" t="inlineStr"/>
@@ -64650,33 +64650,33 @@
         </is>
       </c>
       <c r="E1959" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="F1959" t="n">
-        <v>50000000</v>
+        <v>400000000</v>
       </c>
       <c r="G1959" s="2" t="n">
-        <v>45901</v>
+        <v>45383</v>
       </c>
       <c r="H1959" t="n">
-        <v>50000000</v>
+        <v>400000000</v>
       </c>
       <c r="I1959" t="n">
-        <v>58270000</v>
+        <v>430456000.0000001</v>
       </c>
       <c r="J1959" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1960">
       <c r="A1960" t="inlineStr">
         <is>
-          <t>€1.8 billion</t>
+          <t>50 million euro</t>
         </is>
       </c>
       <c r="B1960" t="inlineStr"/>
       <c r="C1960" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1960" t="inlineStr">
         <is>
@@ -64684,33 +64684,33 @@
         </is>
       </c>
       <c r="E1960" t="n">
-        <v>1.8</v>
+        <v>50</v>
       </c>
       <c r="F1960" t="n">
-        <v>1800000000</v>
+        <v>50000000</v>
       </c>
       <c r="G1960" s="2" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="H1960" t="n">
-        <v>1800000000</v>
+        <v>50000000</v>
       </c>
       <c r="I1960" t="n">
-        <v>1959300000</v>
+        <v>58270000</v>
       </c>
       <c r="J1960" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1961">
       <c r="A1961" t="inlineStr">
         <is>
-          <t>€1.8 billion</t>
+          <t>50 million euro</t>
         </is>
       </c>
       <c r="B1961" t="inlineStr"/>
       <c r="C1961" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1961" t="inlineStr">
         <is>
@@ -64718,33 +64718,33 @@
         </is>
       </c>
       <c r="E1961" t="n">
-        <v>1.8</v>
+        <v>50</v>
       </c>
       <c r="F1961" t="n">
-        <v>1800000000</v>
+        <v>50000000</v>
       </c>
       <c r="G1961" s="2" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="H1961" t="n">
-        <v>1800000000</v>
+        <v>50000000</v>
       </c>
       <c r="I1961" t="n">
-        <v>1959300000</v>
+        <v>58270000</v>
       </c>
       <c r="J1961" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1962">
       <c r="A1962" t="inlineStr">
         <is>
-          <t>€1.8 billion</t>
+          <t>50 million euro</t>
         </is>
       </c>
       <c r="B1962" t="inlineStr"/>
       <c r="C1962" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1962" t="inlineStr">
         <is>
@@ -64752,67 +64752,67 @@
         </is>
       </c>
       <c r="E1962" t="n">
-        <v>1.8</v>
+        <v>50</v>
       </c>
       <c r="F1962" t="n">
-        <v>1800000000</v>
+        <v>50000000</v>
       </c>
       <c r="G1962" s="2" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="H1962" t="n">
-        <v>1800000000</v>
+        <v>50000000</v>
       </c>
       <c r="I1962" t="n">
-        <v>1959300000</v>
+        <v>58270000</v>
       </c>
       <c r="J1962" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1963">
       <c r="A1963" t="inlineStr">
         <is>
-          <t>SEK 6.2 billion</t>
+          <t>50 million euro</t>
         </is>
       </c>
       <c r="B1963" t="inlineStr"/>
       <c r="C1963" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1963" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1963" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="F1963" t="n">
-        <v>6200000000</v>
+        <v>50000000</v>
       </c>
       <c r="G1963" s="2" t="n">
-        <v>45231</v>
+        <v>45901</v>
       </c>
       <c r="H1963" t="n">
-        <v>525156699.9830595</v>
+        <v>50000000</v>
       </c>
       <c r="I1963" t="n">
-        <v>553357614.7721499</v>
+        <v>58270000</v>
       </c>
       <c r="J1963" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1964">
       <c r="A1964" t="inlineStr">
         <is>
-          <t>€13.6 million</t>
+          <t>€1.8 billion</t>
         </is>
       </c>
       <c r="B1964" t="inlineStr"/>
       <c r="C1964" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1964" t="inlineStr">
         <is>
@@ -64820,33 +64820,33 @@
         </is>
       </c>
       <c r="E1964" t="n">
-        <v>13.6</v>
+        <v>1.8</v>
       </c>
       <c r="F1964" t="n">
-        <v>13600000</v>
+        <v>1800000000</v>
       </c>
       <c r="G1964" s="2" t="n">
-        <v>45901</v>
+        <v>45597</v>
       </c>
       <c r="H1964" t="n">
-        <v>13600000</v>
+        <v>1800000000</v>
       </c>
       <c r="I1964" t="n">
-        <v>15849440</v>
+        <v>1959300000</v>
       </c>
       <c r="J1964" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1965">
       <c r="A1965" t="inlineStr">
         <is>
-          <t>€13.6 million</t>
+          <t>€1.8 billion</t>
         </is>
       </c>
       <c r="B1965" t="inlineStr"/>
       <c r="C1965" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1965" t="inlineStr">
         <is>
@@ -64854,33 +64854,33 @@
         </is>
       </c>
       <c r="E1965" t="n">
-        <v>13.6</v>
+        <v>1.8</v>
       </c>
       <c r="F1965" t="n">
-        <v>13600000</v>
+        <v>1800000000</v>
       </c>
       <c r="G1965" s="2" t="n">
-        <v>45901</v>
+        <v>45597</v>
       </c>
       <c r="H1965" t="n">
-        <v>13600000</v>
+        <v>1800000000</v>
       </c>
       <c r="I1965" t="n">
-        <v>15849440</v>
+        <v>1959300000</v>
       </c>
       <c r="J1965" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1966">
       <c r="A1966" t="inlineStr">
         <is>
-          <t>€13.6 million</t>
+          <t>€1.8 billion</t>
         </is>
       </c>
       <c r="B1966" t="inlineStr"/>
       <c r="C1966" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1966" t="inlineStr">
         <is>
@@ -64888,28 +64888,28 @@
         </is>
       </c>
       <c r="E1966" t="n">
-        <v>13.6</v>
+        <v>1.8</v>
       </c>
       <c r="F1966" t="n">
-        <v>13600000</v>
+        <v>1800000000</v>
       </c>
       <c r="G1966" s="2" t="n">
-        <v>45901</v>
+        <v>45597</v>
       </c>
       <c r="H1966" t="n">
-        <v>13600000</v>
+        <v>1800000000</v>
       </c>
       <c r="I1966" t="n">
-        <v>15849440</v>
+        <v>1959300000</v>
       </c>
       <c r="J1966" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1967">
       <c r="A1967" t="inlineStr">
         <is>
-          <t>€1.65 billion</t>
+          <t>SEK 6.2 billion</t>
         </is>
       </c>
       <c r="B1967" t="inlineStr"/>
@@ -64918,37 +64918,37 @@
       </c>
       <c r="D1967" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="E1967" t="n">
-        <v>1.65</v>
+        <v>6.2</v>
       </c>
       <c r="F1967" t="n">
-        <v>1650000000</v>
+        <v>6200000000</v>
       </c>
       <c r="G1967" s="2" t="n">
-        <v>45474</v>
+        <v>45231</v>
       </c>
       <c r="H1967" t="n">
-        <v>1650000000</v>
+        <v>525156699.9830595</v>
       </c>
       <c r="I1967" t="n">
-        <v>1772925000</v>
+        <v>553357614.7721499</v>
       </c>
       <c r="J1967" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1968">
       <c r="A1968" t="inlineStr">
         <is>
-          <t>€1.65 billion</t>
+          <t>€13.6 million</t>
         </is>
       </c>
       <c r="B1968" t="inlineStr"/>
       <c r="C1968" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1968" t="inlineStr">
         <is>
@@ -64956,33 +64956,33 @@
         </is>
       </c>
       <c r="E1968" t="n">
-        <v>1.65</v>
+        <v>13.6</v>
       </c>
       <c r="F1968" t="n">
-        <v>1650000000</v>
+        <v>13600000</v>
       </c>
       <c r="G1968" s="2" t="n">
-        <v>45474</v>
+        <v>45901</v>
       </c>
       <c r="H1968" t="n">
-        <v>1650000000</v>
+        <v>13600000</v>
       </c>
       <c r="I1968" t="n">
-        <v>1772925000</v>
+        <v>15849440</v>
       </c>
       <c r="J1968" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1969">
       <c r="A1969" t="inlineStr">
         <is>
-          <t>€1.65 billion</t>
+          <t>€13.6 million</t>
         </is>
       </c>
       <c r="B1969" t="inlineStr"/>
       <c r="C1969" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1969" t="inlineStr">
         <is>
@@ -64990,112 +64990,130 @@
         </is>
       </c>
       <c r="E1969" t="n">
-        <v>1.65</v>
+        <v>13.6</v>
       </c>
       <c r="F1969" t="n">
-        <v>1650000000</v>
+        <v>13600000</v>
       </c>
       <c r="G1969" s="2" t="n">
-        <v>45474</v>
+        <v>45901</v>
       </c>
       <c r="H1969" t="n">
-        <v>1650000000</v>
+        <v>13600000</v>
       </c>
       <c r="I1969" t="n">
-        <v>1772925000</v>
+        <v>15849440</v>
       </c>
       <c r="J1969" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1970">
       <c r="A1970" t="inlineStr">
         <is>
-          <t>single-digit billion-euro sum</t>
-        </is>
-      </c>
-      <c r="B1970" t="inlineStr">
-        <is>
-          <t>single digit billion</t>
-        </is>
-      </c>
-      <c r="C1970" t="inlineStr"/>
+          <t>€13.6 million</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr"/>
+      <c r="C1970" t="n">
+        <v>1000000</v>
+      </c>
       <c r="D1970" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1970" t="inlineStr"/>
-      <c r="F1970" t="inlineStr"/>
+      <c r="E1970" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F1970" t="n">
+        <v>13600000</v>
+      </c>
       <c r="G1970" s="2" t="n">
-        <v>44713</v>
-      </c>
-      <c r="H1970" t="inlineStr"/>
-      <c r="I1970" t="inlineStr"/>
+        <v>45901</v>
+      </c>
+      <c r="H1970" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="I1970" t="n">
+        <v>15849440</v>
+      </c>
       <c r="J1970" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1971">
       <c r="A1971" t="inlineStr">
         <is>
-          <t>single-digit billion-euro sum</t>
-        </is>
-      </c>
-      <c r="B1971" t="inlineStr">
-        <is>
-          <t>single digit billion</t>
-        </is>
-      </c>
-      <c r="C1971" t="inlineStr"/>
+          <t>€1.65 billion</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr"/>
+      <c r="C1971" t="n">
+        <v>1000000000</v>
+      </c>
       <c r="D1971" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1971" t="inlineStr"/>
-      <c r="F1971" t="inlineStr"/>
+      <c r="E1971" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F1971" t="n">
+        <v>1650000000</v>
+      </c>
       <c r="G1971" s="2" t="n">
-        <v>44713</v>
-      </c>
-      <c r="H1971" t="inlineStr"/>
-      <c r="I1971" t="inlineStr"/>
+        <v>45474</v>
+      </c>
+      <c r="H1971" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="I1971" t="n">
+        <v>1772925000</v>
+      </c>
       <c r="J1971" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1972">
       <c r="A1972" t="inlineStr">
         <is>
-          <t>single-digit billion-euro sum</t>
-        </is>
-      </c>
-      <c r="B1972" t="inlineStr">
-        <is>
-          <t>single digit billion</t>
-        </is>
-      </c>
-      <c r="C1972" t="inlineStr"/>
+          <t>€1.65 billion</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr"/>
+      <c r="C1972" t="n">
+        <v>1000000000</v>
+      </c>
       <c r="D1972" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1972" t="inlineStr"/>
-      <c r="F1972" t="inlineStr"/>
+      <c r="E1972" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F1972" t="n">
+        <v>1650000000</v>
+      </c>
       <c r="G1972" s="2" t="n">
-        <v>44713</v>
-      </c>
-      <c r="H1972" t="inlineStr"/>
-      <c r="I1972" t="inlineStr"/>
+        <v>45474</v>
+      </c>
+      <c r="H1972" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="I1972" t="n">
+        <v>1772925000</v>
+      </c>
       <c r="J1972" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1973">
       <c r="A1973" t="inlineStr">
         <is>
-          <t>EUR 3.5 billion</t>
+          <t>€1.65 billion</t>
         </is>
       </c>
       <c r="B1973" t="inlineStr"/>
@@ -65108,67 +65126,65 @@
         </is>
       </c>
       <c r="E1973" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="F1973" t="n">
-        <v>3500000000</v>
+        <v>1650000000</v>
       </c>
       <c r="G1973" s="2" t="n">
-        <v>45078</v>
+        <v>45474</v>
       </c>
       <c r="H1973" t="n">
-        <v>3500000000</v>
+        <v>1650000000</v>
       </c>
       <c r="I1973" t="n">
-        <v>3743950000</v>
+        <v>1772925000</v>
       </c>
       <c r="J1973" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1974">
       <c r="A1974" t="inlineStr">
         <is>
-          <t>EUR 3.5 billion</t>
+          <t>$550,000</t>
         </is>
       </c>
       <c r="B1974" t="inlineStr"/>
-      <c r="C1974" t="n">
-        <v>1000000000</v>
-      </c>
+      <c r="C1974" t="inlineStr"/>
       <c r="D1974" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E1974" t="n">
-        <v>3.5</v>
+        <v>550000</v>
       </c>
       <c r="F1974" t="n">
-        <v>3500000000</v>
+        <v>550000</v>
       </c>
       <c r="G1974" s="2" t="n">
-        <v>45078</v>
+        <v>45566</v>
       </c>
       <c r="H1974" t="n">
-        <v>3500000000</v>
+        <v>496121.2339888147</v>
       </c>
       <c r="I1974" t="n">
-        <v>3743950000</v>
+        <v>550000</v>
       </c>
       <c r="J1974" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1975">
       <c r="A1975" t="inlineStr">
         <is>
-          <t>EUR 3.5 billion</t>
+          <t>€14 million</t>
         </is>
       </c>
       <c r="B1975" t="inlineStr"/>
       <c r="C1975" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1975" t="inlineStr">
         <is>
@@ -65176,33 +65192,33 @@
         </is>
       </c>
       <c r="E1975" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="F1975" t="n">
-        <v>3500000000</v>
+        <v>14000000</v>
       </c>
       <c r="G1975" s="2" t="n">
-        <v>45078</v>
+        <v>44044</v>
       </c>
       <c r="H1975" t="n">
-        <v>3500000000</v>
+        <v>14000000</v>
       </c>
       <c r="I1975" t="n">
-        <v>3743950000</v>
+        <v>16530266.66666667</v>
       </c>
       <c r="J1975" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1976">
       <c r="A1976" t="inlineStr">
         <is>
-          <t>EUR 3.5 billion</t>
+          <t>€14 million</t>
         </is>
       </c>
       <c r="B1976" t="inlineStr"/>
       <c r="C1976" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1976" t="inlineStr">
         <is>
@@ -65210,130 +65226,112 @@
         </is>
       </c>
       <c r="E1976" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="F1976" t="n">
-        <v>3500000000</v>
+        <v>14000000</v>
       </c>
       <c r="G1976" s="2" t="n">
-        <v>45078</v>
+        <v>44044</v>
       </c>
       <c r="H1976" t="n">
-        <v>3500000000</v>
+        <v>14000000</v>
       </c>
       <c r="I1976" t="n">
-        <v>3743950000</v>
+        <v>16530266.66666667</v>
       </c>
       <c r="J1976" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1977">
       <c r="A1977" t="inlineStr">
         <is>
-          <t>€1 billion</t>
-        </is>
-      </c>
-      <c r="B1977" t="inlineStr"/>
-      <c r="C1977" t="n">
-        <v>1000000000</v>
-      </c>
+          <t>single-digit billion-euro sum</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>single digit billion</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr"/>
       <c r="D1977" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1977" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1977" t="n">
-        <v>1000000000</v>
-      </c>
+      <c r="E1977" t="inlineStr"/>
+      <c r="F1977" t="inlineStr"/>
       <c r="G1977" s="2" t="n">
-        <v>45352</v>
-      </c>
-      <c r="H1977" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="I1977" t="n">
-        <v>1081300000</v>
-      </c>
+        <v>44713</v>
+      </c>
+      <c r="H1977" t="inlineStr"/>
+      <c r="I1977" t="inlineStr"/>
       <c r="J1977" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1978">
       <c r="A1978" t="inlineStr">
         <is>
-          <t>€1.8 billion</t>
-        </is>
-      </c>
-      <c r="B1978" t="inlineStr"/>
-      <c r="C1978" t="n">
-        <v>1000000000</v>
-      </c>
+          <t>single-digit billion-euro sum</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>single digit billion</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr"/>
       <c r="D1978" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1978" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F1978" t="n">
-        <v>1800000000</v>
-      </c>
+      <c r="E1978" t="inlineStr"/>
+      <c r="F1978" t="inlineStr"/>
       <c r="G1978" s="2" t="n">
-        <v>45352</v>
-      </c>
-      <c r="H1978" t="n">
-        <v>1800000000</v>
-      </c>
-      <c r="I1978" t="n">
-        <v>1946340000</v>
-      </c>
+        <v>44713</v>
+      </c>
+      <c r="H1978" t="inlineStr"/>
+      <c r="I1978" t="inlineStr"/>
       <c r="J1978" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1979">
       <c r="A1979" t="inlineStr">
         <is>
-          <t>€1.8 billion</t>
-        </is>
-      </c>
-      <c r="B1979" t="inlineStr"/>
-      <c r="C1979" t="n">
-        <v>1000000000</v>
-      </c>
+          <t>single-digit billion-euro sum</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>single digit billion</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr"/>
       <c r="D1979" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1979" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F1979" t="n">
-        <v>1800000000</v>
-      </c>
+      <c r="E1979" t="inlineStr"/>
+      <c r="F1979" t="inlineStr"/>
       <c r="G1979" s="2" t="n">
-        <v>45352</v>
-      </c>
-      <c r="H1979" t="n">
-        <v>1800000000</v>
-      </c>
-      <c r="I1979" t="n">
-        <v>1946340000</v>
-      </c>
+        <v>44713</v>
+      </c>
+      <c r="H1979" t="inlineStr"/>
+      <c r="I1979" t="inlineStr"/>
       <c r="J1979" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1980">
       <c r="A1980" t="inlineStr">
         <is>
-          <t>€1.8 billion</t>
+          <t>EUR 3.5 billion</t>
         </is>
       </c>
       <c r="B1980" t="inlineStr"/>
@@ -65346,28 +65344,28 @@
         </is>
       </c>
       <c r="E1980" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="F1980" t="n">
-        <v>1800000000</v>
+        <v>3500000000</v>
       </c>
       <c r="G1980" s="2" t="n">
-        <v>45352</v>
+        <v>45078</v>
       </c>
       <c r="H1980" t="n">
-        <v>1800000000</v>
+        <v>3500000000</v>
       </c>
       <c r="I1980" t="n">
-        <v>1946340000</v>
+        <v>3743950000</v>
       </c>
       <c r="J1980" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>EUR 3.5 billion</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr"/>
@@ -65379,37 +65377,29 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1981" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F1981" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+      <c r="E1981" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1981" t="n">
+        <v>3500000000</v>
       </c>
       <c r="G1981" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="H1981" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I1981" t="inlineStr">
-        <is>
-          <t>[1205300000.0, 1807950000.0]</t>
-        </is>
+        <v>45078</v>
+      </c>
+      <c r="H1981" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="I1981" t="n">
+        <v>3743950000</v>
       </c>
       <c r="J1981" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1982">
       <c r="A1982" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>EUR 3.5 billion</t>
         </is>
       </c>
       <c r="B1982" t="inlineStr"/>
@@ -65421,37 +65411,29 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1982" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F1982" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+      <c r="E1982" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1982" t="n">
+        <v>3500000000</v>
       </c>
       <c r="G1982" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="H1982" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I1982" t="inlineStr">
-        <is>
-          <t>[1205300000.0, 1807950000.0]</t>
-        </is>
+        <v>45078</v>
+      </c>
+      <c r="H1982" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="I1982" t="n">
+        <v>3743950000</v>
       </c>
       <c r="J1982" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1983">
       <c r="A1983" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>EUR 3.5 billion</t>
         </is>
       </c>
       <c r="B1983" t="inlineStr"/>
@@ -65463,37 +65445,29 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1983" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F1983" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+      <c r="E1983" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1983" t="n">
+        <v>3500000000</v>
       </c>
       <c r="G1983" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="H1983" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I1983" t="inlineStr">
-        <is>
-          <t>[1205300000.0, 1807950000.0]</t>
-        </is>
+        <v>45078</v>
+      </c>
+      <c r="H1983" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="I1983" t="n">
+        <v>3743950000</v>
       </c>
       <c r="J1983" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1984">
       <c r="A1984" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>€1 billion</t>
         </is>
       </c>
       <c r="B1984" t="inlineStr"/>
@@ -65505,37 +65479,29 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1984" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F1984" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+      <c r="E1984" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1984" t="n">
+        <v>1000000000</v>
       </c>
       <c r="G1984" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="H1984" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I1984" t="inlineStr">
-        <is>
-          <t>[1205300000.0, 1807950000.0]</t>
-        </is>
+        <v>45352</v>
+      </c>
+      <c r="H1984" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I1984" t="n">
+        <v>1081300000</v>
       </c>
       <c r="J1984" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1985">
       <c r="A1985" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>€1.8 billion</t>
         </is>
       </c>
       <c r="B1985" t="inlineStr"/>
@@ -65547,37 +65513,29 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1985" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F1985" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+      <c r="E1985" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F1985" t="n">
+        <v>1800000000</v>
       </c>
       <c r="G1985" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="H1985" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I1985" t="inlineStr">
-        <is>
-          <t>[1205300000.0, 1807950000.0]</t>
-        </is>
+        <v>45352</v>
+      </c>
+      <c r="H1985" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="I1985" t="n">
+        <v>1946340000</v>
       </c>
       <c r="J1985" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1986">
       <c r="A1986" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>€1.8 billion</t>
         </is>
       </c>
       <c r="B1986" t="inlineStr"/>
@@ -65589,37 +65547,29 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1986" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F1986" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+      <c r="E1986" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F1986" t="n">
+        <v>1800000000</v>
       </c>
       <c r="G1986" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="H1986" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I1986" t="inlineStr">
-        <is>
-          <t>[1205300000.0, 1807950000.0]</t>
-        </is>
+        <v>45352</v>
+      </c>
+      <c r="H1986" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="I1986" t="n">
+        <v>1946340000</v>
       </c>
       <c r="J1986" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1987">
       <c r="A1987" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>€1.8 billion</t>
         </is>
       </c>
       <c r="B1987" t="inlineStr"/>
@@ -65631,31 +65581,23 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1987" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F1987" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+      <c r="E1987" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F1987" t="n">
+        <v>1800000000</v>
       </c>
       <c r="G1987" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="H1987" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I1987" t="inlineStr">
-        <is>
-          <t>[1205300000.0, 1807950000.0]</t>
-        </is>
+        <v>45352</v>
+      </c>
+      <c r="H1987" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="I1987" t="n">
+        <v>1946340000</v>
       </c>
       <c r="J1987" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1988">
@@ -65703,96 +65645,124 @@
     <row r="1989">
       <c r="A1989" t="inlineStr">
         <is>
-          <t>two billion euros</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B1989" t="inlineStr"/>
-      <c r="C1989" t="inlineStr"/>
+      <c r="C1989" t="n">
+        <v>1000000000</v>
+      </c>
       <c r="D1989" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1989" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="F1989" t="n">
-        <v>1000000000</v>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1989" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G1989" s="2" t="n">
-        <v>45231</v>
-      </c>
-      <c r="H1989" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="I1989" t="n">
-        <v>1053700000</v>
+        <v>44256</v>
+      </c>
+      <c r="H1989" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1989" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
       </c>
       <c r="J1989" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1990">
       <c r="A1990" t="inlineStr">
         <is>
-          <t>two billion euros</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B1990" t="inlineStr"/>
-      <c r="C1990" t="inlineStr"/>
+      <c r="C1990" t="n">
+        <v>1000000000</v>
+      </c>
       <c r="D1990" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1990" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="F1990" t="n">
-        <v>1000000000</v>
+      <c r="E1990" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1990" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G1990" s="2" t="n">
-        <v>45231</v>
-      </c>
-      <c r="H1990" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="I1990" t="n">
-        <v>1053700000</v>
+        <v>44256</v>
+      </c>
+      <c r="H1990" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1990" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
       </c>
       <c r="J1990" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1991">
       <c r="A1991" t="inlineStr">
         <is>
-          <t>EUR 165m</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B1991" t="inlineStr"/>
       <c r="C1991" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1991" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1991" t="n">
-        <v>165</v>
-      </c>
-      <c r="F1991" t="n">
-        <v>165000000</v>
+      <c r="E1991" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1991" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G1991" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="H1991" t="n">
-        <v>165000000</v>
-      </c>
-      <c r="I1991" t="n">
-        <v>199144000</v>
+        <v>44256</v>
+      </c>
+      <c r="H1991" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1991" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
       </c>
       <c r="J1991" t="n">
         <v>2021</v>
@@ -65801,132 +65771,198 @@
     <row r="1992">
       <c r="A1992" t="inlineStr">
         <is>
-          <t>EUR 165m</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B1992" t="inlineStr"/>
       <c r="C1992" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1992" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1992" t="n">
-        <v>165</v>
-      </c>
-      <c r="F1992" t="n">
-        <v>165000000</v>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1992" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G1992" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="H1992" t="n">
-        <v>165000000</v>
-      </c>
-      <c r="I1992" t="n">
-        <v>199144000</v>
+        <v>44256</v>
+      </c>
+      <c r="H1992" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1992" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
       </c>
       <c r="J1992" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="1993">
-      <c r="A1993" t="inlineStr"/>
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
       <c r="B1993" t="inlineStr"/>
-      <c r="C1993" t="inlineStr"/>
-      <c r="D1993" t="inlineStr"/>
-      <c r="E1993" t="inlineStr"/>
-      <c r="F1993" t="inlineStr"/>
+      <c r="C1993" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1993" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1993" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1993" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
       <c r="G1993" s="2" t="n">
-        <v>44652</v>
-      </c>
-      <c r="H1993" t="inlineStr"/>
-      <c r="I1993" t="inlineStr"/>
+        <v>44256</v>
+      </c>
+      <c r="H1993" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1993" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
+      </c>
       <c r="J1993" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1994">
-      <c r="A1994" t="inlineStr"/>
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>€1-1.5 billion</t>
+        </is>
+      </c>
       <c r="B1994" t="inlineStr"/>
-      <c r="C1994" t="inlineStr"/>
-      <c r="D1994" t="inlineStr"/>
-      <c r="E1994" t="inlineStr"/>
-      <c r="F1994" t="inlineStr"/>
+      <c r="C1994" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D1994" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E1994" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1994" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
       <c r="G1994" s="2" t="n">
-        <v>44652</v>
-      </c>
-      <c r="H1994" t="inlineStr"/>
-      <c r="I1994" t="inlineStr"/>
+        <v>44256</v>
+      </c>
+      <c r="H1994" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1994" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
+      </c>
       <c r="J1994" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1995">
       <c r="A1995" t="inlineStr">
         <is>
-          <t>€55 million</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B1995" t="inlineStr"/>
       <c r="C1995" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1995" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E1995" t="n">
-        <v>55</v>
-      </c>
-      <c r="F1995" t="n">
-        <v>55000000</v>
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F1995" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G1995" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="H1995" t="n">
-        <v>55000000</v>
-      </c>
-      <c r="I1995" t="n">
-        <v>64097000</v>
+        <v>44256</v>
+      </c>
+      <c r="H1995" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I1995" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
       </c>
       <c r="J1995" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1996">
       <c r="A1996" t="inlineStr">
         <is>
-          <t>20 million euros</t>
+          <t>two billion euros</t>
         </is>
       </c>
       <c r="B1996" t="inlineStr"/>
-      <c r="C1996" t="n">
-        <v>1000000</v>
-      </c>
+      <c r="C1996" t="inlineStr"/>
       <c r="D1996" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
       <c r="E1996" t="n">
-        <v>20</v>
+        <v>1000000000</v>
       </c>
       <c r="F1996" t="n">
-        <v>20000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G1996" s="2" t="n">
-        <v>45017</v>
+        <v>45231</v>
       </c>
       <c r="H1996" t="n">
-        <v>20000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I1996" t="n">
-        <v>21746666.66666666</v>
+        <v>1053700000</v>
       </c>
       <c r="J1996" t="n">
         <v>2023</v>
@@ -65935,43 +65971,39 @@
     <row r="1997">
       <c r="A1997" t="inlineStr">
         <is>
-          <t>$20.35m</t>
-        </is>
-      </c>
-      <c r="B1997" t="inlineStr">
-        <is>
-          <t>35m</t>
-        </is>
-      </c>
+          <t>two billion euros</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr"/>
       <c r="C1997" t="inlineStr"/>
       <c r="D1997" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E1997" t="n">
-        <v>20</v>
+        <v>1000000000</v>
       </c>
       <c r="F1997" t="n">
-        <v>20</v>
+        <v>1000000000</v>
       </c>
       <c r="G1997" s="2" t="n">
-        <v>44743</v>
+        <v>45231</v>
       </c>
       <c r="H1997" t="n">
-        <v>19.18465227817746</v>
+        <v>1000000000</v>
       </c>
       <c r="I1997" t="n">
-        <v>20</v>
+        <v>1053700000</v>
       </c>
       <c r="J1997" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1998">
       <c r="A1998" t="inlineStr">
         <is>
-          <t>€50 million</t>
+          <t>EUR 165m</t>
         </is>
       </c>
       <c r="B1998" t="inlineStr"/>
@@ -65984,19 +66016,19 @@
         </is>
       </c>
       <c r="E1998" t="n">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="F1998" t="n">
-        <v>50000000</v>
+        <v>165000000</v>
       </c>
       <c r="G1998" s="2" t="n">
-        <v>44378</v>
+        <v>44317</v>
       </c>
       <c r="H1998" t="n">
-        <v>50000000</v>
+        <v>165000000</v>
       </c>
       <c r="I1998" t="n">
-        <v>59419999.99999999</v>
+        <v>199144000</v>
       </c>
       <c r="J1998" t="n">
         <v>2021</v>
@@ -66005,12 +66037,12 @@
     <row r="1999">
       <c r="A1999" t="inlineStr">
         <is>
-          <t>€1 billion</t>
+          <t>EUR 165m</t>
         </is>
       </c>
       <c r="B1999" t="inlineStr"/>
       <c r="C1999" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D1999" t="inlineStr">
         <is>
@@ -66018,86 +66050,52 @@
         </is>
       </c>
       <c r="E1999" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="F1999" t="n">
-        <v>1000000000</v>
+        <v>165000000</v>
       </c>
       <c r="G1999" s="2" t="n">
-        <v>44378</v>
+        <v>44317</v>
       </c>
       <c r="H1999" t="n">
-        <v>1000000000</v>
+        <v>165000000</v>
       </c>
       <c r="I1999" t="n">
-        <v>1188400000</v>
+        <v>199144000</v>
       </c>
       <c r="J1999" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="2000">
-      <c r="A2000" t="inlineStr">
-        <is>
-          <t>around two billion euros</t>
-        </is>
-      </c>
+      <c r="A2000" t="inlineStr"/>
       <c r="B2000" t="inlineStr"/>
       <c r="C2000" t="inlineStr"/>
-      <c r="D2000" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2000" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="F2000" t="n">
-        <v>1000000000</v>
-      </c>
+      <c r="D2000" t="inlineStr"/>
+      <c r="E2000" t="inlineStr"/>
+      <c r="F2000" t="inlineStr"/>
       <c r="G2000" s="2" t="n">
-        <v>45323</v>
-      </c>
-      <c r="H2000" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="I2000" t="n">
-        <v>1081400000</v>
-      </c>
+        <v>44652</v>
+      </c>
+      <c r="H2000" t="inlineStr"/>
+      <c r="I2000" t="inlineStr"/>
       <c r="J2000" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2001">
-      <c r="A2001" t="inlineStr">
-        <is>
-          <t>€2 billion</t>
-        </is>
-      </c>
+      <c r="A2001" t="inlineStr"/>
       <c r="B2001" t="inlineStr"/>
-      <c r="C2001" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D2001" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2001" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2001" t="n">
-        <v>2000000000</v>
-      </c>
+      <c r="C2001" t="inlineStr"/>
+      <c r="D2001" t="inlineStr"/>
+      <c r="E2001" t="inlineStr"/>
+      <c r="F2001" t="inlineStr"/>
       <c r="G2001" s="2" t="n">
-        <v>44805</v>
-      </c>
-      <c r="H2001" t="n">
-        <v>2000000000</v>
-      </c>
-      <c r="I2001" t="n">
-        <v>2000800000</v>
-      </c>
+        <v>44652</v>
+      </c>
+      <c r="H2001" t="inlineStr"/>
+      <c r="I2001" t="inlineStr"/>
       <c r="J2001" t="n">
         <v>2022</v>
       </c>
@@ -66105,12 +66103,12 @@
     <row r="2002">
       <c r="A2002" t="inlineStr">
         <is>
-          <t>€2 billion</t>
+          <t>€55 million</t>
         </is>
       </c>
       <c r="B2002" t="inlineStr"/>
       <c r="C2002" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2002" t="inlineStr">
         <is>
@@ -66118,51 +66116,53 @@
         </is>
       </c>
       <c r="E2002" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="F2002" t="n">
-        <v>2000000000</v>
+        <v>55000000</v>
       </c>
       <c r="G2002" s="2" t="n">
-        <v>44805</v>
+        <v>45901</v>
       </c>
       <c r="H2002" t="n">
-        <v>2000000000</v>
+        <v>55000000</v>
       </c>
       <c r="I2002" t="n">
-        <v>2000800000</v>
+        <v>64097000</v>
       </c>
       <c r="J2002" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2003">
       <c r="A2003" t="inlineStr">
         <is>
-          <t>two billion euros</t>
+          <t>20 million euros</t>
         </is>
       </c>
       <c r="B2003" t="inlineStr"/>
-      <c r="C2003" t="inlineStr"/>
+      <c r="C2003" t="n">
+        <v>1000000</v>
+      </c>
       <c r="D2003" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
       <c r="E2003" t="n">
-        <v>1000000000</v>
+        <v>20</v>
       </c>
       <c r="F2003" t="n">
-        <v>1000000000</v>
+        <v>20000000</v>
       </c>
       <c r="G2003" s="2" t="n">
-        <v>45261</v>
+        <v>45017</v>
       </c>
       <c r="H2003" t="n">
-        <v>1000000000</v>
+        <v>20000000</v>
       </c>
       <c r="I2003" t="n">
-        <v>1087500000</v>
+        <v>21746666.66666666</v>
       </c>
       <c r="J2003" t="n">
         <v>2023</v>
@@ -66171,39 +66171,43 @@
     <row r="2004">
       <c r="A2004" t="inlineStr">
         <is>
-          <t>two billion euros</t>
-        </is>
-      </c>
-      <c r="B2004" t="inlineStr"/>
+          <t>$20.35m</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>35m</t>
+        </is>
+      </c>
       <c r="C2004" t="inlineStr"/>
       <c r="D2004" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E2004" t="n">
-        <v>1000000000</v>
+        <v>20</v>
       </c>
       <c r="F2004" t="n">
-        <v>1000000000</v>
+        <v>20</v>
       </c>
       <c r="G2004" s="2" t="n">
-        <v>45108</v>
+        <v>44743</v>
       </c>
       <c r="H2004" t="n">
-        <v>1000000000</v>
+        <v>19.18465227817746</v>
       </c>
       <c r="I2004" t="n">
-        <v>1087700000</v>
+        <v>20</v>
       </c>
       <c r="J2004" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2005">
       <c r="A2005" t="inlineStr">
         <is>
-          <t>€74 million</t>
+          <t>€50 million</t>
         </is>
       </c>
       <c r="B2005" t="inlineStr"/>
@@ -66216,28 +66220,28 @@
         </is>
       </c>
       <c r="E2005" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="F2005" t="n">
-        <v>74000000</v>
+        <v>50000000</v>
       </c>
       <c r="G2005" s="2" t="n">
-        <v>45474</v>
+        <v>44378</v>
       </c>
       <c r="H2005" t="n">
-        <v>74000000</v>
+        <v>50000000</v>
       </c>
       <c r="I2005" t="n">
-        <v>79513000</v>
+        <v>59419999.99999999</v>
       </c>
       <c r="J2005" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2006">
       <c r="A2006" t="inlineStr">
         <is>
-          <t>SEK 6.2 billion</t>
+          <t>€1 billion</t>
         </is>
       </c>
       <c r="B2006" t="inlineStr"/>
@@ -66246,82 +66250,98 @@
       </c>
       <c r="D2006" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E2006" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="F2006" t="n">
-        <v>6200000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G2006" s="2" t="n">
-        <v>45078</v>
+        <v>44378</v>
       </c>
       <c r="H2006" t="n">
-        <v>532394487.1409557</v>
+        <v>1000000000</v>
       </c>
       <c r="I2006" t="n">
-        <v>569502382.8946804</v>
+        <v>1188400000</v>
       </c>
       <c r="J2006" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2007">
       <c r="A2007" t="inlineStr">
         <is>
-          <t>SEK 400 million</t>
+          <t>around two billion euros</t>
         </is>
       </c>
       <c r="B2007" t="inlineStr"/>
-      <c r="C2007" t="n">
-        <v>1000000</v>
-      </c>
+      <c r="C2007" t="inlineStr"/>
       <c r="D2007" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E2007" t="n">
-        <v>400</v>
+        <v>1000000000</v>
       </c>
       <c r="F2007" t="n">
-        <v>400000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G2007" s="2" t="n">
-        <v>45536</v>
+        <v>45323</v>
       </c>
       <c r="H2007" t="n">
-        <v>35255233.19867793</v>
+        <v>1000000000</v>
       </c>
       <c r="I2007" t="n">
-        <v>39026367.97649651</v>
+        <v>1081400000</v>
       </c>
       <c r="J2007" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="2008">
-      <c r="A2008" t="inlineStr"/>
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>€2 billion</t>
+        </is>
+      </c>
       <c r="B2008" t="inlineStr"/>
-      <c r="C2008" t="inlineStr"/>
-      <c r="D2008" t="inlineStr"/>
-      <c r="E2008" t="inlineStr"/>
-      <c r="F2008" t="inlineStr"/>
+      <c r="C2008" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2008" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2008" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2008" t="n">
+        <v>2000000000</v>
+      </c>
       <c r="G2008" s="2" t="n">
-        <v>44927</v>
-      </c>
-      <c r="H2008" t="inlineStr"/>
-      <c r="I2008" t="inlineStr"/>
+        <v>44805</v>
+      </c>
+      <c r="H2008" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="I2008" t="n">
+        <v>2000800000</v>
+      </c>
       <c r="J2008" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2009">
       <c r="A2009" t="inlineStr">
         <is>
-          <t>€4.2 billion</t>
+          <t>€2 billion</t>
         </is>
       </c>
       <c r="B2009" t="inlineStr"/>
@@ -66334,96 +66354,92 @@
         </is>
       </c>
       <c r="E2009" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="F2009" t="n">
-        <v>4200000000</v>
+        <v>2000000000</v>
       </c>
       <c r="G2009" s="2" t="n">
-        <v>45292</v>
+        <v>44805</v>
       </c>
       <c r="H2009" t="n">
-        <v>4200000000</v>
+        <v>2000000000</v>
       </c>
       <c r="I2009" t="n">
-        <v>4611390000</v>
+        <v>2000800000</v>
       </c>
       <c r="J2009" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2010">
       <c r="A2010" t="inlineStr">
         <is>
-          <t>€4.2 billion</t>
+          <t>two billion euros</t>
         </is>
       </c>
       <c r="B2010" t="inlineStr"/>
-      <c r="C2010" t="n">
-        <v>1000000000</v>
-      </c>
+      <c r="C2010" t="inlineStr"/>
       <c r="D2010" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
       <c r="E2010" t="n">
-        <v>4.2</v>
+        <v>1000000000</v>
       </c>
       <c r="F2010" t="n">
-        <v>4200000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G2010" s="2" t="n">
-        <v>45292</v>
+        <v>45261</v>
       </c>
       <c r="H2010" t="n">
-        <v>4200000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I2010" t="n">
-        <v>4611390000</v>
+        <v>1087500000</v>
       </c>
       <c r="J2010" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2011">
       <c r="A2011" t="inlineStr">
         <is>
-          <t>€4.2 billion</t>
+          <t>two billion euros</t>
         </is>
       </c>
       <c r="B2011" t="inlineStr"/>
-      <c r="C2011" t="n">
-        <v>1000000000</v>
-      </c>
+      <c r="C2011" t="inlineStr"/>
       <c r="D2011" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
       <c r="E2011" t="n">
-        <v>4.2</v>
+        <v>1000000000</v>
       </c>
       <c r="F2011" t="n">
-        <v>4200000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G2011" s="2" t="n">
-        <v>45292</v>
+        <v>45108</v>
       </c>
       <c r="H2011" t="n">
-        <v>4200000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I2011" t="n">
-        <v>4611390000</v>
+        <v>1087700000</v>
       </c>
       <c r="J2011" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2012">
       <c r="A2012" t="inlineStr">
         <is>
-          <t>€300 million</t>
+          <t>€74 million</t>
         </is>
       </c>
       <c r="B2012" t="inlineStr"/>
@@ -66436,19 +66452,19 @@
         </is>
       </c>
       <c r="E2012" t="n">
-        <v>300</v>
+        <v>74</v>
       </c>
       <c r="F2012" t="n">
-        <v>300000000</v>
+        <v>74000000</v>
       </c>
       <c r="G2012" s="2" t="n">
-        <v>45292</v>
+        <v>45474</v>
       </c>
       <c r="H2012" t="n">
-        <v>300000000</v>
+        <v>74000000</v>
       </c>
       <c r="I2012" t="n">
-        <v>329385000</v>
+        <v>79513000</v>
       </c>
       <c r="J2012" t="n">
         <v>2024</v>
@@ -66457,41 +66473,41 @@
     <row r="2013">
       <c r="A2013" t="inlineStr">
         <is>
-          <t>€300 million</t>
+          <t>SEK 6.2 billion</t>
         </is>
       </c>
       <c r="B2013" t="inlineStr"/>
       <c r="C2013" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2013" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="E2013" t="n">
-        <v>300</v>
+        <v>6.2</v>
       </c>
       <c r="F2013" t="n">
-        <v>300000000</v>
+        <v>6200000000</v>
       </c>
       <c r="G2013" s="2" t="n">
-        <v>45292</v>
+        <v>45078</v>
       </c>
       <c r="H2013" t="n">
-        <v>300000000</v>
+        <v>532394487.1409557</v>
       </c>
       <c r="I2013" t="n">
-        <v>329385000</v>
+        <v>569502382.8946804</v>
       </c>
       <c r="J2013" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2014">
       <c r="A2014" t="inlineStr">
         <is>
-          <t>€300 million</t>
+          <t>SEK 400 million</t>
         </is>
       </c>
       <c r="B2014" t="inlineStr"/>
@@ -66500,71 +66516,53 @@
       </c>
       <c r="D2014" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="E2014" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F2014" t="n">
-        <v>300000000</v>
+        <v>400000000</v>
       </c>
       <c r="G2014" s="2" t="n">
-        <v>45292</v>
+        <v>45536</v>
       </c>
       <c r="H2014" t="n">
-        <v>300000000</v>
+        <v>35255233.19867793</v>
       </c>
       <c r="I2014" t="n">
-        <v>329385000</v>
+        <v>39026367.97649651</v>
       </c>
       <c r="J2014" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="2015">
-      <c r="A2015" t="inlineStr">
-        <is>
-          <t>€250 million</t>
-        </is>
-      </c>
+      <c r="A2015" t="inlineStr"/>
       <c r="B2015" t="inlineStr"/>
-      <c r="C2015" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D2015" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2015" t="n">
-        <v>250</v>
-      </c>
-      <c r="F2015" t="n">
-        <v>250000000</v>
-      </c>
+      <c r="C2015" t="inlineStr"/>
+      <c r="D2015" t="inlineStr"/>
+      <c r="E2015" t="inlineStr"/>
+      <c r="F2015" t="inlineStr"/>
       <c r="G2015" s="2" t="n">
-        <v>45292</v>
-      </c>
-      <c r="H2015" t="n">
-        <v>250000000</v>
-      </c>
-      <c r="I2015" t="n">
-        <v>274487500</v>
-      </c>
+        <v>44927</v>
+      </c>
+      <c r="H2015" t="inlineStr"/>
+      <c r="I2015" t="inlineStr"/>
       <c r="J2015" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2016">
       <c r="A2016" t="inlineStr">
         <is>
-          <t>€250 million</t>
+          <t>€4.2 billion</t>
         </is>
       </c>
       <c r="B2016" t="inlineStr"/>
       <c r="C2016" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2016" t="inlineStr">
         <is>
@@ -66572,19 +66570,19 @@
         </is>
       </c>
       <c r="E2016" t="n">
-        <v>250</v>
+        <v>4.2</v>
       </c>
       <c r="F2016" t="n">
-        <v>250000000</v>
+        <v>4200000000</v>
       </c>
       <c r="G2016" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="H2016" t="n">
-        <v>250000000</v>
+        <v>4200000000</v>
       </c>
       <c r="I2016" t="n">
-        <v>274487500</v>
+        <v>4611390000</v>
       </c>
       <c r="J2016" t="n">
         <v>2024</v>
@@ -66593,12 +66591,12 @@
     <row r="2017">
       <c r="A2017" t="inlineStr">
         <is>
-          <t>€250 million</t>
+          <t>€4.2 billion</t>
         </is>
       </c>
       <c r="B2017" t="inlineStr"/>
       <c r="C2017" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2017" t="inlineStr">
         <is>
@@ -66606,19 +66604,19 @@
         </is>
       </c>
       <c r="E2017" t="n">
-        <v>250</v>
+        <v>4.2</v>
       </c>
       <c r="F2017" t="n">
-        <v>250000000</v>
+        <v>4200000000</v>
       </c>
       <c r="G2017" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="H2017" t="n">
-        <v>250000000</v>
+        <v>4200000000</v>
       </c>
       <c r="I2017" t="n">
-        <v>274487500</v>
+        <v>4611390000</v>
       </c>
       <c r="J2017" t="n">
         <v>2024</v>
@@ -66627,12 +66625,12 @@
     <row r="2018">
       <c r="A2018" t="inlineStr">
         <is>
-          <t>€265m ($284m)</t>
+          <t>€4.2 billion</t>
         </is>
       </c>
       <c r="B2018" t="inlineStr"/>
       <c r="C2018" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2018" t="inlineStr">
         <is>
@@ -66640,19 +66638,19 @@
         </is>
       </c>
       <c r="E2018" t="n">
-        <v>265</v>
+        <v>4.2</v>
       </c>
       <c r="F2018" t="n">
-        <v>265000000</v>
+        <v>4200000000</v>
       </c>
       <c r="G2018" s="2" t="n">
-        <v>45444</v>
+        <v>45292</v>
       </c>
       <c r="H2018" t="n">
-        <v>265000000</v>
+        <v>4200000000</v>
       </c>
       <c r="I2018" t="n">
-        <v>287489666.6666667</v>
+        <v>4611390000</v>
       </c>
       <c r="J2018" t="n">
         <v>2024</v>
@@ -66661,7 +66659,7 @@
     <row r="2019">
       <c r="A2019" t="inlineStr">
         <is>
-          <t>$150m</t>
+          <t>€300 million</t>
         </is>
       </c>
       <c r="B2019" t="inlineStr"/>
@@ -66670,23 +66668,23 @@
       </c>
       <c r="D2019" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E2019" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F2019" t="n">
-        <v>150000000</v>
+        <v>300000000</v>
       </c>
       <c r="G2019" s="2" t="n">
-        <v>45383</v>
+        <v>45292</v>
       </c>
       <c r="H2019" t="n">
-        <v>139387068.5970227</v>
+        <v>300000000</v>
       </c>
       <c r="I2019" t="n">
-        <v>150000000</v>
+        <v>329385000</v>
       </c>
       <c r="J2019" t="n">
         <v>2024</v>
@@ -66695,7 +66693,7 @@
     <row r="2020">
       <c r="A2020" t="inlineStr">
         <is>
-          <t>$150m</t>
+          <t>€300 million</t>
         </is>
       </c>
       <c r="B2020" t="inlineStr"/>
@@ -66704,56 +66702,92 @@
       </c>
       <c r="D2020" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E2020" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F2020" t="n">
-        <v>150000000</v>
+        <v>300000000</v>
       </c>
       <c r="G2020" s="2" t="n">
-        <v>45383</v>
+        <v>45292</v>
       </c>
       <c r="H2020" t="n">
-        <v>139387068.5970227</v>
+        <v>300000000</v>
       </c>
       <c r="I2020" t="n">
-        <v>150000000</v>
+        <v>329385000</v>
       </c>
       <c r="J2020" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="2021">
-      <c r="A2021" t="inlineStr"/>
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>€300 million</t>
+        </is>
+      </c>
       <c r="B2021" t="inlineStr"/>
-      <c r="C2021" t="inlineStr"/>
-      <c r="D2021" t="inlineStr"/>
-      <c r="E2021" t="inlineStr"/>
-      <c r="F2021" t="inlineStr"/>
+      <c r="C2021" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2021" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2021" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2021" t="n">
+        <v>300000000</v>
+      </c>
       <c r="G2021" s="2" t="n">
-        <v>45474</v>
-      </c>
-      <c r="H2021" t="inlineStr"/>
-      <c r="I2021" t="inlineStr"/>
+        <v>45292</v>
+      </c>
+      <c r="H2021" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="I2021" t="n">
+        <v>329385000</v>
+      </c>
       <c r="J2021" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="2022">
-      <c r="A2022" t="inlineStr"/>
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>€250 million</t>
+        </is>
+      </c>
       <c r="B2022" t="inlineStr"/>
-      <c r="C2022" t="inlineStr"/>
-      <c r="D2022" t="inlineStr"/>
-      <c r="E2022" t="inlineStr"/>
-      <c r="F2022" t="inlineStr"/>
+      <c r="C2022" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2022" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2022" t="n">
+        <v>250</v>
+      </c>
+      <c r="F2022" t="n">
+        <v>250000000</v>
+      </c>
       <c r="G2022" s="2" t="n">
-        <v>45474</v>
-      </c>
-      <c r="H2022" t="inlineStr"/>
-      <c r="I2022" t="inlineStr"/>
+        <v>45292</v>
+      </c>
+      <c r="H2022" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="I2022" t="n">
+        <v>274487500</v>
+      </c>
       <c r="J2022" t="n">
         <v>2024</v>
       </c>
@@ -66761,7 +66795,7 @@
     <row r="2023">
       <c r="A2023" t="inlineStr">
         <is>
-          <t>€55 million</t>
+          <t>€250 million</t>
         </is>
       </c>
       <c r="B2023" t="inlineStr"/>
@@ -66774,269 +66808,201 @@
         </is>
       </c>
       <c r="E2023" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="F2023" t="n">
-        <v>55000000</v>
+        <v>250000000</v>
       </c>
       <c r="G2023" s="2" t="n">
-        <v>44958</v>
+        <v>45292</v>
       </c>
       <c r="H2023" t="n">
-        <v>55000000</v>
+        <v>250000000</v>
       </c>
       <c r="I2023" t="n">
-        <v>59916999.99999999</v>
+        <v>274487500</v>
       </c>
       <c r="J2023" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2024">
       <c r="A2024" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>€250 million</t>
         </is>
       </c>
       <c r="B2024" t="inlineStr"/>
       <c r="C2024" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2024" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2024" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F2024" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+      <c r="E2024" t="n">
+        <v>250</v>
+      </c>
+      <c r="F2024" t="n">
+        <v>250000000</v>
       </c>
       <c r="G2024" s="2" t="n">
-        <v>44287</v>
-      </c>
-      <c r="H2024" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I2024" t="inlineStr">
-        <is>
-          <t>[1174600000.0, 1761900000.0000002]</t>
-        </is>
+        <v>45292</v>
+      </c>
+      <c r="H2024" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="I2024" t="n">
+        <v>274487500</v>
       </c>
       <c r="J2024" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2025">
       <c r="A2025" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>€265m ($284m)</t>
         </is>
       </c>
       <c r="B2025" t="inlineStr"/>
       <c r="C2025" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2025" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2025" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F2025" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+      <c r="E2025" t="n">
+        <v>265</v>
+      </c>
+      <c r="F2025" t="n">
+        <v>265000000</v>
       </c>
       <c r="G2025" s="2" t="n">
-        <v>44287</v>
-      </c>
-      <c r="H2025" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I2025" t="inlineStr">
-        <is>
-          <t>[1174600000.0, 1761900000.0000002]</t>
-        </is>
+        <v>45444</v>
+      </c>
+      <c r="H2025" t="n">
+        <v>265000000</v>
+      </c>
+      <c r="I2025" t="n">
+        <v>287489666.6666667</v>
       </c>
       <c r="J2025" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2026">
       <c r="A2026" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>$150m</t>
         </is>
       </c>
       <c r="B2026" t="inlineStr"/>
       <c r="C2026" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2026" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2026" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F2026" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E2026" t="n">
+        <v>150</v>
+      </c>
+      <c r="F2026" t="n">
+        <v>150000000</v>
       </c>
       <c r="G2026" s="2" t="n">
-        <v>44287</v>
-      </c>
-      <c r="H2026" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I2026" t="inlineStr">
-        <is>
-          <t>[1174600000.0, 1761900000.0000002]</t>
-        </is>
+        <v>45383</v>
+      </c>
+      <c r="H2026" t="n">
+        <v>139387068.5970227</v>
+      </c>
+      <c r="I2026" t="n">
+        <v>150000000</v>
       </c>
       <c r="J2026" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2027">
       <c r="A2027" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>$150m</t>
         </is>
       </c>
       <c r="B2027" t="inlineStr"/>
       <c r="C2027" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2027" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2027" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F2027" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E2027" t="n">
+        <v>150</v>
+      </c>
+      <c r="F2027" t="n">
+        <v>150000000</v>
       </c>
       <c r="G2027" s="2" t="n">
-        <v>44287</v>
-      </c>
-      <c r="H2027" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I2027" t="inlineStr">
-        <is>
-          <t>[1174600000.0, 1761900000.0000002]</t>
-        </is>
+        <v>45383</v>
+      </c>
+      <c r="H2027" t="n">
+        <v>139387068.5970227</v>
+      </c>
+      <c r="I2027" t="n">
+        <v>150000000</v>
       </c>
       <c r="J2027" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2028">
-      <c r="A2028" t="inlineStr">
-        <is>
-          <t>€2.5 billion</t>
-        </is>
-      </c>
+      <c r="A2028" t="inlineStr"/>
       <c r="B2028" t="inlineStr"/>
-      <c r="C2028" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D2028" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2028" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F2028" t="n">
-        <v>2500000000</v>
-      </c>
+      <c r="C2028" t="inlineStr"/>
+      <c r="D2028" t="inlineStr"/>
+      <c r="E2028" t="inlineStr"/>
+      <c r="F2028" t="inlineStr"/>
       <c r="G2028" s="2" t="n">
-        <v>45139</v>
-      </c>
-      <c r="H2028" t="n">
-        <v>2500000000</v>
-      </c>
-      <c r="I2028" t="n">
-        <v>2742500000</v>
-      </c>
+        <v>45474</v>
+      </c>
+      <c r="H2028" t="inlineStr"/>
+      <c r="I2028" t="inlineStr"/>
       <c r="J2028" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2029">
-      <c r="A2029" t="inlineStr">
-        <is>
-          <t>€2.5 billion</t>
-        </is>
-      </c>
+      <c r="A2029" t="inlineStr"/>
       <c r="B2029" t="inlineStr"/>
-      <c r="C2029" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D2029" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2029" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F2029" t="n">
-        <v>2500000000</v>
-      </c>
+      <c r="C2029" t="inlineStr"/>
+      <c r="D2029" t="inlineStr"/>
+      <c r="E2029" t="inlineStr"/>
+      <c r="F2029" t="inlineStr"/>
       <c r="G2029" s="2" t="n">
-        <v>45139</v>
-      </c>
-      <c r="H2029" t="n">
-        <v>2500000000</v>
-      </c>
-      <c r="I2029" t="n">
-        <v>2742500000</v>
-      </c>
+        <v>45474</v>
+      </c>
+      <c r="H2029" t="inlineStr"/>
+      <c r="I2029" t="inlineStr"/>
       <c r="J2029" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2030">
       <c r="A2030" t="inlineStr">
         <is>
-          <t>€2.5 billion</t>
+          <t>€55 million</t>
         </is>
       </c>
       <c r="B2030" t="inlineStr"/>
       <c r="C2030" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2030" t="inlineStr">
         <is>
@@ -67044,19 +67010,19 @@
         </is>
       </c>
       <c r="E2030" t="n">
-        <v>2.5</v>
+        <v>55</v>
       </c>
       <c r="F2030" t="n">
-        <v>2500000000</v>
+        <v>55000000</v>
       </c>
       <c r="G2030" s="2" t="n">
-        <v>45139</v>
+        <v>44958</v>
       </c>
       <c r="H2030" t="n">
-        <v>2500000000</v>
+        <v>55000000</v>
       </c>
       <c r="I2030" t="n">
-        <v>2742500000</v>
+        <v>59916999.99999999</v>
       </c>
       <c r="J2030" t="n">
         <v>2023</v>
@@ -67065,7 +67031,7 @@
     <row r="2031">
       <c r="A2031" t="inlineStr">
         <is>
-          <t>€2.5 billion</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B2031" t="inlineStr"/>
@@ -67077,29 +67043,37 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2031" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F2031" t="n">
-        <v>2500000000</v>
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F2031" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G2031" s="2" t="n">
-        <v>45139</v>
-      </c>
-      <c r="H2031" t="n">
-        <v>2500000000</v>
-      </c>
-      <c r="I2031" t="n">
-        <v>2742500000</v>
+        <v>44287</v>
+      </c>
+      <c r="H2031" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I2031" t="inlineStr">
+        <is>
+          <t>[1174600000.0, 1761900000.0000002]</t>
+        </is>
       </c>
       <c r="J2031" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2032">
       <c r="A2032" t="inlineStr">
         <is>
-          <t>€1.3 billion</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B2032" t="inlineStr"/>
@@ -67111,29 +67085,37 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2032" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F2032" t="n">
-        <v>1300000000</v>
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F2032" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G2032" s="2" t="n">
-        <v>45323</v>
-      </c>
-      <c r="H2032" t="n">
-        <v>1300000000</v>
-      </c>
-      <c r="I2032" t="n">
-        <v>1405820000</v>
+        <v>44287</v>
+      </c>
+      <c r="H2032" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I2032" t="inlineStr">
+        <is>
+          <t>[1174600000.0, 1761900000.0000002]</t>
+        </is>
       </c>
       <c r="J2032" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2033">
       <c r="A2033" t="inlineStr">
         <is>
-          <t>€1.3 billion</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B2033" t="inlineStr"/>
@@ -67145,29 +67127,37 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2033" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F2033" t="n">
-        <v>1300000000</v>
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F2033" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G2033" s="2" t="n">
-        <v>45323</v>
-      </c>
-      <c r="H2033" t="n">
-        <v>1300000000</v>
-      </c>
-      <c r="I2033" t="n">
-        <v>1405820000</v>
+        <v>44287</v>
+      </c>
+      <c r="H2033" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I2033" t="inlineStr">
+        <is>
+          <t>[1174600000.0, 1761900000.0000002]</t>
+        </is>
       </c>
       <c r="J2033" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2034">
       <c r="A2034" t="inlineStr">
         <is>
-          <t>€1.3 billion</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B2034" t="inlineStr"/>
@@ -67179,29 +67169,37 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2034" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F2034" t="n">
-        <v>1300000000</v>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F2034" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G2034" s="2" t="n">
-        <v>45323</v>
-      </c>
-      <c r="H2034" t="n">
-        <v>1300000000</v>
-      </c>
-      <c r="I2034" t="n">
-        <v>1405820000</v>
+        <v>44287</v>
+      </c>
+      <c r="H2034" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I2034" t="inlineStr">
+        <is>
+          <t>[1174600000.0, 1761900000.0000002]</t>
+        </is>
       </c>
       <c r="J2034" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2035">
       <c r="A2035" t="inlineStr">
         <is>
-          <t>€1.3 billion</t>
+          <t>€2.5 billion</t>
         </is>
       </c>
       <c r="B2035" t="inlineStr"/>
@@ -67214,28 +67212,28 @@
         </is>
       </c>
       <c r="E2035" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="F2035" t="n">
-        <v>1300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="G2035" s="2" t="n">
-        <v>45323</v>
+        <v>45139</v>
       </c>
       <c r="H2035" t="n">
-        <v>1300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="I2035" t="n">
-        <v>1405820000</v>
+        <v>2742500000</v>
       </c>
       <c r="J2035" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2036">
       <c r="A2036" t="inlineStr">
         <is>
-          <t>€1.3 billion</t>
+          <t>€2.5 billion</t>
         </is>
       </c>
       <c r="B2036" t="inlineStr"/>
@@ -67248,28 +67246,28 @@
         </is>
       </c>
       <c r="E2036" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="F2036" t="n">
-        <v>1300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="G2036" s="2" t="n">
-        <v>45323</v>
+        <v>45139</v>
       </c>
       <c r="H2036" t="n">
-        <v>1300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="I2036" t="n">
-        <v>1405820000</v>
+        <v>2742500000</v>
       </c>
       <c r="J2036" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2037">
       <c r="A2037" t="inlineStr">
         <is>
-          <t>€1.3 billion</t>
+          <t>€2.5 billion</t>
         </is>
       </c>
       <c r="B2037" t="inlineStr"/>
@@ -67282,28 +67280,28 @@
         </is>
       </c>
       <c r="E2037" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="F2037" t="n">
-        <v>1300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="G2037" s="2" t="n">
-        <v>45323</v>
+        <v>45139</v>
       </c>
       <c r="H2037" t="n">
-        <v>1300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="I2037" t="n">
-        <v>1405820000</v>
+        <v>2742500000</v>
       </c>
       <c r="J2037" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2038">
       <c r="A2038" t="inlineStr">
         <is>
-          <t>€1.3 billion</t>
+          <t>€2.5 billion</t>
         </is>
       </c>
       <c r="B2038" t="inlineStr"/>
@@ -67316,22 +67314,22 @@
         </is>
       </c>
       <c r="E2038" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="F2038" t="n">
-        <v>1300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="G2038" s="2" t="n">
-        <v>45323</v>
+        <v>45139</v>
       </c>
       <c r="H2038" t="n">
-        <v>1300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="I2038" t="n">
-        <v>1405820000</v>
+        <v>2742500000</v>
       </c>
       <c r="J2038" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2039">
@@ -67371,12 +67369,12 @@
     <row r="2040">
       <c r="A2040" t="inlineStr">
         <is>
-          <t>EUR € 50 million</t>
+          <t>€1.3 billion</t>
         </is>
       </c>
       <c r="B2040" t="inlineStr"/>
       <c r="C2040" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2040" t="inlineStr">
         <is>
@@ -67384,33 +67382,33 @@
         </is>
       </c>
       <c r="E2040" t="n">
-        <v>50</v>
+        <v>1.3</v>
       </c>
       <c r="F2040" t="n">
-        <v>50000000</v>
+        <v>1300000000</v>
       </c>
       <c r="G2040" s="2" t="n">
-        <v>44256</v>
+        <v>45323</v>
       </c>
       <c r="H2040" t="n">
-        <v>50000000</v>
+        <v>1300000000</v>
       </c>
       <c r="I2040" t="n">
-        <v>60265000</v>
+        <v>1405820000</v>
       </c>
       <c r="J2040" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2041">
       <c r="A2041" t="inlineStr">
         <is>
-          <t>EUR € 50 million</t>
+          <t>€1.3 billion</t>
         </is>
       </c>
       <c r="B2041" t="inlineStr"/>
       <c r="C2041" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2041" t="inlineStr">
         <is>
@@ -67418,33 +67416,33 @@
         </is>
       </c>
       <c r="E2041" t="n">
-        <v>50</v>
+        <v>1.3</v>
       </c>
       <c r="F2041" t="n">
-        <v>50000000</v>
+        <v>1300000000</v>
       </c>
       <c r="G2041" s="2" t="n">
-        <v>44256</v>
+        <v>45323</v>
       </c>
       <c r="H2041" t="n">
-        <v>50000000</v>
+        <v>1300000000</v>
       </c>
       <c r="I2041" t="n">
-        <v>60265000</v>
+        <v>1405820000</v>
       </c>
       <c r="J2041" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2042">
       <c r="A2042" t="inlineStr">
         <is>
-          <t>€8 million ($8.7m)</t>
+          <t>€1.3 billion</t>
         </is>
       </c>
       <c r="B2042" t="inlineStr"/>
       <c r="C2042" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2042" t="inlineStr">
         <is>
@@ -67452,19 +67450,19 @@
         </is>
       </c>
       <c r="E2042" t="n">
-        <v>8</v>
+        <v>1.3</v>
       </c>
       <c r="F2042" t="n">
-        <v>8000000</v>
+        <v>1300000000</v>
       </c>
       <c r="G2042" s="2" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="H2042" t="n">
-        <v>8000000</v>
+        <v>1300000000</v>
       </c>
       <c r="I2042" t="n">
-        <v>8783600</v>
+        <v>1405820000</v>
       </c>
       <c r="J2042" t="n">
         <v>2024</v>
@@ -67473,7 +67471,7 @@
     <row r="2043">
       <c r="A2043" t="inlineStr">
         <is>
-          <t>EUR 4.5 billion</t>
+          <t>€1.3 billion</t>
         </is>
       </c>
       <c r="B2043" t="inlineStr"/>
@@ -67486,19 +67484,19 @@
         </is>
       </c>
       <c r="E2043" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="F2043" t="n">
-        <v>4500000000</v>
+        <v>1300000000</v>
       </c>
       <c r="G2043" s="2" t="n">
-        <v>45383</v>
+        <v>45323</v>
       </c>
       <c r="H2043" t="n">
-        <v>4500000000</v>
+        <v>1300000000</v>
       </c>
       <c r="I2043" t="n">
-        <v>4842630000</v>
+        <v>1405820000</v>
       </c>
       <c r="J2043" t="n">
         <v>2024</v>
@@ -67507,7 +67505,7 @@
     <row r="2044">
       <c r="A2044" t="inlineStr">
         <is>
-          <t>EUR 2.6 billion</t>
+          <t>€1.3 billion</t>
         </is>
       </c>
       <c r="B2044" t="inlineStr"/>
@@ -67520,19 +67518,19 @@
         </is>
       </c>
       <c r="E2044" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="F2044" t="n">
-        <v>2600000000</v>
+        <v>1300000000</v>
       </c>
       <c r="G2044" s="2" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="H2044" t="n">
-        <v>2600000000</v>
+        <v>1300000000</v>
       </c>
       <c r="I2044" t="n">
-        <v>2854670000</v>
+        <v>1405820000</v>
       </c>
       <c r="J2044" t="n">
         <v>2024</v>
@@ -67541,7 +67539,7 @@
     <row r="2045">
       <c r="A2045" t="inlineStr">
         <is>
-          <t>EUR 2.6 billion</t>
+          <t>€1.3 billion</t>
         </is>
       </c>
       <c r="B2045" t="inlineStr"/>
@@ -67554,19 +67552,19 @@
         </is>
       </c>
       <c r="E2045" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="F2045" t="n">
-        <v>2600000000</v>
+        <v>1300000000</v>
       </c>
       <c r="G2045" s="2" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="H2045" t="n">
-        <v>2600000000</v>
+        <v>1300000000</v>
       </c>
       <c r="I2045" t="n">
-        <v>2854670000</v>
+        <v>1405820000</v>
       </c>
       <c r="J2045" t="n">
         <v>2024</v>
@@ -67575,12 +67573,12 @@
     <row r="2046">
       <c r="A2046" t="inlineStr">
         <is>
-          <t>three million euros</t>
+          <t>€1.3 billion</t>
         </is>
       </c>
       <c r="B2046" t="inlineStr"/>
       <c r="C2046" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2046" t="inlineStr">
         <is>
@@ -67588,33 +67586,33 @@
         </is>
       </c>
       <c r="E2046" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="F2046" t="n">
-        <v>3000000</v>
+        <v>1300000000</v>
       </c>
       <c r="G2046" s="2" t="n">
-        <v>45139</v>
+        <v>45323</v>
       </c>
       <c r="H2046" t="n">
-        <v>3000000</v>
+        <v>1300000000</v>
       </c>
       <c r="I2046" t="n">
-        <v>3291000</v>
+        <v>1405820000</v>
       </c>
       <c r="J2046" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2047">
       <c r="A2047" t="inlineStr">
         <is>
-          <t>EUR 1.5 billion</t>
+          <t>EUR € 50 million</t>
         </is>
       </c>
       <c r="B2047" t="inlineStr"/>
       <c r="C2047" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2047" t="inlineStr">
         <is>
@@ -67622,33 +67620,33 @@
         </is>
       </c>
       <c r="E2047" t="n">
-        <v>1.5</v>
+        <v>50</v>
       </c>
       <c r="F2047" t="n">
-        <v>1500000000</v>
+        <v>50000000</v>
       </c>
       <c r="G2047" s="2" t="n">
-        <v>44986</v>
+        <v>44256</v>
       </c>
       <c r="H2047" t="n">
-        <v>1500000000</v>
+        <v>50000000</v>
       </c>
       <c r="I2047" t="n">
-        <v>1602600000</v>
+        <v>60265000</v>
       </c>
       <c r="J2047" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2048">
       <c r="A2048" t="inlineStr">
         <is>
-          <t>EUR 1.5 billion</t>
+          <t>EUR € 50 million</t>
         </is>
       </c>
       <c r="B2048" t="inlineStr"/>
       <c r="C2048" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2048" t="inlineStr">
         <is>
@@ -67656,22 +67654,462 @@
         </is>
       </c>
       <c r="E2048" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2048" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G2048" s="2" t="n">
+        <v>44256</v>
+      </c>
+      <c r="H2048" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="I2048" t="n">
+        <v>60265000</v>
+      </c>
+      <c r="J2048" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>€8 million ($8.7m)</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr"/>
+      <c r="C2049" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2049" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2049" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2049" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="G2049" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2049" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I2049" t="n">
+        <v>8783600</v>
+      </c>
+      <c r="J2049" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>EUR 4.5 billion</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr"/>
+      <c r="C2050" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2050" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2050" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F2050" t="n">
+        <v>4500000000</v>
+      </c>
+      <c r="G2050" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="H2050" t="n">
+        <v>4500000000</v>
+      </c>
+      <c r="I2050" t="n">
+        <v>4842630000</v>
+      </c>
+      <c r="J2050" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>EUR 2.6 billion</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr"/>
+      <c r="C2051" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2051" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2051" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F2051" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="G2051" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2051" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="I2051" t="n">
+        <v>2854670000</v>
+      </c>
+      <c r="J2051" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>EUR 2.6 billion</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr"/>
+      <c r="C2052" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2052" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2052" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F2052" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="G2052" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H2052" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="I2052" t="n">
+        <v>2854670000</v>
+      </c>
+      <c r="J2052" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>three million euros</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr"/>
+      <c r="C2053" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2053" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2053" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2053" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G2053" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="H2053" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I2053" t="n">
+        <v>3291000</v>
+      </c>
+      <c r="J2053" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>EUR 1.5 billion</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr"/>
+      <c r="C2054" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2054" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2054" t="n">
         <v>1.5</v>
       </c>
-      <c r="F2048" t="n">
+      <c r="F2054" t="n">
         <v>1500000000</v>
       </c>
-      <c r="G2048" s="2" t="n">
+      <c r="G2054" s="2" t="n">
         <v>44986</v>
       </c>
-      <c r="H2048" t="n">
+      <c r="H2054" t="n">
         <v>1500000000</v>
       </c>
-      <c r="I2048" t="n">
+      <c r="I2054" t="n">
         <v>1602600000</v>
       </c>
-      <c r="J2048" t="n">
+      <c r="J2054" t="n">
         <v>2023</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>EUR 1.5 billion</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr"/>
+      <c r="C2055" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2055" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2055" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2055" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="G2055" s="2" t="n">
+        <v>44986</v>
+      </c>
+      <c r="H2055" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="I2055" t="n">
+        <v>1602600000</v>
+      </c>
+      <c r="J2055" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr"/>
+      <c r="B2056" t="inlineStr"/>
+      <c r="C2056" t="inlineStr"/>
+      <c r="D2056" t="inlineStr"/>
+      <c r="E2056" t="inlineStr"/>
+      <c r="F2056" t="inlineStr"/>
+      <c r="G2056" s="2" t="n">
+        <v>44835</v>
+      </c>
+      <c r="H2056" t="inlineStr"/>
+      <c r="I2056" t="inlineStr"/>
+      <c r="J2056" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr"/>
+      <c r="B2057" t="inlineStr"/>
+      <c r="C2057" t="inlineStr"/>
+      <c r="D2057" t="inlineStr"/>
+      <c r="E2057" t="inlineStr"/>
+      <c r="F2057" t="inlineStr"/>
+      <c r="G2057" s="2" t="n">
+        <v>44835</v>
+      </c>
+      <c r="H2057" t="inlineStr"/>
+      <c r="I2057" t="inlineStr"/>
+      <c r="J2057" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>£186 million</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr"/>
+      <c r="C2058" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2058" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2058" t="n">
+        <v>186</v>
+      </c>
+      <c r="F2058" t="n">
+        <v>186000000</v>
+      </c>
+      <c r="G2058" s="2" t="n">
+        <v>44409</v>
+      </c>
+      <c r="H2058" t="n">
+        <v>217734005.5252931</v>
+      </c>
+      <c r="I2058" t="n">
+        <v>258834927.9682842</v>
+      </c>
+      <c r="J2058" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>£78 million</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr"/>
+      <c r="C2059" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2059" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2059" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="G2059" s="2" t="n">
+        <v>44409</v>
+      </c>
+      <c r="H2059" t="n">
+        <v>91307808.76867127</v>
+      </c>
+      <c r="I2059" t="n">
+        <v>108543679.4705708</v>
+      </c>
+      <c r="J2059" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>GBP 82 million (around EUR 96 million)</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr"/>
+      <c r="C2060" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2060" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2060" t="n">
+        <v>82</v>
+      </c>
+      <c r="F2060" t="n">
+        <v>82000000</v>
+      </c>
+      <c r="G2060" s="2" t="n">
+        <v>44470</v>
+      </c>
+      <c r="H2060" t="n">
+        <v>95735117.27551866</v>
+      </c>
+      <c r="I2060" t="n">
+        <v>111052736.0396016</v>
+      </c>
+      <c r="J2060" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>€400 million</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr"/>
+      <c r="C2061" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2061" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2061" t="n">
+        <v>400</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="G2061" s="2" t="n">
+        <v>40483</v>
+      </c>
+      <c r="H2061" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="I2061" t="n">
+        <v>557040000</v>
+      </c>
+      <c r="J2061" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>€400 million</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr"/>
+      <c r="C2062" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2062" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2062" t="n">
+        <v>400</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="G2062" s="2" t="n">
+        <v>40483</v>
+      </c>
+      <c r="H2062" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="I2062" t="n">
+        <v>557040000</v>
+      </c>
+      <c r="J2062" t="n">
+        <v>2010</v>
       </c>
     </row>
   </sheetData>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2062"/>
+  <dimension ref="A1:J2065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67927,25 +67927,43 @@
       </c>
     </row>
     <row r="2057">
-      <c r="A2057" t="inlineStr"/>
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>£186 million</t>
+        </is>
+      </c>
       <c r="B2057" t="inlineStr"/>
-      <c r="C2057" t="inlineStr"/>
-      <c r="D2057" t="inlineStr"/>
-      <c r="E2057" t="inlineStr"/>
-      <c r="F2057" t="inlineStr"/>
+      <c r="C2057" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2057" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2057" t="n">
+        <v>186</v>
+      </c>
+      <c r="F2057" t="n">
+        <v>186000000</v>
+      </c>
       <c r="G2057" s="2" t="n">
-        <v>44835</v>
-      </c>
-      <c r="H2057" t="inlineStr"/>
-      <c r="I2057" t="inlineStr"/>
+        <v>44409</v>
+      </c>
+      <c r="H2057" t="n">
+        <v>217734005.5252931</v>
+      </c>
+      <c r="I2057" t="n">
+        <v>258834927.9682842</v>
+      </c>
       <c r="J2057" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2058">
       <c r="A2058" t="inlineStr">
         <is>
-          <t>£186 million</t>
+          <t>£78 million</t>
         </is>
       </c>
       <c r="B2058" t="inlineStr"/>
@@ -67958,19 +67976,19 @@
         </is>
       </c>
       <c r="E2058" t="n">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="F2058" t="n">
-        <v>186000000</v>
+        <v>78000000</v>
       </c>
       <c r="G2058" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="H2058" t="n">
-        <v>217734005.5252931</v>
+        <v>91307808.76867127</v>
       </c>
       <c r="I2058" t="n">
-        <v>258834927.9682842</v>
+        <v>108543679.4705708</v>
       </c>
       <c r="J2058" t="n">
         <v>2021</v>
@@ -67979,7 +67997,7 @@
     <row r="2059">
       <c r="A2059" t="inlineStr">
         <is>
-          <t>£78 million</t>
+          <t>GBP 82 million (around EUR 96 million)</t>
         </is>
       </c>
       <c r="B2059" t="inlineStr"/>
@@ -67992,19 +68010,19 @@
         </is>
       </c>
       <c r="E2059" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F2059" t="n">
-        <v>78000000</v>
+        <v>82000000</v>
       </c>
       <c r="G2059" s="2" t="n">
-        <v>44409</v>
+        <v>44470</v>
       </c>
       <c r="H2059" t="n">
-        <v>91307808.76867127</v>
+        <v>95735117.27551866</v>
       </c>
       <c r="I2059" t="n">
-        <v>108543679.4705708</v>
+        <v>111052736.0396016</v>
       </c>
       <c r="J2059" t="n">
         <v>2021</v>
@@ -68013,7 +68031,7 @@
     <row r="2060">
       <c r="A2060" t="inlineStr">
         <is>
-          <t>GBP 82 million (around EUR 96 million)</t>
+          <t>€400 million</t>
         </is>
       </c>
       <c r="B2060" t="inlineStr"/>
@@ -68022,26 +68040,26 @@
       </c>
       <c r="D2060" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E2060" t="n">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="F2060" t="n">
-        <v>82000000</v>
+        <v>400000000</v>
       </c>
       <c r="G2060" s="2" t="n">
-        <v>44470</v>
+        <v>40483</v>
       </c>
       <c r="H2060" t="n">
-        <v>95735117.27551866</v>
+        <v>400000000</v>
       </c>
       <c r="I2060" t="n">
-        <v>111052736.0396016</v>
+        <v>557040000</v>
       </c>
       <c r="J2060" t="n">
-        <v>2021</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="2061">
@@ -68081,35 +68099,137 @@
     <row r="2062">
       <c r="A2062" t="inlineStr">
         <is>
-          <t>€400 million</t>
+          <t>323.6 billion won</t>
         </is>
       </c>
       <c r="B2062" t="inlineStr"/>
       <c r="C2062" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2062" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="E2062" t="n">
-        <v>400</v>
+        <v>323.6</v>
       </c>
       <c r="F2062" t="n">
-        <v>400000000</v>
+        <v>323600000000</v>
       </c>
       <c r="G2062" s="2" t="n">
-        <v>40483</v>
+        <v>45809</v>
       </c>
       <c r="H2062" t="n">
-        <v>400000000</v>
+        <v>206224548.5386055</v>
       </c>
       <c r="I2062" t="n">
-        <v>557040000</v>
+        <v>234937879.8467973</v>
       </c>
       <c r="J2062" t="n">
-        <v>2010</v>
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>500 billion won</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr"/>
+      <c r="C2063" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2063" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="E2063" t="n">
+        <v>500</v>
+      </c>
+      <c r="F2063" t="n">
+        <v>500000000000</v>
+      </c>
+      <c r="G2063" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="H2063" t="n">
+        <v>353716856.7305244</v>
+      </c>
+      <c r="I2063" t="n">
+        <v>388027391.8333852</v>
+      </c>
+      <c r="J2063" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>500 billion won</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr"/>
+      <c r="C2064" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2064" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="E2064" t="n">
+        <v>500</v>
+      </c>
+      <c r="F2064" t="n">
+        <v>500000000000</v>
+      </c>
+      <c r="G2064" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="H2064" t="n">
+        <v>353716856.7305244</v>
+      </c>
+      <c r="I2064" t="n">
+        <v>388027391.8333852</v>
+      </c>
+      <c r="J2064" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>500 billion won</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr"/>
+      <c r="C2065" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2065" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="E2065" t="n">
+        <v>500</v>
+      </c>
+      <c r="F2065" t="n">
+        <v>500000000000</v>
+      </c>
+      <c r="G2065" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="H2065" t="n">
+        <v>353716856.7305244</v>
+      </c>
+      <c r="I2065" t="n">
+        <v>388027391.8333852</v>
+      </c>
+      <c r="J2065" t="n">
+        <v>2023</v>
       </c>
     </row>
   </sheetData>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2357"/>
+  <dimension ref="A1:J2356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76397,7 +76397,7 @@
     <row r="2319">
       <c r="A2319" t="inlineStr">
         <is>
-          <t>EUR 200 mn</t>
+          <t>€200 million</t>
         </is>
       </c>
       <c r="B2319" t="inlineStr"/>
@@ -76431,12 +76431,12 @@
     <row r="2320">
       <c r="A2320" t="inlineStr">
         <is>
-          <t>€200 million</t>
+          <t>€7 billion</t>
         </is>
       </c>
       <c r="B2320" t="inlineStr"/>
       <c r="C2320" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2320" t="inlineStr">
         <is>
@@ -76444,22 +76444,22 @@
         </is>
       </c>
       <c r="E2320" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="F2320" t="n">
-        <v>200000000</v>
+        <v>7000000000</v>
       </c>
       <c r="G2320" s="2" t="n">
-        <v>45901</v>
+        <v>45444</v>
       </c>
       <c r="H2320" t="n">
-        <v>200000000</v>
+        <v>7000000000</v>
       </c>
       <c r="I2320" t="n">
-        <v>233080000</v>
+        <v>7594066666.666667</v>
       </c>
       <c r="J2320" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2321">
@@ -76567,12 +76567,12 @@
     <row r="2324">
       <c r="A2324" t="inlineStr">
         <is>
-          <t>€7 billion</t>
+          <t>EUR 1941 million</t>
         </is>
       </c>
       <c r="B2324" t="inlineStr"/>
       <c r="C2324" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2324" t="inlineStr">
         <is>
@@ -76580,62 +76580,62 @@
         </is>
       </c>
       <c r="E2324" t="n">
-        <v>7</v>
+        <v>1941</v>
       </c>
       <c r="F2324" t="n">
-        <v>7000000000</v>
+        <v>1941000000</v>
       </c>
       <c r="G2324" s="2" t="n">
-        <v>45444</v>
+        <v>44866</v>
       </c>
       <c r="H2324" t="n">
-        <v>7000000000</v>
+        <v>1941000000</v>
       </c>
       <c r="I2324" t="n">
-        <v>7594066666.666667</v>
+        <v>1930712700</v>
       </c>
       <c r="J2324" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2325">
       <c r="A2325" t="inlineStr">
         <is>
-          <t>EUR 1941 million</t>
+          <t>1 billion pound ($1.33 billion)</t>
         </is>
       </c>
       <c r="B2325" t="inlineStr"/>
       <c r="C2325" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2325" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E2325" t="n">
-        <v>1941</v>
+        <v>1</v>
       </c>
       <c r="F2325" t="n">
-        <v>1941000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G2325" s="2" t="n">
-        <v>44866</v>
+        <v>45778</v>
       </c>
       <c r="H2325" t="n">
-        <v>1941000000</v>
+        <v>1172951733.036186</v>
       </c>
       <c r="I2325" t="n">
-        <v>1930712700</v>
+        <v>1332238578.3825</v>
       </c>
       <c r="J2325" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2326">
       <c r="A2326" t="inlineStr">
         <is>
-          <t>1 billion pound ($1.33 billion)</t>
+          <t>£1bn</t>
         </is>
       </c>
       <c r="B2326" t="inlineStr"/>
@@ -76669,7 +76669,7 @@
     <row r="2327">
       <c r="A2327" t="inlineStr">
         <is>
-          <t>£1bn</t>
+          <t>NOK 1.5 billion (USD 134m/EUR 128m)</t>
         </is>
       </c>
       <c r="B2327" t="inlineStr"/>
@@ -76678,60 +76678,60 @@
       </c>
       <c r="D2327" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="E2327" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F2327" t="n">
-        <v>1000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="G2327" s="2" t="n">
-        <v>45778</v>
+        <v>45627</v>
       </c>
       <c r="H2327" t="n">
-        <v>1172951733.036186</v>
+        <v>128576939.0116719</v>
       </c>
       <c r="I2327" t="n">
-        <v>1332238578.3825</v>
+        <v>135331514.2077518</v>
       </c>
       <c r="J2327" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2328">
       <c r="A2328" t="inlineStr">
         <is>
-          <t>NOK 1.5 billion (USD 134m/EUR 128m)</t>
+          <t>700 million euros</t>
         </is>
       </c>
       <c r="B2328" t="inlineStr"/>
       <c r="C2328" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2328" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E2328" t="n">
-        <v>1.5</v>
+        <v>700</v>
       </c>
       <c r="F2328" t="n">
-        <v>1500000000</v>
+        <v>700000000</v>
       </c>
       <c r="G2328" s="2" t="n">
-        <v>45627</v>
+        <v>44713</v>
       </c>
       <c r="H2328" t="n">
-        <v>128576939.0116719</v>
+        <v>700000000</v>
       </c>
       <c r="I2328" t="n">
-        <v>135331514.2077518</v>
+        <v>749840000</v>
       </c>
       <c r="J2328" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2329">
@@ -76769,37 +76769,19 @@
       </c>
     </row>
     <row r="2330">
-      <c r="A2330" t="inlineStr">
-        <is>
-          <t>700 million euros</t>
-        </is>
-      </c>
+      <c r="A2330" t="inlineStr"/>
       <c r="B2330" t="inlineStr"/>
-      <c r="C2330" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D2330" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2330" t="n">
-        <v>700</v>
-      </c>
-      <c r="F2330" t="n">
-        <v>700000000</v>
-      </c>
+      <c r="C2330" t="inlineStr"/>
+      <c r="D2330" t="inlineStr"/>
+      <c r="E2330" t="inlineStr"/>
+      <c r="F2330" t="inlineStr"/>
       <c r="G2330" s="2" t="n">
-        <v>44713</v>
-      </c>
-      <c r="H2330" t="n">
-        <v>700000000</v>
-      </c>
-      <c r="I2330" t="n">
-        <v>749840000</v>
-      </c>
+        <v>45292</v>
+      </c>
+      <c r="H2330" t="inlineStr"/>
+      <c r="I2330" t="inlineStr"/>
       <c r="J2330" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2331">
@@ -76819,19 +76801,37 @@
       </c>
     </row>
     <row r="2332">
-      <c r="A2332" t="inlineStr"/>
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>EUR 1.5 billion</t>
+        </is>
+      </c>
       <c r="B2332" t="inlineStr"/>
-      <c r="C2332" t="inlineStr"/>
-      <c r="D2332" t="inlineStr"/>
-      <c r="E2332" t="inlineStr"/>
-      <c r="F2332" t="inlineStr"/>
+      <c r="C2332" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2332" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2332" t="n">
+        <v>1500000000</v>
+      </c>
       <c r="G2332" s="2" t="n">
-        <v>45292</v>
-      </c>
-      <c r="H2332" t="inlineStr"/>
-      <c r="I2332" t="inlineStr"/>
+        <v>44986</v>
+      </c>
+      <c r="H2332" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="I2332" t="n">
+        <v>1602600000</v>
+      </c>
       <c r="J2332" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2333">
@@ -76871,7 +76871,7 @@
     <row r="2334">
       <c r="A2334" t="inlineStr">
         <is>
-          <t>EUR 1.5 billion</t>
+          <t>€1 billion</t>
         </is>
       </c>
       <c r="B2334" t="inlineStr"/>
@@ -76884,19 +76884,19 @@
         </is>
       </c>
       <c r="E2334" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F2334" t="n">
-        <v>1500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G2334" s="2" t="n">
-        <v>44986</v>
+        <v>44958</v>
       </c>
       <c r="H2334" t="n">
-        <v>1500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I2334" t="n">
-        <v>1602600000</v>
+        <v>1089400000</v>
       </c>
       <c r="J2334" t="n">
         <v>2023</v>
@@ -76905,12 +76905,12 @@
     <row r="2335">
       <c r="A2335" t="inlineStr">
         <is>
-          <t>€1 billion</t>
+          <t>600 million euros</t>
         </is>
       </c>
       <c r="B2335" t="inlineStr"/>
       <c r="C2335" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2335" t="inlineStr">
         <is>
@@ -76918,19 +76918,19 @@
         </is>
       </c>
       <c r="E2335" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="F2335" t="n">
-        <v>1000000000</v>
+        <v>600000000</v>
       </c>
       <c r="G2335" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="H2335" t="n">
-        <v>1000000000</v>
+        <v>600000000</v>
       </c>
       <c r="I2335" t="n">
-        <v>1089400000</v>
+        <v>653640000</v>
       </c>
       <c r="J2335" t="n">
         <v>2023</v>
@@ -76939,7 +76939,7 @@
     <row r="2336">
       <c r="A2336" t="inlineStr">
         <is>
-          <t>600 million euros</t>
+          <t>€1.65 million</t>
         </is>
       </c>
       <c r="B2336" t="inlineStr"/>
@@ -76952,33 +76952,33 @@
         </is>
       </c>
       <c r="E2336" t="n">
-        <v>600</v>
+        <v>1.65</v>
       </c>
       <c r="F2336" t="n">
-        <v>600000000</v>
+        <v>1650000</v>
       </c>
       <c r="G2336" s="2" t="n">
-        <v>44958</v>
+        <v>45323</v>
       </c>
       <c r="H2336" t="n">
-        <v>600000000</v>
+        <v>1650000</v>
       </c>
       <c r="I2336" t="n">
-        <v>653640000</v>
+        <v>1784310</v>
       </c>
       <c r="J2336" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2337">
       <c r="A2337" t="inlineStr">
         <is>
-          <t>€1.65 million</t>
+          <t>€1.65 billion</t>
         </is>
       </c>
       <c r="B2337" t="inlineStr"/>
       <c r="C2337" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2337" t="inlineStr">
         <is>
@@ -76989,16 +76989,16 @@
         <v>1.65</v>
       </c>
       <c r="F2337" t="n">
-        <v>1650000</v>
+        <v>1650000000</v>
       </c>
       <c r="G2337" s="2" t="n">
-        <v>45323</v>
+        <v>45474</v>
       </c>
       <c r="H2337" t="n">
-        <v>1650000</v>
+        <v>1650000000</v>
       </c>
       <c r="I2337" t="n">
-        <v>1784310</v>
+        <v>1772925000</v>
       </c>
       <c r="J2337" t="n">
         <v>2024</v>
@@ -77041,7 +77041,7 @@
     <row r="2339">
       <c r="A2339" t="inlineStr">
         <is>
-          <t>€1.65 billion</t>
+          <t>over £1 billion</t>
         </is>
       </c>
       <c r="B2339" t="inlineStr"/>
@@ -77050,32 +77050,40 @@
       </c>
       <c r="D2339" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2339" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="F2339" t="n">
-        <v>1650000000</v>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2339" t="inlineStr">
+        <is>
+          <t>[1.0, None]</t>
+        </is>
+      </c>
+      <c r="F2339" t="inlineStr">
+        <is>
+          <t>[1000000000.0, None]</t>
+        </is>
       </c>
       <c r="G2339" s="2" t="n">
-        <v>45474</v>
-      </c>
-      <c r="H2339" t="n">
-        <v>1650000000</v>
-      </c>
-      <c r="I2339" t="n">
-        <v>1772925000</v>
+        <v>45108</v>
+      </c>
+      <c r="H2339" t="inlineStr">
+        <is>
+          <t>[1164433541.896319, None]</t>
+        </is>
+      </c>
+      <c r="I2339" t="inlineStr">
+        <is>
+          <t>[1266554363.5206263, None]</t>
+        </is>
       </c>
       <c r="J2339" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2340">
       <c r="A2340" t="inlineStr">
         <is>
-          <t>over £1 billion</t>
+          <t>€1 billion</t>
         </is>
       </c>
       <c r="B2340" t="inlineStr"/>
@@ -77084,34 +77092,26 @@
       </c>
       <c r="D2340" t="inlineStr">
         <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="E2340" t="inlineStr">
-        <is>
-          <t>[1.0, None]</t>
-        </is>
-      </c>
-      <c r="F2340" t="inlineStr">
-        <is>
-          <t>[1000000000.0, None]</t>
-        </is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2340" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2340" t="n">
+        <v>1000000000</v>
       </c>
       <c r="G2340" s="2" t="n">
-        <v>45108</v>
-      </c>
-      <c r="H2340" t="inlineStr">
-        <is>
-          <t>[1164433541.896319, None]</t>
-        </is>
-      </c>
-      <c r="I2340" t="inlineStr">
-        <is>
-          <t>[1266554363.5206263, None]</t>
-        </is>
+        <v>44835</v>
+      </c>
+      <c r="H2340" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I2340" t="n">
+        <v>975333333.3333334</v>
       </c>
       <c r="J2340" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2341">
@@ -77151,7 +77151,7 @@
     <row r="2342">
       <c r="A2342" t="inlineStr">
         <is>
-          <t>€1 billion</t>
+          <t>€1.1 billion</t>
         </is>
       </c>
       <c r="B2342" t="inlineStr"/>
@@ -77164,22 +77164,22 @@
         </is>
       </c>
       <c r="E2342" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F2342" t="n">
-        <v>1000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="G2342" s="2" t="n">
-        <v>44835</v>
+        <v>44440</v>
       </c>
       <c r="H2342" t="n">
-        <v>1000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="I2342" t="n">
-        <v>975333333.3333334</v>
+        <v>1299870000</v>
       </c>
       <c r="J2342" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2343">
@@ -77219,12 +77219,12 @@
     <row r="2344">
       <c r="A2344" t="inlineStr">
         <is>
-          <t>€1.1 billion</t>
+          <t>€ 13.6 million</t>
         </is>
       </c>
       <c r="B2344" t="inlineStr"/>
       <c r="C2344" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2344" t="inlineStr">
         <is>
@@ -77232,19 +77232,19 @@
         </is>
       </c>
       <c r="E2344" t="n">
-        <v>1.1</v>
+        <v>13.6</v>
       </c>
       <c r="F2344" t="n">
-        <v>1100000000</v>
+        <v>13600000</v>
       </c>
       <c r="G2344" s="2" t="n">
-        <v>44440</v>
+        <v>44317</v>
       </c>
       <c r="H2344" t="n">
-        <v>1100000000</v>
+        <v>13600000</v>
       </c>
       <c r="I2344" t="n">
-        <v>1299870000</v>
+        <v>16414293.33333333</v>
       </c>
       <c r="J2344" t="n">
         <v>2021</v>
@@ -77253,32 +77253,40 @@
     <row r="2345">
       <c r="A2345" t="inlineStr">
         <is>
-          <t>€ 13.6 million</t>
+          <t>€1-1.5 billion</t>
         </is>
       </c>
       <c r="B2345" t="inlineStr"/>
       <c r="C2345" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2345" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2345" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F2345" t="n">
-        <v>13600000</v>
+      <c r="E2345" t="inlineStr">
+        <is>
+          <t>[1.0, 1.5]</t>
+        </is>
+      </c>
+      <c r="F2345" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
       </c>
       <c r="G2345" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="H2345" t="n">
-        <v>13600000</v>
-      </c>
-      <c r="I2345" t="n">
-        <v>16414293.33333333</v>
+        <v>44256</v>
+      </c>
+      <c r="H2345" t="inlineStr">
+        <is>
+          <t>[1000000000.0, 1500000000.0]</t>
+        </is>
+      </c>
+      <c r="I2345" t="inlineStr">
+        <is>
+          <t>[1205300000.0, 1807950000.0]</t>
+        </is>
       </c>
       <c r="J2345" t="n">
         <v>2021</v>
@@ -77413,7 +77421,7 @@
     <row r="2349">
       <c r="A2349" t="inlineStr">
         <is>
-          <t>€1-1.5 billion</t>
+          <t>SEK 3.1 billion</t>
         </is>
       </c>
       <c r="B2349" t="inlineStr"/>
@@ -77422,40 +77430,32 @@
       </c>
       <c r="D2349" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2349" t="inlineStr">
-        <is>
-          <t>[1.0, 1.5]</t>
-        </is>
-      </c>
-      <c r="F2349" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="E2349" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F2349" t="n">
+        <v>3100000000</v>
       </c>
       <c r="G2349" s="2" t="n">
-        <v>44256</v>
-      </c>
-      <c r="H2349" t="inlineStr">
-        <is>
-          <t>[1000000000.0, 1500000000.0]</t>
-        </is>
-      </c>
-      <c r="I2349" t="inlineStr">
-        <is>
-          <t>[1205300000.0, 1807950000.0]</t>
-        </is>
+        <v>45383</v>
+      </c>
+      <c r="H2349" t="n">
+        <v>268375032.4647217</v>
+      </c>
+      <c r="I2349" t="n">
+        <v>288809107.4365857</v>
       </c>
       <c r="J2349" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2350">
       <c r="A2350" t="inlineStr">
         <is>
-          <t>SEK 3.1 billion</t>
+          <t>SEK 3,1 billion</t>
         </is>
       </c>
       <c r="B2350" t="inlineStr"/>
@@ -77474,22 +77474,22 @@
         <v>3100000000</v>
       </c>
       <c r="G2350" s="2" t="n">
-        <v>45383</v>
+        <v>45261</v>
       </c>
       <c r="H2350" t="n">
-        <v>268375032.4647217</v>
+        <v>272611352.943763</v>
       </c>
       <c r="I2350" t="n">
-        <v>288809107.4365857</v>
+        <v>296464846.3263422</v>
       </c>
       <c r="J2350" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2351">
       <c r="A2351" t="inlineStr">
         <is>
-          <t>SEK 3,1 billion</t>
+          <t>SEK 3,7 billion</t>
         </is>
       </c>
       <c r="B2351" t="inlineStr"/>
@@ -77502,19 +77502,19 @@
         </is>
       </c>
       <c r="E2351" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="F2351" t="n">
-        <v>3100000000</v>
+        <v>3700000000</v>
       </c>
       <c r="G2351" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="H2351" t="n">
-        <v>272611352.943763</v>
+        <v>325374840.6102977</v>
       </c>
       <c r="I2351" t="n">
-        <v>296464846.3263422</v>
+        <v>353845139.1636987</v>
       </c>
       <c r="J2351" t="n">
         <v>2023</v>
@@ -77523,7 +77523,7 @@
     <row r="2352">
       <c r="A2352" t="inlineStr">
         <is>
-          <t>SEK 3,7 billion</t>
+          <t>SEK 6,2 billion</t>
         </is>
       </c>
       <c r="B2352" t="inlineStr"/>
@@ -77536,19 +77536,19 @@
         </is>
       </c>
       <c r="E2352" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="F2352" t="n">
-        <v>3700000000</v>
+        <v>6200000000</v>
       </c>
       <c r="G2352" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="H2352" t="n">
-        <v>325374840.6102977</v>
+        <v>545222705.8875259</v>
       </c>
       <c r="I2352" t="n">
-        <v>353845139.1636987</v>
+        <v>592929692.6526843</v>
       </c>
       <c r="J2352" t="n">
         <v>2023</v>
@@ -77557,35 +77557,35 @@
     <row r="2353">
       <c r="A2353" t="inlineStr">
         <is>
-          <t>SEK 6,2 billion</t>
+          <t>EUR 506 million</t>
         </is>
       </c>
       <c r="B2353" t="inlineStr"/>
       <c r="C2353" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2353" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E2353" t="n">
-        <v>6.2</v>
+        <v>506</v>
       </c>
       <c r="F2353" t="n">
-        <v>6200000000</v>
+        <v>506000000</v>
       </c>
       <c r="G2353" s="2" t="n">
-        <v>45261</v>
+        <v>44621</v>
       </c>
       <c r="H2353" t="n">
-        <v>545222705.8875259</v>
+        <v>506000000</v>
       </c>
       <c r="I2353" t="n">
-        <v>592929692.6526843</v>
+        <v>564797200</v>
       </c>
       <c r="J2353" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2354">
@@ -77625,94 +77625,60 @@
     <row r="2355">
       <c r="A2355" t="inlineStr">
         <is>
-          <t>EUR 506 million</t>
+          <t>CZK 1.4 billion (EUR 52 million)</t>
         </is>
       </c>
       <c r="B2355" t="inlineStr"/>
       <c r="C2355" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2355" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E2355" t="n">
-        <v>506</v>
+        <v>1.4</v>
       </c>
       <c r="F2355" t="n">
-        <v>506000000</v>
+        <v>1400000000</v>
       </c>
       <c r="G2355" s="2" t="n">
-        <v>44621</v>
+        <v>44075</v>
       </c>
       <c r="H2355" t="n">
-        <v>506000000</v>
+        <v>53382139.86120643</v>
       </c>
       <c r="I2355" t="n">
-        <v>564797200</v>
+        <v>63989171.05162816</v>
       </c>
       <c r="J2355" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="2356">
       <c r="A2356" t="inlineStr">
         <is>
-          <t>CZK 1.4 billion (EUR 52 million)</t>
+          <t>30 billion-krona ($2.8 billion)</t>
         </is>
       </c>
       <c r="B2356" t="inlineStr"/>
       <c r="C2356" t="n">
         <v>1000000000</v>
       </c>
-      <c r="D2356" t="inlineStr">
-        <is>
-          <t>CZK</t>
-        </is>
-      </c>
+      <c r="D2356" t="inlineStr"/>
       <c r="E2356" t="n">
-        <v>1.4</v>
+        <v>30</v>
       </c>
       <c r="F2356" t="n">
-        <v>1400000000</v>
+        <v>30000000000</v>
       </c>
       <c r="G2356" s="2" t="n">
-        <v>44075</v>
-      </c>
-      <c r="H2356" t="n">
-        <v>53382139.86120643</v>
-      </c>
-      <c r="I2356" t="n">
-        <v>63989171.05162816</v>
-      </c>
+        <v>45658</v>
+      </c>
+      <c r="H2356" t="inlineStr"/>
+      <c r="I2356" t="inlineStr"/>
       <c r="J2356" t="n">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="2357">
-      <c r="A2357" t="inlineStr">
-        <is>
-          <t>30 billion-krona ($2.8 billion)</t>
-        </is>
-      </c>
-      <c r="B2357" t="inlineStr"/>
-      <c r="C2357" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D2357" t="inlineStr"/>
-      <c r="E2357" t="n">
-        <v>30</v>
-      </c>
-      <c r="F2357" t="n">
-        <v>30000000000</v>
-      </c>
-      <c r="G2357" s="2" t="n">
-        <v>45658</v>
-      </c>
-      <c r="H2357" t="inlineStr"/>
-      <c r="I2357" t="inlineStr"/>
-      <c r="J2357" t="n">
         <v>2025</v>
       </c>
     </row>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -59915,34 +59915,32 @@
     <row r="1832">
       <c r="A1832" t="inlineStr">
         <is>
-          <t>US$1.1bn</t>
-        </is>
-      </c>
-      <c r="B1832" t="inlineStr">
-        <is>
-          <t>1bn</t>
-        </is>
-      </c>
-      <c r="C1832" t="inlineStr"/>
+          <t>$1.1 billion</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr"/>
+      <c r="C1832" t="n">
+        <v>1000000000</v>
+      </c>
       <c r="D1832" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="E1832" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1832" t="n">
-        <v>1</v>
+        <v>1100000000</v>
       </c>
       <c r="G1832" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="H1832" t="n">
-        <v>0.9306654257794322</v>
+        <v>1023731968.357376</v>
       </c>
       <c r="I1832" t="n">
-        <v>1</v>
+        <v>1100000000</v>
       </c>
       <c r="J1832" t="n">
         <v>2024</v>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2391"/>
+  <dimension ref="A1:J2397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78808,6 +78808,210 @@
         <v>2025</v>
       </c>
     </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>420 million GBP (468.2 million euros)</t>
+        </is>
+      </c>
+      <c r="B2392" t="inlineStr"/>
+      <c r="C2392" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2392" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2392" t="n">
+        <v>420</v>
+      </c>
+      <c r="F2392" t="n">
+        <v>420000000</v>
+      </c>
+      <c r="G2392" s="2" t="n">
+        <v>40238</v>
+      </c>
+      <c r="H2392" t="n">
+        <v>463218264.0344105</v>
+      </c>
+      <c r="I2392" t="n">
+        <v>626502702.1065403</v>
+      </c>
+      <c r="J2392" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>420 million GBP (468.2 million euros)</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr"/>
+      <c r="C2393" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2393" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2393" t="n">
+        <v>420</v>
+      </c>
+      <c r="F2393" t="n">
+        <v>420000000</v>
+      </c>
+      <c r="G2393" s="2" t="n">
+        <v>40238</v>
+      </c>
+      <c r="H2393" t="n">
+        <v>463218264.0344105</v>
+      </c>
+      <c r="I2393" t="n">
+        <v>626502702.1065403</v>
+      </c>
+      <c r="J2393" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>420 million GBP (468.2 million euros)</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr"/>
+      <c r="C2394" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2394" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2394" t="n">
+        <v>420</v>
+      </c>
+      <c r="F2394" t="n">
+        <v>420000000</v>
+      </c>
+      <c r="G2394" s="2" t="n">
+        <v>40238</v>
+      </c>
+      <c r="H2394" t="n">
+        <v>463218264.0344105</v>
+      </c>
+      <c r="I2394" t="n">
+        <v>626502702.1065403</v>
+      </c>
+      <c r="J2394" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>420 million GBP (468.2 million euros)</t>
+        </is>
+      </c>
+      <c r="B2395" t="inlineStr"/>
+      <c r="C2395" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2395" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2395" t="n">
+        <v>420</v>
+      </c>
+      <c r="F2395" t="n">
+        <v>420000000</v>
+      </c>
+      <c r="G2395" s="2" t="n">
+        <v>40238</v>
+      </c>
+      <c r="H2395" t="n">
+        <v>463218264.0344105</v>
+      </c>
+      <c r="I2395" t="n">
+        <v>626502702.1065403</v>
+      </c>
+      <c r="J2395" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>£420m (EUR 468.2m)</t>
+        </is>
+      </c>
+      <c r="B2396" t="inlineStr"/>
+      <c r="C2396" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2396" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2396" t="n">
+        <v>420</v>
+      </c>
+      <c r="F2396" t="n">
+        <v>420000000</v>
+      </c>
+      <c r="G2396" s="2" t="n">
+        <v>40848</v>
+      </c>
+      <c r="H2396" t="n">
+        <v>491141904.9289598</v>
+      </c>
+      <c r="I2396" t="n">
+        <v>669279073.8466936</v>
+      </c>
+      <c r="J2396" t="n">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>£420m (EUR 468.2m)</t>
+        </is>
+      </c>
+      <c r="B2397" t="inlineStr"/>
+      <c r="C2397" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2397" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2397" t="n">
+        <v>420</v>
+      </c>
+      <c r="F2397" t="n">
+        <v>420000000</v>
+      </c>
+      <c r="G2397" s="2" t="n">
+        <v>40848</v>
+      </c>
+      <c r="H2397" t="n">
+        <v>491141904.9289598</v>
+      </c>
+      <c r="I2397" t="n">
+        <v>669279073.8466936</v>
+      </c>
+      <c r="J2397" t="n">
+        <v>2011</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2441"/>
+  <dimension ref="A1:J2479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80582,6 +80582,1262 @@
         <v>2023</v>
       </c>
     </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>€21 million</t>
+        </is>
+      </c>
+      <c r="B2442" t="inlineStr"/>
+      <c r="C2442" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2442" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2442" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2442" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="G2442" s="2" t="n">
+        <v>44440</v>
+      </c>
+      <c r="H2442" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="I2442" t="n">
+        <v>24815700</v>
+      </c>
+      <c r="J2442" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>€10 million ($11.3 million)</t>
+        </is>
+      </c>
+      <c r="B2443" t="inlineStr"/>
+      <c r="C2443" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2443" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2443" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2443" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="G2443" s="2" t="n">
+        <v>46874</v>
+      </c>
+      <c r="H2443" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I2443" t="n">
+        <v>11654000</v>
+      </c>
+      <c r="J2443" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>20 million euros</t>
+        </is>
+      </c>
+      <c r="B2444" t="inlineStr"/>
+      <c r="C2444" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2444" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2444" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2444" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G2444" s="2" t="n">
+        <v>45200</v>
+      </c>
+      <c r="H2444" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I2444" t="n">
+        <v>21102667</v>
+      </c>
+      <c r="J2444" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>20 million euros</t>
+        </is>
+      </c>
+      <c r="B2445" t="inlineStr"/>
+      <c r="C2445" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2445" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2445" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2445" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G2445" s="2" t="n">
+        <v>45200</v>
+      </c>
+      <c r="H2445" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I2445" t="n">
+        <v>21102667</v>
+      </c>
+      <c r="J2445" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>20 million euros</t>
+        </is>
+      </c>
+      <c r="B2446" t="inlineStr"/>
+      <c r="C2446" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2446" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2446" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2446" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G2446" s="2" t="n">
+        <v>45200</v>
+      </c>
+      <c r="H2446" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I2446" t="n">
+        <v>21102667</v>
+      </c>
+      <c r="J2446" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>20 million euros</t>
+        </is>
+      </c>
+      <c r="B2447" t="inlineStr"/>
+      <c r="C2447" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2447" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2447" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2447" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G2447" s="2" t="n">
+        <v>45200</v>
+      </c>
+      <c r="H2447" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I2447" t="n">
+        <v>21102667</v>
+      </c>
+      <c r="J2447" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>€1.2M</t>
+        </is>
+      </c>
+      <c r="B2448" t="inlineStr"/>
+      <c r="C2448" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2448" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2448" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F2448" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="G2448" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H2448" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I2448" t="n">
+        <v>1297680</v>
+      </c>
+      <c r="J2448" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>€10 million</t>
+        </is>
+      </c>
+      <c r="B2449" t="inlineStr"/>
+      <c r="C2449" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2449" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2449" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2449" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="G2449" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="H2449" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I2449" t="n">
+        <v>10788000</v>
+      </c>
+      <c r="J2449" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>€4.2 million ($4.6 million)</t>
+        </is>
+      </c>
+      <c r="B2450" t="inlineStr"/>
+      <c r="C2450" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2450" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2450" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F2450" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="G2450" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="H2450" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="I2450" t="n">
+        <v>4530960</v>
+      </c>
+      <c r="J2450" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>€4.2 million</t>
+        </is>
+      </c>
+      <c r="B2451" t="inlineStr"/>
+      <c r="C2451" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2451" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2451" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F2451" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="G2451" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="H2451" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="I2451" t="n">
+        <v>4656120</v>
+      </c>
+      <c r="J2451" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr"/>
+      <c r="B2452" t="inlineStr"/>
+      <c r="C2452" t="inlineStr"/>
+      <c r="D2452" t="inlineStr"/>
+      <c r="E2452" t="inlineStr"/>
+      <c r="F2452" t="inlineStr"/>
+      <c r="G2452" s="2" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H2452" t="inlineStr"/>
+      <c r="I2452" t="inlineStr"/>
+      <c r="J2452" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>€60 million</t>
+        </is>
+      </c>
+      <c r="B2453" t="inlineStr"/>
+      <c r="C2453" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2453" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2453" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2453" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="G2453" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="H2453" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="I2453" t="n">
+        <v>69924000</v>
+      </c>
+      <c r="J2453" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="inlineStr">
+        <is>
+          <t>€85.6 million</t>
+        </is>
+      </c>
+      <c r="B2454" t="inlineStr"/>
+      <c r="C2454" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2454" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2454" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="F2454" t="n">
+        <v>85600000</v>
+      </c>
+      <c r="G2454" s="2" t="n">
+        <v>43525</v>
+      </c>
+      <c r="H2454" t="n">
+        <v>85600000</v>
+      </c>
+      <c r="I2454" t="n">
+        <v>97438480</v>
+      </c>
+      <c r="J2454" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>€85.6 million</t>
+        </is>
+      </c>
+      <c r="B2455" t="inlineStr"/>
+      <c r="C2455" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2455" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2455" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="F2455" t="n">
+        <v>85600000</v>
+      </c>
+      <c r="G2455" s="2" t="n">
+        <v>43525</v>
+      </c>
+      <c r="H2455" t="n">
+        <v>85600000</v>
+      </c>
+      <c r="I2455" t="n">
+        <v>97438480</v>
+      </c>
+      <c r="J2455" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="inlineStr">
+        <is>
+          <t>€20 million</t>
+        </is>
+      </c>
+      <c r="B2456" t="inlineStr"/>
+      <c r="C2456" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2456" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2456" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2456" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G2456" s="2" t="n">
+        <v>44105</v>
+      </c>
+      <c r="H2456" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I2456" t="n">
+        <v>23504000</v>
+      </c>
+      <c r="J2456" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>€170m</t>
+        </is>
+      </c>
+      <c r="B2457" t="inlineStr"/>
+      <c r="C2457" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2457" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2457" t="n">
+        <v>170</v>
+      </c>
+      <c r="F2457" t="n">
+        <v>170000000</v>
+      </c>
+      <c r="G2457" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="H2457" t="n">
+        <v>170000000</v>
+      </c>
+      <c r="I2457" t="n">
+        <v>193086000</v>
+      </c>
+      <c r="J2457" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="inlineStr">
+        <is>
+          <t>€170m</t>
+        </is>
+      </c>
+      <c r="B2458" t="inlineStr"/>
+      <c r="C2458" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2458" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2458" t="n">
+        <v>170</v>
+      </c>
+      <c r="F2458" t="n">
+        <v>170000000</v>
+      </c>
+      <c r="G2458" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="H2458" t="n">
+        <v>170000000</v>
+      </c>
+      <c r="I2458" t="n">
+        <v>193086000</v>
+      </c>
+      <c r="J2458" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>€50m</t>
+        </is>
+      </c>
+      <c r="B2459" t="inlineStr"/>
+      <c r="C2459" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2459" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2459" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2459" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G2459" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="H2459" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="I2459" t="n">
+        <v>56790000</v>
+      </c>
+      <c r="J2459" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="inlineStr">
+        <is>
+          <t>€32.3 million</t>
+        </is>
+      </c>
+      <c r="B2460" t="inlineStr"/>
+      <c r="C2460" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2460" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2460" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F2460" t="n">
+        <v>32300000</v>
+      </c>
+      <c r="G2460" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="H2460" t="n">
+        <v>32300000</v>
+      </c>
+      <c r="I2460" t="n">
+        <v>34759322</v>
+      </c>
+      <c r="J2460" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>EUR 22m</t>
+        </is>
+      </c>
+      <c r="B2461" t="inlineStr"/>
+      <c r="C2461" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2461" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2461" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2461" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="G2461" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="H2461" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="I2461" t="n">
+        <v>25063133</v>
+      </c>
+      <c r="J2461" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="inlineStr">
+        <is>
+          <t>EUR 22m</t>
+        </is>
+      </c>
+      <c r="B2462" t="inlineStr"/>
+      <c r="C2462" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2462" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2462" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2462" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="G2462" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="H2462" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="I2462" t="n">
+        <v>25063133</v>
+      </c>
+      <c r="J2462" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>EUR 22m</t>
+        </is>
+      </c>
+      <c r="B2463" t="inlineStr"/>
+      <c r="C2463" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2463" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2463" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2463" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="G2463" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="H2463" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="I2463" t="n">
+        <v>25063133</v>
+      </c>
+      <c r="J2463" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>30 million euros ($33 million)</t>
+        </is>
+      </c>
+      <c r="B2464" t="inlineStr"/>
+      <c r="C2464" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2464" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2464" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2464" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="G2464" s="2" t="n">
+        <v>45047</v>
+      </c>
+      <c r="H2464" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="I2464" t="n">
+        <v>32907000</v>
+      </c>
+      <c r="J2464" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>€30M</t>
+        </is>
+      </c>
+      <c r="B2465" t="inlineStr"/>
+      <c r="C2465" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2465" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2465" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2465" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="G2465" s="2" t="n">
+        <v>45047</v>
+      </c>
+      <c r="H2465" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="I2465" t="n">
+        <v>32907000</v>
+      </c>
+      <c r="J2465" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="inlineStr"/>
+      <c r="B2466" t="inlineStr"/>
+      <c r="C2466" t="inlineStr"/>
+      <c r="D2466" t="inlineStr"/>
+      <c r="E2466" t="inlineStr"/>
+      <c r="F2466" t="inlineStr"/>
+      <c r="G2466" s="2" t="n">
+        <v>44805</v>
+      </c>
+      <c r="H2466" t="inlineStr"/>
+      <c r="I2466" t="inlineStr"/>
+      <c r="J2466" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>SEK 1.2 billion</t>
+        </is>
+      </c>
+      <c r="B2467" t="inlineStr"/>
+      <c r="C2467" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2467" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="E2467" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F2467" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="G2467" s="2" t="n">
+        <v>45536</v>
+      </c>
+      <c r="H2467" t="n">
+        <v>105765700</v>
+      </c>
+      <c r="I2467" t="n">
+        <v>117079104</v>
+      </c>
+      <c r="J2467" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="inlineStr">
+        <is>
+          <t>SEK 1.2 billion</t>
+        </is>
+      </c>
+      <c r="B2468" t="inlineStr"/>
+      <c r="C2468" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2468" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="E2468" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F2468" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="G2468" s="2" t="n">
+        <v>45536</v>
+      </c>
+      <c r="H2468" t="n">
+        <v>105765700</v>
+      </c>
+      <c r="I2468" t="n">
+        <v>117079104</v>
+      </c>
+      <c r="J2468" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>160 million euros</t>
+        </is>
+      </c>
+      <c r="B2469" t="inlineStr"/>
+      <c r="C2469" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2469" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2469" t="n">
+        <v>160</v>
+      </c>
+      <c r="F2469" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="G2469" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H2469" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="I2469" t="n">
+        <v>171152000</v>
+      </c>
+      <c r="J2469" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="inlineStr">
+        <is>
+          <t>€160 million ($176 million)</t>
+        </is>
+      </c>
+      <c r="B2470" t="inlineStr"/>
+      <c r="C2470" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2470" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2470" t="n">
+        <v>160</v>
+      </c>
+      <c r="F2470" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="G2470" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H2470" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="I2470" t="n">
+        <v>171152000</v>
+      </c>
+      <c r="J2470" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>€160 million ($176 million)</t>
+        </is>
+      </c>
+      <c r="B2471" t="inlineStr"/>
+      <c r="C2471" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2471" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2471" t="n">
+        <v>160</v>
+      </c>
+      <c r="F2471" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="G2471" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H2471" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="I2471" t="n">
+        <v>171152000</v>
+      </c>
+      <c r="J2471" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" t="inlineStr">
+        <is>
+          <t>€160 million ($176 million)</t>
+        </is>
+      </c>
+      <c r="B2472" t="inlineStr"/>
+      <c r="C2472" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2472" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2472" t="n">
+        <v>160</v>
+      </c>
+      <c r="F2472" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="G2472" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H2472" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="I2472" t="n">
+        <v>171152000</v>
+      </c>
+      <c r="J2472" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>€160 million ($176 million)</t>
+        </is>
+      </c>
+      <c r="B2473" t="inlineStr"/>
+      <c r="C2473" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2473" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2473" t="n">
+        <v>160</v>
+      </c>
+      <c r="F2473" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="G2473" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H2473" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="I2473" t="n">
+        <v>171152000</v>
+      </c>
+      <c r="J2473" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="inlineStr">
+        <is>
+          <t>€150 million</t>
+        </is>
+      </c>
+      <c r="B2474" t="inlineStr"/>
+      <c r="C2474" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2474" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2474" t="n">
+        <v>150</v>
+      </c>
+      <c r="F2474" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="G2474" s="2" t="n">
+        <v>43313</v>
+      </c>
+      <c r="H2474" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="I2474" t="n">
+        <v>175440000</v>
+      </c>
+      <c r="J2474" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>200 million euros</t>
+        </is>
+      </c>
+      <c r="B2475" t="inlineStr"/>
+      <c r="C2475" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2475" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2475" t="n">
+        <v>200</v>
+      </c>
+      <c r="F2475" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="G2475" s="2" t="n">
+        <v>44805</v>
+      </c>
+      <c r="H2475" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="I2475" t="n">
+        <v>200080000</v>
+      </c>
+      <c r="J2475" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="inlineStr">
+        <is>
+          <t>200 million euros</t>
+        </is>
+      </c>
+      <c r="B2476" t="inlineStr"/>
+      <c r="C2476" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2476" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2476" t="n">
+        <v>200</v>
+      </c>
+      <c r="F2476" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G2476" s="2" t="n">
+        <v>44805</v>
+      </c>
+      <c r="H2476" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="I2476" t="n">
+        <v>50020000</v>
+      </c>
+      <c r="J2476" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>200 million euros</t>
+        </is>
+      </c>
+      <c r="B2477" t="inlineStr"/>
+      <c r="C2477" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2477" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2477" t="n">
+        <v>200</v>
+      </c>
+      <c r="F2477" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="G2477" s="2" t="n">
+        <v>44805</v>
+      </c>
+      <c r="H2477" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="I2477" t="n">
+        <v>100040000</v>
+      </c>
+      <c r="J2477" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="inlineStr">
+        <is>
+          <t>200 million euros</t>
+        </is>
+      </c>
+      <c r="B2478" t="inlineStr"/>
+      <c r="C2478" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2478" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2478" t="n">
+        <v>200</v>
+      </c>
+      <c r="F2478" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G2478" s="2" t="n">
+        <v>44805</v>
+      </c>
+      <c r="H2478" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="I2478" t="n">
+        <v>50020000</v>
+      </c>
+      <c r="J2478" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>33 million euros</t>
+        </is>
+      </c>
+      <c r="B2479" t="inlineStr"/>
+      <c r="C2479" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2479" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2479" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2479" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="G2479" s="2" t="n">
+        <v>44805</v>
+      </c>
+      <c r="H2479" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="I2479" t="n">
+        <v>33013200</v>
+      </c>
+      <c r="J2479" t="n">
+        <v>2022</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -66487,16 +66487,16 @@
         <v>2</v>
       </c>
       <c r="F2024" t="n">
-        <v>800000000</v>
+        <v>1600000000</v>
       </c>
       <c r="G2024" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="H2024" t="n">
-        <v>747873235</v>
+        <v>1495746471</v>
       </c>
       <c r="I2024" t="n">
-        <v>800000000</v>
+        <v>1600000000</v>
       </c>
       <c r="J2024" t="n">
         <v>2023</v>
@@ -66521,16 +66521,16 @@
         <v>2</v>
       </c>
       <c r="F2025" t="n">
-        <v>800000000</v>
+        <v>1600000000</v>
       </c>
       <c r="G2025" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="H2025" t="n">
-        <v>747873235</v>
+        <v>1495746471</v>
       </c>
       <c r="I2025" t="n">
-        <v>800000000</v>
+        <v>1600000000</v>
       </c>
       <c r="J2025" t="n">
         <v>2023</v>
@@ -68681,16 +68681,16 @@
         <v>500</v>
       </c>
       <c r="F2089" t="n">
-        <v>200000000</v>
+        <v>400000000</v>
       </c>
       <c r="G2089" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="H2089" t="n">
-        <v>231286066</v>
+        <v>462572132</v>
       </c>
       <c r="I2089" t="n">
-        <v>231378581</v>
+        <v>462757161</v>
       </c>
       <c r="J2089" t="n">
         <v>2022</v>
@@ -68715,16 +68715,16 @@
         <v>500</v>
       </c>
       <c r="F2090" t="n">
-        <v>200000000</v>
+        <v>400000000</v>
       </c>
       <c r="G2090" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="H2090" t="n">
-        <v>231286066</v>
+        <v>462572132</v>
       </c>
       <c r="I2090" t="n">
-        <v>231378581</v>
+        <v>462757161</v>
       </c>
       <c r="J2090" t="n">
         <v>2022</v>
@@ -68817,16 +68817,16 @@
         <v>2</v>
       </c>
       <c r="F2093" t="n">
-        <v>800000000</v>
+        <v>1600000000</v>
       </c>
       <c r="G2093" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="H2093" t="n">
-        <v>800000000</v>
+        <v>1600000000</v>
       </c>
       <c r="I2093" t="n">
-        <v>932320000</v>
+        <v>1864640000</v>
       </c>
       <c r="J2093" t="n">
         <v>2025</v>
@@ -68851,16 +68851,16 @@
         <v>2</v>
       </c>
       <c r="F2094" t="n">
-        <v>800000000</v>
+        <v>1600000000</v>
       </c>
       <c r="G2094" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="H2094" t="n">
-        <v>800000000</v>
+        <v>1600000000</v>
       </c>
       <c r="I2094" t="n">
-        <v>932320000</v>
+        <v>1864640000</v>
       </c>
       <c r="J2094" t="n">
         <v>2025</v>
@@ -79042,7 +79042,7 @@
       </c>
       <c r="F2396" t="inlineStr">
         <is>
-          <t>[400000000.0, None]</t>
+          <t>[800000000.0, None]</t>
         </is>
       </c>
       <c r="G2396" s="2" t="n">
@@ -79050,12 +79050,12 @@
       </c>
       <c r="H2396" t="inlineStr">
         <is>
-          <t>[400000000.0, None]</t>
+          <t>[800000000.0, None]</t>
         </is>
       </c>
       <c r="I2396" t="inlineStr">
         <is>
-          <t>[454320000.0, None]</t>
+          <t>[908640000.0, None]</t>
         </is>
       </c>
       <c r="J2396" t="n">
@@ -79084,7 +79084,7 @@
       </c>
       <c r="F2397" t="inlineStr">
         <is>
-          <t>[400000000.0, None]</t>
+          <t>[800000000.0, None]</t>
         </is>
       </c>
       <c r="G2397" s="2" t="n">
@@ -79092,12 +79092,12 @@
       </c>
       <c r="H2397" t="inlineStr">
         <is>
-          <t>[400000000.0, None]</t>
+          <t>[800000000.0, None]</t>
         </is>
       </c>
       <c r="I2397" t="inlineStr">
         <is>
-          <t>[454320000.0, None]</t>
+          <t>[908640000.0, None]</t>
         </is>
       </c>
       <c r="J2397" t="n">
@@ -81721,16 +81721,16 @@
         <v>200</v>
       </c>
       <c r="F2476" t="n">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="G2476" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="H2476" t="n">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="I2476" t="n">
-        <v>50020000</v>
+        <v>100040000</v>
       </c>
       <c r="J2476" t="n">
         <v>2022</v>
@@ -81789,16 +81789,16 @@
         <v>200</v>
       </c>
       <c r="F2478" t="n">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="G2478" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="H2478" t="n">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="I2478" t="n">
-        <v>50020000</v>
+        <v>100040000</v>
       </c>
       <c r="J2478" t="n">
         <v>2022</v>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2427"/>
+  <dimension ref="A1:J2426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78445,127 +78445,127 @@
       </c>
     </row>
     <row r="2379">
-      <c r="A2379" t="inlineStr">
-        <is>
-          <t>HUF 15 bln</t>
-        </is>
-      </c>
+      <c r="A2379" t="inlineStr"/>
       <c r="B2379" t="inlineStr"/>
-      <c r="C2379" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D2379" t="inlineStr">
-        <is>
-          <t>HUF</t>
-        </is>
-      </c>
-      <c r="E2379" t="n">
-        <v>15</v>
-      </c>
-      <c r="F2379" t="n">
-        <v>15000000000</v>
-      </c>
+      <c r="C2379" t="inlineStr"/>
+      <c r="D2379" t="inlineStr"/>
+      <c r="E2379" t="inlineStr"/>
+      <c r="F2379" t="inlineStr"/>
       <c r="G2379" s="2" t="n">
-        <v>41883</v>
-      </c>
-      <c r="H2379" t="n">
-        <v>47732697</v>
-      </c>
-      <c r="I2379" t="n">
-        <v>62687351</v>
-      </c>
+        <v>41306</v>
+      </c>
+      <c r="H2379" t="inlineStr"/>
+      <c r="I2379" t="inlineStr"/>
       <c r="J2379" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="2380">
-      <c r="A2380" t="inlineStr"/>
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>€53 million ($57.4 million)</t>
+        </is>
+      </c>
       <c r="B2380" t="inlineStr"/>
-      <c r="C2380" t="inlineStr"/>
-      <c r="D2380" t="inlineStr"/>
-      <c r="E2380" t="inlineStr"/>
-      <c r="F2380" t="inlineStr"/>
+      <c r="C2380" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2380" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2380" t="n">
+        <v>53000000</v>
+      </c>
       <c r="G2380" s="2" t="n">
-        <v>41306</v>
-      </c>
-      <c r="H2380" t="inlineStr"/>
-      <c r="I2380" t="inlineStr"/>
+        <v>45566</v>
+      </c>
+      <c r="H2380" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="I2380" t="n">
+        <v>58755800</v>
+      </c>
       <c r="J2380" t="n">
-        <v>2013</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2381">
       <c r="A2381" t="inlineStr">
         <is>
-          <t>€53 million ($57.4 million)</t>
+          <t>PLN 1 billion</t>
         </is>
       </c>
       <c r="B2381" t="inlineStr"/>
       <c r="C2381" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2381" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="E2381" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="F2381" t="n">
-        <v>53000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G2381" s="2" t="n">
-        <v>45566</v>
+        <v>44197</v>
       </c>
       <c r="H2381" t="n">
-        <v>53000000</v>
+        <v>219459471</v>
       </c>
       <c r="I2381" t="n">
-        <v>58755800</v>
+        <v>269435879</v>
       </c>
       <c r="J2381" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2382">
       <c r="A2382" t="inlineStr">
         <is>
-          <t>PLN 1 billion</t>
+          <t>€90 million</t>
         </is>
       </c>
       <c r="B2382" t="inlineStr"/>
       <c r="C2382" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2382" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E2382" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="F2382" t="n">
-        <v>1000000000</v>
+        <v>90000000</v>
       </c>
       <c r="G2382" s="2" t="n">
-        <v>44197</v>
+        <v>44986</v>
       </c>
       <c r="H2382" t="n">
-        <v>219459471</v>
+        <v>90000000</v>
       </c>
       <c r="I2382" t="n">
-        <v>269435879</v>
+        <v>96156000</v>
       </c>
       <c r="J2382" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2383">
       <c r="A2383" t="inlineStr">
         <is>
-          <t>€90 million</t>
+          <t>€21 million</t>
         </is>
       </c>
       <c r="B2383" t="inlineStr"/>
@@ -78578,28 +78578,28 @@
         </is>
       </c>
       <c r="E2383" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F2383" t="n">
-        <v>90000000</v>
+        <v>21000000</v>
       </c>
       <c r="G2383" s="2" t="n">
-        <v>44986</v>
+        <v>44440</v>
       </c>
       <c r="H2383" t="n">
-        <v>90000000</v>
+        <v>21000000</v>
       </c>
       <c r="I2383" t="n">
-        <v>96156000</v>
+        <v>24815700</v>
       </c>
       <c r="J2383" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2384">
       <c r="A2384" t="inlineStr">
         <is>
-          <t>€21 million</t>
+          <t>€10 million ($11.3 million)</t>
         </is>
       </c>
       <c r="B2384" t="inlineStr"/>
@@ -78612,28 +78612,28 @@
         </is>
       </c>
       <c r="E2384" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F2384" t="n">
-        <v>21000000</v>
+        <v>10000000</v>
       </c>
       <c r="G2384" s="2" t="n">
-        <v>44440</v>
+        <v>46874</v>
       </c>
       <c r="H2384" t="n">
-        <v>21000000</v>
+        <v>10000000</v>
       </c>
       <c r="I2384" t="n">
-        <v>24815700</v>
+        <v>11654000</v>
       </c>
       <c r="J2384" t="n">
-        <v>2021</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="2385">
       <c r="A2385" t="inlineStr">
         <is>
-          <t>€10 million ($11.3 million)</t>
+          <t>20 million euros</t>
         </is>
       </c>
       <c r="B2385" t="inlineStr"/>
@@ -78646,22 +78646,22 @@
         </is>
       </c>
       <c r="E2385" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F2385" t="n">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
       <c r="G2385" s="2" t="n">
-        <v>46874</v>
+        <v>45200</v>
       </c>
       <c r="H2385" t="n">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
       <c r="I2385" t="n">
-        <v>11654000</v>
+        <v>21102667</v>
       </c>
       <c r="J2385" t="n">
-        <v>2028</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2386">
@@ -78769,7 +78769,7 @@
     <row r="2389">
       <c r="A2389" t="inlineStr">
         <is>
-          <t>20 million euros</t>
+          <t>€1.2M</t>
         </is>
       </c>
       <c r="B2389" t="inlineStr"/>
@@ -78782,28 +78782,28 @@
         </is>
       </c>
       <c r="E2389" t="n">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="F2389" t="n">
-        <v>20000000</v>
+        <v>1200000</v>
       </c>
       <c r="G2389" s="2" t="n">
-        <v>45200</v>
+        <v>45323</v>
       </c>
       <c r="H2389" t="n">
-        <v>20000000</v>
+        <v>1200000</v>
       </c>
       <c r="I2389" t="n">
-        <v>21102667</v>
+        <v>1297680</v>
       </c>
       <c r="J2389" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2390">
       <c r="A2390" t="inlineStr">
         <is>
-          <t>€1.2M</t>
+          <t>€10 million</t>
         </is>
       </c>
       <c r="B2390" t="inlineStr"/>
@@ -78816,28 +78816,28 @@
         </is>
       </c>
       <c r="E2390" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="F2390" t="n">
-        <v>1200000</v>
+        <v>10000000</v>
       </c>
       <c r="G2390" s="2" t="n">
-        <v>45323</v>
+        <v>45748</v>
       </c>
       <c r="H2390" t="n">
-        <v>1200000</v>
+        <v>10000000</v>
       </c>
       <c r="I2390" t="n">
-        <v>1297680</v>
+        <v>10788000</v>
       </c>
       <c r="J2390" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2391">
       <c r="A2391" t="inlineStr">
         <is>
-          <t>€10 million</t>
+          <t>€4.2 million ($4.6 million)</t>
         </is>
       </c>
       <c r="B2391" t="inlineStr"/>
@@ -78850,19 +78850,19 @@
         </is>
       </c>
       <c r="E2391" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="F2391" t="n">
-        <v>10000000</v>
+        <v>4200000</v>
       </c>
       <c r="G2391" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="H2391" t="n">
-        <v>10000000</v>
+        <v>4200000</v>
       </c>
       <c r="I2391" t="n">
-        <v>10788000</v>
+        <v>4530960</v>
       </c>
       <c r="J2391" t="n">
         <v>2025</v>
@@ -78871,7 +78871,7 @@
     <row r="2392">
       <c r="A2392" t="inlineStr">
         <is>
-          <t>€4.2 million ($4.6 million)</t>
+          <t>€4.2 million</t>
         </is>
       </c>
       <c r="B2392" t="inlineStr"/>
@@ -78890,72 +78890,72 @@
         <v>4200000</v>
       </c>
       <c r="G2392" s="2" t="n">
-        <v>45748</v>
+        <v>45566</v>
       </c>
       <c r="H2392" t="n">
         <v>4200000</v>
       </c>
       <c r="I2392" t="n">
-        <v>4530960</v>
+        <v>4656120</v>
       </c>
       <c r="J2392" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr"/>
+      <c r="B2393" t="inlineStr"/>
+      <c r="C2393" t="inlineStr"/>
+      <c r="D2393" t="inlineStr"/>
+      <c r="E2393" t="inlineStr"/>
+      <c r="F2393" t="inlineStr"/>
+      <c r="G2393" s="2" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H2393" t="inlineStr"/>
+      <c r="I2393" t="inlineStr"/>
+      <c r="J2393" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>€60 million</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr"/>
+      <c r="C2394" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2394" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2394" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2394" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="G2394" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="H2394" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="I2394" t="n">
+        <v>69924000</v>
+      </c>
+      <c r="J2394" t="n">
         <v>2025</v>
-      </c>
-    </row>
-    <row r="2393">
-      <c r="A2393" t="inlineStr">
-        <is>
-          <t>€4.2 million</t>
-        </is>
-      </c>
-      <c r="B2393" t="inlineStr"/>
-      <c r="C2393" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D2393" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2393" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F2393" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="G2393" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="H2393" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="I2393" t="n">
-        <v>4656120</v>
-      </c>
-      <c r="J2393" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="2394">
-      <c r="A2394" t="inlineStr"/>
-      <c r="B2394" t="inlineStr"/>
-      <c r="C2394" t="inlineStr"/>
-      <c r="D2394" t="inlineStr"/>
-      <c r="E2394" t="inlineStr"/>
-      <c r="F2394" t="inlineStr"/>
-      <c r="G2394" s="2" t="n">
-        <v>44682</v>
-      </c>
-      <c r="H2394" t="inlineStr"/>
-      <c r="I2394" t="inlineStr"/>
-      <c r="J2394" t="n">
-        <v>2022</v>
       </c>
     </row>
     <row r="2395">
       <c r="A2395" t="inlineStr">
         <is>
-          <t>€60 million</t>
+          <t>€85.6 million</t>
         </is>
       </c>
       <c r="B2395" t="inlineStr"/>
@@ -78968,22 +78968,22 @@
         </is>
       </c>
       <c r="E2395" t="n">
-        <v>60</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F2395" t="n">
-        <v>60000000</v>
+        <v>85600000</v>
       </c>
       <c r="G2395" s="2" t="n">
-        <v>45931</v>
+        <v>43525</v>
       </c>
       <c r="H2395" t="n">
-        <v>60000000</v>
+        <v>85600000</v>
       </c>
       <c r="I2395" t="n">
-        <v>69924000</v>
+        <v>97438480</v>
       </c>
       <c r="J2395" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="2396">
@@ -79023,7 +79023,7 @@
     <row r="2397">
       <c r="A2397" t="inlineStr">
         <is>
-          <t>€85.6 million</t>
+          <t>€20 million</t>
         </is>
       </c>
       <c r="B2397" t="inlineStr"/>
@@ -79036,28 +79036,28 @@
         </is>
       </c>
       <c r="E2397" t="n">
-        <v>85.59999999999999</v>
+        <v>20</v>
       </c>
       <c r="F2397" t="n">
-        <v>85600000</v>
+        <v>20000000</v>
       </c>
       <c r="G2397" s="2" t="n">
-        <v>43525</v>
+        <v>44105</v>
       </c>
       <c r="H2397" t="n">
-        <v>85600000</v>
+        <v>20000000</v>
       </c>
       <c r="I2397" t="n">
-        <v>97438480</v>
+        <v>23504000</v>
       </c>
       <c r="J2397" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="2398">
       <c r="A2398" t="inlineStr">
         <is>
-          <t>€20 million</t>
+          <t>€170m</t>
         </is>
       </c>
       <c r="B2398" t="inlineStr"/>
@@ -79070,22 +79070,22 @@
         </is>
       </c>
       <c r="E2398" t="n">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="F2398" t="n">
-        <v>20000000</v>
+        <v>170000000</v>
       </c>
       <c r="G2398" s="2" t="n">
-        <v>44105</v>
+        <v>45778</v>
       </c>
       <c r="H2398" t="n">
-        <v>20000000</v>
+        <v>170000000</v>
       </c>
       <c r="I2398" t="n">
-        <v>23504000</v>
+        <v>193086000</v>
       </c>
       <c r="J2398" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2399">
@@ -79125,7 +79125,7 @@
     <row r="2400">
       <c r="A2400" t="inlineStr">
         <is>
-          <t>€170m</t>
+          <t>€50m</t>
         </is>
       </c>
       <c r="B2400" t="inlineStr"/>
@@ -79138,19 +79138,19 @@
         </is>
       </c>
       <c r="E2400" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="F2400" t="n">
-        <v>170000000</v>
+        <v>50000000</v>
       </c>
       <c r="G2400" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="H2400" t="n">
-        <v>170000000</v>
+        <v>50000000</v>
       </c>
       <c r="I2400" t="n">
-        <v>193086000</v>
+        <v>56790000</v>
       </c>
       <c r="J2400" t="n">
         <v>2025</v>
@@ -79159,7 +79159,7 @@
     <row r="2401">
       <c r="A2401" t="inlineStr">
         <is>
-          <t>€50m</t>
+          <t>€32.3 million</t>
         </is>
       </c>
       <c r="B2401" t="inlineStr"/>
@@ -79172,28 +79172,28 @@
         </is>
       </c>
       <c r="E2401" t="n">
-        <v>50</v>
+        <v>32.3</v>
       </c>
       <c r="F2401" t="n">
-        <v>50000000</v>
+        <v>32300000</v>
       </c>
       <c r="G2401" s="2" t="n">
-        <v>45778</v>
+        <v>45383</v>
       </c>
       <c r="H2401" t="n">
-        <v>50000000</v>
+        <v>32300000</v>
       </c>
       <c r="I2401" t="n">
-        <v>56790000</v>
+        <v>34759322</v>
       </c>
       <c r="J2401" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2402">
       <c r="A2402" t="inlineStr">
         <is>
-          <t>€32.3 million</t>
+          <t>EUR 22m</t>
         </is>
       </c>
       <c r="B2402" t="inlineStr"/>
@@ -79206,22 +79206,22 @@
         </is>
       </c>
       <c r="E2402" t="n">
-        <v>32.3</v>
+        <v>22</v>
       </c>
       <c r="F2402" t="n">
-        <v>32300000</v>
+        <v>22000000</v>
       </c>
       <c r="G2402" s="2" t="n">
-        <v>45383</v>
+        <v>45809</v>
       </c>
       <c r="H2402" t="n">
-        <v>32300000</v>
+        <v>22000000</v>
       </c>
       <c r="I2402" t="n">
-        <v>34759322</v>
+        <v>25063133</v>
       </c>
       <c r="J2402" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2403">
@@ -79295,7 +79295,7 @@
     <row r="2405">
       <c r="A2405" t="inlineStr">
         <is>
-          <t>EUR 22m</t>
+          <t>30 million euros ($33 million)</t>
         </is>
       </c>
       <c r="B2405" t="inlineStr"/>
@@ -79308,28 +79308,28 @@
         </is>
       </c>
       <c r="E2405" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F2405" t="n">
-        <v>22000000</v>
+        <v>30000000</v>
       </c>
       <c r="G2405" s="2" t="n">
-        <v>45809</v>
+        <v>45047</v>
       </c>
       <c r="H2405" t="n">
-        <v>22000000</v>
+        <v>30000000</v>
       </c>
       <c r="I2405" t="n">
-        <v>25063133</v>
+        <v>32907000</v>
       </c>
       <c r="J2405" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2406">
       <c r="A2406" t="inlineStr">
         <is>
-          <t>30 million euros ($33 million)</t>
+          <t>€30M</t>
         </is>
       </c>
       <c r="B2406" t="inlineStr"/>
@@ -79361,53 +79361,53 @@
       </c>
     </row>
     <row r="2407">
-      <c r="A2407" t="inlineStr">
-        <is>
-          <t>€30M</t>
-        </is>
-      </c>
+      <c r="A2407" t="inlineStr"/>
       <c r="B2407" t="inlineStr"/>
-      <c r="C2407" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D2407" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2407" t="n">
-        <v>30</v>
-      </c>
-      <c r="F2407" t="n">
-        <v>30000000</v>
-      </c>
+      <c r="C2407" t="inlineStr"/>
+      <c r="D2407" t="inlineStr"/>
+      <c r="E2407" t="inlineStr"/>
+      <c r="F2407" t="inlineStr"/>
       <c r="G2407" s="2" t="n">
-        <v>45047</v>
-      </c>
-      <c r="H2407" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="I2407" t="n">
-        <v>32907000</v>
-      </c>
+        <v>44805</v>
+      </c>
+      <c r="H2407" t="inlineStr"/>
+      <c r="I2407" t="inlineStr"/>
       <c r="J2407" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2408">
-      <c r="A2408" t="inlineStr"/>
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>SEK 1.2 billion</t>
+        </is>
+      </c>
       <c r="B2408" t="inlineStr"/>
-      <c r="C2408" t="inlineStr"/>
-      <c r="D2408" t="inlineStr"/>
-      <c r="E2408" t="inlineStr"/>
-      <c r="F2408" t="inlineStr"/>
+      <c r="C2408" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2408" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="E2408" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F2408" t="n">
+        <v>1200000000</v>
+      </c>
       <c r="G2408" s="2" t="n">
-        <v>44805</v>
-      </c>
-      <c r="H2408" t="inlineStr"/>
-      <c r="I2408" t="inlineStr"/>
+        <v>45536</v>
+      </c>
+      <c r="H2408" t="n">
+        <v>105765700</v>
+      </c>
+      <c r="I2408" t="n">
+        <v>117079104</v>
+      </c>
       <c r="J2408" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2409">
@@ -79447,41 +79447,41 @@
     <row r="2410">
       <c r="A2410" t="inlineStr">
         <is>
-          <t>SEK 1.2 billion</t>
+          <t>160 million euros</t>
         </is>
       </c>
       <c r="B2410" t="inlineStr"/>
       <c r="C2410" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2410" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E2410" t="n">
-        <v>1.2</v>
+        <v>160</v>
       </c>
       <c r="F2410" t="n">
-        <v>1200000000</v>
+        <v>160000000</v>
       </c>
       <c r="G2410" s="2" t="n">
-        <v>45536</v>
+        <v>45078</v>
       </c>
       <c r="H2410" t="n">
-        <v>105765700</v>
+        <v>160000000</v>
       </c>
       <c r="I2410" t="n">
-        <v>117079104</v>
+        <v>171152000</v>
       </c>
       <c r="J2410" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="2411">
       <c r="A2411" t="inlineStr">
         <is>
-          <t>160 million euros</t>
+          <t>€160 million ($176 million)</t>
         </is>
       </c>
       <c r="B2411" t="inlineStr"/>
@@ -79617,7 +79617,7 @@
     <row r="2415">
       <c r="A2415" t="inlineStr">
         <is>
-          <t>€160 million ($176 million)</t>
+          <t>€150 million</t>
         </is>
       </c>
       <c r="B2415" t="inlineStr"/>
@@ -79630,28 +79630,28 @@
         </is>
       </c>
       <c r="E2415" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F2415" t="n">
-        <v>160000000</v>
+        <v>150000000</v>
       </c>
       <c r="G2415" s="2" t="n">
-        <v>45078</v>
+        <v>43313</v>
       </c>
       <c r="H2415" t="n">
-        <v>160000000</v>
+        <v>150000000</v>
       </c>
       <c r="I2415" t="n">
-        <v>171152000</v>
+        <v>175440000</v>
       </c>
       <c r="J2415" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="2416">
       <c r="A2416" t="inlineStr">
         <is>
-          <t>€150 million</t>
+          <t>200 million euros</t>
         </is>
       </c>
       <c r="B2416" t="inlineStr"/>
@@ -79664,22 +79664,22 @@
         </is>
       </c>
       <c r="E2416" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F2416" t="n">
-        <v>150000000</v>
+        <v>200000000</v>
       </c>
       <c r="G2416" s="2" t="n">
-        <v>43313</v>
+        <v>44805</v>
       </c>
       <c r="H2416" t="n">
-        <v>150000000</v>
+        <v>200000000</v>
       </c>
       <c r="I2416" t="n">
-        <v>175440000</v>
+        <v>200080000</v>
       </c>
       <c r="J2416" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2417">
@@ -79701,16 +79701,16 @@
         <v>200</v>
       </c>
       <c r="F2417" t="n">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="G2417" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="H2417" t="n">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="I2417" t="n">
-        <v>200080000</v>
+        <v>100040000</v>
       </c>
       <c r="J2417" t="n">
         <v>2022</v>
@@ -79787,7 +79787,7 @@
     <row r="2420">
       <c r="A2420" t="inlineStr">
         <is>
-          <t>200 million euros</t>
+          <t>33 million euros</t>
         </is>
       </c>
       <c r="B2420" t="inlineStr"/>
@@ -79800,19 +79800,19 @@
         </is>
       </c>
       <c r="E2420" t="n">
-        <v>200</v>
+        <v>33</v>
       </c>
       <c r="F2420" t="n">
-        <v>100000000</v>
+        <v>33000000</v>
       </c>
       <c r="G2420" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="H2420" t="n">
-        <v>100000000</v>
+        <v>33000000</v>
       </c>
       <c r="I2420" t="n">
-        <v>100040000</v>
+        <v>33013200</v>
       </c>
       <c r="J2420" t="n">
         <v>2022</v>
@@ -79821,7 +79821,7 @@
     <row r="2421">
       <c r="A2421" t="inlineStr">
         <is>
-          <t>33 million euros</t>
+          <t>€35 million</t>
         </is>
       </c>
       <c r="B2421" t="inlineStr"/>
@@ -79834,22 +79834,22 @@
         </is>
       </c>
       <c r="E2421" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F2421" t="n">
-        <v>33000000</v>
+        <v>35000000</v>
       </c>
       <c r="G2421" s="2" t="n">
-        <v>44805</v>
+        <v>45901</v>
       </c>
       <c r="H2421" t="n">
-        <v>33000000</v>
+        <v>35000000</v>
       </c>
       <c r="I2421" t="n">
-        <v>33013200</v>
+        <v>40789000</v>
       </c>
       <c r="J2421" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2422">
@@ -79889,7 +79889,7 @@
     <row r="2423">
       <c r="A2423" t="inlineStr">
         <is>
-          <t>€35 million</t>
+          <t>up to USD $320 million</t>
         </is>
       </c>
       <c r="B2423" t="inlineStr"/>
@@ -79898,23 +79898,31 @@
       </c>
       <c r="D2423" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2423" t="n">
-        <v>35</v>
-      </c>
-      <c r="F2423" t="n">
-        <v>35000000</v>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E2423" t="inlineStr">
+        <is>
+          <t>[None, 320.0]</t>
+        </is>
+      </c>
+      <c r="F2423" t="inlineStr">
+        <is>
+          <t>[None, 320000000.0]</t>
+        </is>
       </c>
       <c r="G2423" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="H2423" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="I2423" t="n">
-        <v>40789000</v>
+        <v>45778</v>
+      </c>
+      <c r="H2423" t="inlineStr">
+        <is>
+          <t>[None, 281739743.0]</t>
+        </is>
+      </c>
+      <c r="I2423" t="inlineStr">
+        <is>
+          <t>[None, 320000000.0]</t>
+        </is>
       </c>
       <c r="J2423" t="n">
         <v>2025</v>
@@ -79923,40 +79931,32 @@
     <row r="2424">
       <c r="A2424" t="inlineStr">
         <is>
-          <t>up to USD $320 million</t>
+          <t>€2 billion</t>
         </is>
       </c>
       <c r="B2424" t="inlineStr"/>
       <c r="C2424" t="n">
-        <v>1000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D2424" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E2424" t="inlineStr">
-        <is>
-          <t>[None, 320.0]</t>
-        </is>
-      </c>
-      <c r="F2424" t="inlineStr">
-        <is>
-          <t>[None, 320000000.0]</t>
-        </is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2424" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2424" t="n">
+        <v>2000000000</v>
       </c>
       <c r="G2424" s="2" t="n">
-        <v>45778</v>
-      </c>
-      <c r="H2424" t="inlineStr">
-        <is>
-          <t>[None, 281739743.0]</t>
-        </is>
-      </c>
-      <c r="I2424" t="inlineStr">
-        <is>
-          <t>[None, 320000000.0]</t>
-        </is>
+        <v>45689</v>
+      </c>
+      <c r="H2424" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="I2424" t="n">
+        <v>2070666667</v>
       </c>
       <c r="J2424" t="n">
         <v>2025</v>
@@ -79999,12 +79999,12 @@
     <row r="2426">
       <c r="A2426" t="inlineStr">
         <is>
-          <t>€2 billion</t>
+          <t>EUR 150 million</t>
         </is>
       </c>
       <c r="B2426" t="inlineStr"/>
       <c r="C2426" t="n">
-        <v>1000000000</v>
+        <v>1000000</v>
       </c>
       <c r="D2426" t="inlineStr">
         <is>
@@ -80012,55 +80012,21 @@
         </is>
       </c>
       <c r="E2426" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="F2426" t="n">
-        <v>2000000000</v>
+        <v>150000000</v>
       </c>
       <c r="G2426" s="2" t="n">
-        <v>45689</v>
+        <v>44531</v>
       </c>
       <c r="H2426" t="n">
-        <v>2000000000</v>
+        <v>150000000</v>
       </c>
       <c r="I2426" t="n">
-        <v>2070666667</v>
+        <v>169710000</v>
       </c>
       <c r="J2426" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2427">
-      <c r="A2427" t="inlineStr">
-        <is>
-          <t>EUR 150 million</t>
-        </is>
-      </c>
-      <c r="B2427" t="inlineStr"/>
-      <c r="C2427" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D2427" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E2427" t="n">
-        <v>150</v>
-      </c>
-      <c r="F2427" t="n">
-        <v>150000000</v>
-      </c>
-      <c r="G2427" s="2" t="n">
-        <v>44531</v>
-      </c>
-      <c r="H2427" t="n">
-        <v>150000000</v>
-      </c>
-      <c r="I2427" t="n">
-        <v>169710000</v>
-      </c>
-      <c r="J2427" t="n">
         <v>2021</v>
       </c>
     </row>

--- a/reconcile/storage/output/check_investments.xlsx
+++ b/reconcile/storage/output/check_investments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2426"/>
+  <dimension ref="A1:J2446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80030,6 +80030,684 @@
         <v>2021</v>
       </c>
     </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>EUR 16.1 million</t>
+        </is>
+      </c>
+      <c r="B2427" t="inlineStr"/>
+      <c r="C2427" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2427" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2427" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F2427" t="n">
+        <v>16100000</v>
+      </c>
+      <c r="G2427" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="H2427" t="n">
+        <v>16100000</v>
+      </c>
+      <c r="I2427" t="n">
+        <v>17299450</v>
+      </c>
+      <c r="J2427" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>70 million euros each from three partners</t>
+        </is>
+      </c>
+      <c r="B2428" t="inlineStr">
+        <is>
+          <t>each from three partners</t>
+        </is>
+      </c>
+      <c r="C2428" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2428" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2428" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2428" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="G2428" s="2" t="n">
+        <v>44378</v>
+      </c>
+      <c r="H2428" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="I2428" t="n">
+        <v>83188000</v>
+      </c>
+      <c r="J2428" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>70 million euros each from three partners</t>
+        </is>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t>each from three partners</t>
+        </is>
+      </c>
+      <c r="C2429" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2429" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2429" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2429" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="G2429" s="2" t="n">
+        <v>44378</v>
+      </c>
+      <c r="H2429" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="I2429" t="n">
+        <v>83188000</v>
+      </c>
+      <c r="J2429" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>70 million euros</t>
+        </is>
+      </c>
+      <c r="B2430" t="inlineStr"/>
+      <c r="C2430" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2430" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2430" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2430" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="G2430" s="2" t="n">
+        <v>40725</v>
+      </c>
+      <c r="H2430" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="I2430" t="n">
+        <v>101416000</v>
+      </c>
+      <c r="J2430" t="n">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>70 million euros</t>
+        </is>
+      </c>
+      <c r="B2431" t="inlineStr"/>
+      <c r="C2431" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2431" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2431" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2431" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="G2431" s="2" t="n">
+        <v>40725</v>
+      </c>
+      <c r="H2431" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="I2431" t="n">
+        <v>101416000</v>
+      </c>
+      <c r="J2431" t="n">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>70 million euros each from three partners</t>
+        </is>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t>each from three partners</t>
+        </is>
+      </c>
+      <c r="C2432" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2432" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2432" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2432" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="G2432" s="2" t="n">
+        <v>40725</v>
+      </c>
+      <c r="H2432" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="I2432" t="n">
+        <v>101416000</v>
+      </c>
+      <c r="J2432" t="n">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>70 million euros each from three partners</t>
+        </is>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t>each from three partners</t>
+        </is>
+      </c>
+      <c r="C2433" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2433" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2433" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2433" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="G2433" s="2" t="n">
+        <v>40725</v>
+      </c>
+      <c r="H2433" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="I2433" t="n">
+        <v>101416000</v>
+      </c>
+      <c r="J2433" t="n">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>€100 million</t>
+        </is>
+      </c>
+      <c r="B2434" t="inlineStr"/>
+      <c r="C2434" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2434" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2434" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2434" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="G2434" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2434" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="I2434" t="n">
+        <v>116540000</v>
+      </c>
+      <c r="J2434" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>€37 million</t>
+        </is>
+      </c>
+      <c r="B2435" t="inlineStr"/>
+      <c r="C2435" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2435" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2435" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2435" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="G2435" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2435" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="I2435" t="n">
+        <v>43119800</v>
+      </c>
+      <c r="J2435" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr"/>
+      <c r="B2436" t="inlineStr"/>
+      <c r="C2436" t="inlineStr"/>
+      <c r="D2436" t="inlineStr"/>
+      <c r="E2436" t="inlineStr"/>
+      <c r="F2436" t="inlineStr"/>
+      <c r="G2436" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="H2436" t="inlineStr"/>
+      <c r="I2436" t="inlineStr"/>
+      <c r="J2436" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>€37m ($43m)</t>
+        </is>
+      </c>
+      <c r="B2437" t="inlineStr"/>
+      <c r="C2437" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2437" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2437" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2437" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="G2437" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2437" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="I2437" t="n">
+        <v>43119800</v>
+      </c>
+      <c r="J2437" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>€6.5bn ($7.15bn)</t>
+        </is>
+      </c>
+      <c r="B2438" t="inlineStr"/>
+      <c r="C2438" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2438" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2438" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F2438" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="G2438" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2438" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="I2438" t="n">
+        <v>7575100000</v>
+      </c>
+      <c r="J2438" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>€6.5bn ($7.15bn)</t>
+        </is>
+      </c>
+      <c r="B2439" t="inlineStr"/>
+      <c r="C2439" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2439" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2439" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F2439" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="G2439" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2439" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="I2439" t="n">
+        <v>7575100000</v>
+      </c>
+      <c r="J2439" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>€6.5bn ($7.15bn)</t>
+        </is>
+      </c>
+      <c r="B2440" t="inlineStr"/>
+      <c r="C2440" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2440" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2440" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F2440" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="G2440" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2440" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="I2440" t="n">
+        <v>7575100000</v>
+      </c>
+      <c r="J2440" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>€6.5bn ($7.15bn)</t>
+        </is>
+      </c>
+      <c r="B2441" t="inlineStr"/>
+      <c r="C2441" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2441" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2441" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F2441" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="G2441" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2441" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="I2441" t="n">
+        <v>7575100000</v>
+      </c>
+      <c r="J2441" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>€975m ($1.07bn)</t>
+        </is>
+      </c>
+      <c r="B2442" t="inlineStr"/>
+      <c r="C2442" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2442" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2442" t="n">
+        <v>975</v>
+      </c>
+      <c r="F2442" t="n">
+        <v>975000000</v>
+      </c>
+      <c r="G2442" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2442" t="n">
+        <v>975000000</v>
+      </c>
+      <c r="I2442" t="n">
+        <v>1136265000</v>
+      </c>
+      <c r="J2442" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>€975m ($1.07bn)</t>
+        </is>
+      </c>
+      <c r="B2443" t="inlineStr"/>
+      <c r="C2443" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2443" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2443" t="n">
+        <v>975</v>
+      </c>
+      <c r="F2443" t="n">
+        <v>975000000</v>
+      </c>
+      <c r="G2443" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2443" t="n">
+        <v>975000000</v>
+      </c>
+      <c r="I2443" t="n">
+        <v>1136265000</v>
+      </c>
+      <c r="J2443" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>€975m ($1.07bn)</t>
+        </is>
+      </c>
+      <c r="B2444" t="inlineStr"/>
+      <c r="C2444" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2444" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2444" t="n">
+        <v>975</v>
+      </c>
+      <c r="F2444" t="n">
+        <v>975000000</v>
+      </c>
+      <c r="G2444" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2444" t="n">
+        <v>975000000</v>
+      </c>
+      <c r="I2444" t="n">
+        <v>1136265000</v>
+      </c>
+      <c r="J2444" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>€975m ($1.07bn)</t>
+        </is>
+      </c>
+      <c r="B2445" t="inlineStr"/>
+      <c r="C2445" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2445" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2445" t="n">
+        <v>975</v>
+      </c>
+      <c r="F2445" t="n">
+        <v>975000000</v>
+      </c>
+      <c r="G2445" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H2445" t="n">
+        <v>975000000</v>
+      </c>
+      <c r="I2445" t="n">
+        <v>1136265000</v>
+      </c>
+      <c r="J2445" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>€100m ($111.7m)</t>
+        </is>
+      </c>
+      <c r="B2446" t="inlineStr"/>
+      <c r="C2446" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D2446" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E2446" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2446" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="G2446" s="2" t="n">
+        <v>45536</v>
+      </c>
+      <c r="H2446" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="I2446" t="n">
+        <v>110696667</v>
+      </c>
+      <c r="J2446" t="n">
+        <v>2024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
